--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,6 +727,1946 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>07:30:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>76 Igdir Belediyespor</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bodrum Belediyesi Bodrums</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Boluspor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Corum Belediyespor</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Erokspor A.S</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bandirmaspor</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Gimnasia Mendoza</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Talleres</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Instituto</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SE Palmeiras</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="G2" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -957,10 +957,10 @@
         <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>1.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="I4" t="n">
         <v>16.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" t="n">
         <v>2.76</v>
       </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.16</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
         <v>4.2</v>
@@ -1736,7 +1736,7 @@
         <v>2.04</v>
       </c>
       <c r="I7" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
         <v>2.08</v>
@@ -1781,13 +1781,13 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1835,7 +1835,7 @@
         <v>17.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
         <v>8.199999999999999</v>
@@ -1865,32 +1865,32 @@
         <v>14.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF7" t="n">
         <v>38</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.6</v>
       </c>
       <c r="BG7" t="n">
         <v>12</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="G8" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>2.22</v>
+        <v>1.41</v>
       </c>
       <c r="I8" t="n">
         <v>2.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3</v>
+        <v>1.58</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="H10" t="n">
         <v>2.3</v>
       </c>
       <c r="I10" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.18</v>
       </c>
       <c r="G11" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="H11" t="n">
         <v>4.6</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -766,7 +766,7 @@
         <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -957,10 +957,10 @@
         <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G7" t="n">
         <v>4.2</v>
@@ -1835,7 +1835,7 @@
         <v>17.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>8.199999999999999</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>2.98</v>
       </c>
       <c r="G8" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="I8" t="n">
         <v>2.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2124,10 +2124,10 @@
         <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K9" t="n">
         <v>3.2</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
         <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G2" t="n">
         <v>2.02</v>
@@ -766,7 +766,7 @@
         <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -775,152 +775,152 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
         <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I3" t="n">
         <v>2.2</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
         <v>2.52</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>2.76</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1781,46 +1781,46 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
         <v>9.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
         <v>11.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1862,35 +1862,35 @@
         <v>20</v>
       </c>
       <c r="AY7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>38</v>
+        <v>5.2</v>
       </c>
       <c r="BG7" t="n">
         <v>12</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="G8" t="n">
         <v>5.1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="I8" t="n">
         <v>2.7</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I10" t="n">
         <v>2.42</v>
@@ -2342,7 +2342,7 @@
         <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="H11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J11" t="n">
         <v>4.6</v>
       </c>
-      <c r="I11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.4</v>
-      </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -757,28 +757,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="I2" t="n">
         <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
         <v>3.95</v>
@@ -790,46 +790,46 @@
         <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="Y2" t="n">
-        <v>20</v>
+        <v>980</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AA2" t="n">
         <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AE2" t="n">
         <v>65</v>
@@ -841,19 +841,19 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AI2" t="n">
         <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -865,62 +865,62 @@
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.95</v>
+        <v>2.66</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>2.68</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>2.38</v>
       </c>
       <c r="AV2" t="n">
-        <v>13.5</v>
+        <v>2.68</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>2.94</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>2.46</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>2.68</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>2.96</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>3.05</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="BF2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>2.96</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
         <v>1.98</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>980</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
         <v>1.7</v>
@@ -1154,10 +1154,10 @@
         <v>2.5</v>
       </c>
       <c r="I4" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1178,7 +1178,7 @@
         <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>1.41</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
         <v>2.78</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="G6" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="I7" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1781,40 +1781,40 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
@@ -1826,71 +1826,71 @@
         <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.75</v>
+        <v>1.41</v>
       </c>
       <c r="G8" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.96</v>
+        <v>1.41</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
@@ -1954,7 +1954,7 @@
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.26</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.26</v>
+        <v>1.32</v>
       </c>
       <c r="I10" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="G11" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="H11" t="n">
-        <v>9.199999999999999</v>
+        <v>2.92</v>
       </c>
       <c r="I11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
         <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -757,28 +757,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
         <v>3.95</v>
@@ -787,7 +787,7 @@
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
         <v>1.8</v>
@@ -796,19 +796,19 @@
         <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="X2" t="n">
         <v>980</v>
@@ -823,7 +823,7 @@
         <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
@@ -847,7 +847,7 @@
         <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK2" t="n">
         <v>980</v>
@@ -865,62 +865,62 @@
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.66</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.68</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.86</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.38</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.68</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.94</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.68</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.05</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.86</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
         <v>1.98</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>980</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1014,13 +1014,13 @@
         <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
@@ -1032,19 +1032,19 @@
         <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
         <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1053,68 +1053,68 @@
         <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.6</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.52</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.56</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.73</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.73</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.73</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.52</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.61</v>
+        <v>16</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.64</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.73</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.59</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.73</v>
+        <v>4.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.73</v>
+        <v>4.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.73</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.68</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.73</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.73</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>1.41</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q5" t="n">
         <v>2.78</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1781,116 +1781,116 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.41</v>
+        <v>3.7</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="I8" t="n">
-        <v>3.35</v>
+        <v>2.68</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
@@ -1954,7 +1954,7 @@
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>2.24</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="K9" t="n">
         <v>3.45</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.32</v>
+        <v>2.38</v>
       </c>
       <c r="I10" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="J10" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="G11" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="H11" t="n">
-        <v>2.92</v>
+        <v>9.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH11"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +766,7 @@
         <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
@@ -790,13 +790,13 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
         <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
@@ -805,7 +805,7 @@
         <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
         <v>1.95</v>
@@ -892,7 +892,7 @@
         <v>9.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I3" t="n">
         <v>2.2</v>
@@ -972,7 +972,7 @@
         <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
         <v>4.1</v>
@@ -981,10 +981,10 @@
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="R3" t="n">
         <v>1.41</v>
@@ -993,10 +993,10 @@
         <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
         <v>1.83</v>
@@ -1059,7 +1059,7 @@
         <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.199999999999999</v>
@@ -1071,10 +1071,10 @@
         <v>19</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
         <v>8.199999999999999</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -1163,16 +1163,16 @@
         <v>5.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
@@ -1181,141 +1181,141 @@
         <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,42 +1325,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>2.78</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>2.88</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.78</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1381,10 +1381,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1393,123 +1393,123 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,42 +1519,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.34</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1587,123 +1587,123 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="I7" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1784,120 +1784,120 @@
         <v>15</v>
       </c>
       <c r="Y7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD7" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AE7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF7" t="n">
         <v>32</v>
       </c>
-      <c r="AB7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI7" t="n">
         <v>36</v>
       </c>
-      <c r="AG7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>48</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK7" t="n">
         <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
         <v>60</v>
       </c>
       <c r="AO7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>17.5</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="BA7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR7" t="n">
+      <c r="BC7" t="n">
         <v>11</v>
       </c>
-      <c r="AS7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD7" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,67 +1907,67 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I8" t="n">
         <v>3.7</v>
       </c>
-      <c r="G8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.22</v>
       </c>
-      <c r="I8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
@@ -1975,123 +1975,123 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,66 +2101,66 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.24</v>
+        <v>3.95</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="H9" t="n">
-        <v>3.75</v>
+        <v>2.18</v>
       </c>
       <c r="I9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S9" t="n">
         <v>4.8</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2169,123 +2169,123 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,66 +2295,66 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G10" t="n">
         <v>3.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="I10" t="n">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,310 +2363,3414 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Genk</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ferencvaros</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nottm Forest</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NK Celje</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Gimnasia Mendoza</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sigma Olomouc</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AEK Larnaca</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>17</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>190</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>350</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Brazilian Serie A</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Talleres</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Instituto</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SE Palmeiras</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Sao Paulo</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F27" t="n">
         <v>1.37</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G27" t="n">
         <v>1.45</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H27" t="n">
         <v>9.4</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I27" t="n">
         <v>13</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J27" t="n">
         <v>4.8</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K27" t="n">
         <v>5.6</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1.87</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2026-03-10 12:45:09</t>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>1.81</v>
       </c>
       <c r="G2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
@@ -787,10 +787,10 @@
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
         <v>1.39</v>
@@ -808,7 +808,7 @@
         <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X2" t="n">
         <v>980</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I3" t="n">
         <v>2.2</v>
@@ -972,7 +972,7 @@
         <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
         <v>4.1</v>
@@ -984,7 +984,7 @@
         <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
         <v>1.41</v>
@@ -1089,7 +1089,7 @@
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
         <v>4.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="O4" t="n">
         <v>1.23</v>
@@ -1187,10 +1187,10 @@
         <v>2.46</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.1</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,61 +1330,61 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1393,123 +1393,123 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD5" t="n">
         <v>15</v>
       </c>
-      <c r="Y5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU5" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BB5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE5" t="n">
         <v>34</v>
       </c>
-      <c r="BE5" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BF5" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,61 +1524,61 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="H6" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1587,123 +1587,123 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD6" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AE6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT6" t="n">
         <v>9.4</v>
       </c>
-      <c r="Z6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="AU6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BG6" t="n">
         <v>32</v>
       </c>
-      <c r="AB6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,61 +1718,61 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="I7" t="n">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1781,123 +1781,123 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH7" t="n">
         <v>22</v>
       </c>
-      <c r="AB7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AI7" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AK7" t="n">
         <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AO7" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AR7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AX7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AY7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BB7" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="BC7" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BD7" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BG7" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,61 +1912,61 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.18</v>
+        <v>3.05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="J8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1975,123 +1975,123 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
         <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AO8" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="AP8" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY8" t="n">
         <v>12</v>
       </c>
-      <c r="AR8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.5</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BC8" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.3</v>
+        <v>44</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="BF8" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,61 +2106,61 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="G9" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="H9" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="I9" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2169,123 +2169,123 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z9" t="n">
         <v>12</v>
       </c>
       <c r="AA9" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AK9" t="n">
         <v>60</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AO9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AP9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV9" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AY9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BB9" t="n">
-        <v>36</v>
+        <v>13.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="BE9" t="n">
-        <v>46</v>
+        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BG9" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,62 +2300,62 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="H10" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="I10" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.04</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.91</v>
-      </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
@@ -2363,123 +2363,123 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>8.6</v>
       </c>
-      <c r="Z10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AR10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS10" t="n">
         <v>10</v>
       </c>
-      <c r="AC10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AT10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD10" t="n">
         <v>12</v>
       </c>
-      <c r="AE10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="BE10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG10" t="n">
         <v>20</v>
       </c>
-      <c r="AG10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>28</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>32</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,61 +2494,61 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="I11" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2557,123 +2557,123 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AB11" t="n">
         <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK11" t="n">
         <v>30</v>
       </c>
-      <c r="AF11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>38</v>
-      </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AO11" t="n">
         <v>26</v>
       </c>
       <c r="AP11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT11" t="n">
         <v>10.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY11" t="n">
         <v>11</v>
       </c>
-      <c r="AW11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB11" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BC11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BD11" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BE11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BG11" t="n">
         <v>22</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2721,28 +2721,28 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2751,82 +2751,82 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
         <v>42</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR12" t="n">
         <v>21</v>
       </c>
-      <c r="AL12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>24</v>
-      </c>
       <c r="AS12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>34</v>
+        <v>5.3</v>
       </c>
       <c r="AX12" t="n">
         <v>12.5</v>
@@ -2838,36 +2838,36 @@
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>29</v>
+        <v>5.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>34</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.18</v>
+        <v>2.68</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="H13" t="n">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>2.02</v>
       </c>
       <c r="O13" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="R13" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.75</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H14" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>2.84</v>
+        <v>3.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AA14" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX14" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
         <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>24</v>
+        <v>3.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.8</v>
+        <v>3.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>19</v>
+        <v>3.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>19.5</v>
+        <v>3.9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,120 +3265,120 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="G15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.25</v>
       </c>
-      <c r="H15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
         <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AB15" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AG15" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK15" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM15" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.5</v>
+        <v>2.46</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.2</v>
+        <v>2.62</v>
       </c>
       <c r="AT15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>25</v>
+        <v>2.58</v>
       </c>
       <c r="AX15" t="n">
-        <v>18.5</v>
+        <v>2.52</v>
       </c>
       <c r="AY15" t="n">
-        <v>11.5</v>
+        <v>2.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6</v>
+        <v>2.48</v>
       </c>
       <c r="BA15" t="n">
-        <v>36</v>
+        <v>2.64</v>
       </c>
       <c r="BB15" t="n">
-        <v>46</v>
+        <v>2.64</v>
       </c>
       <c r="BC15" t="n">
-        <v>32</v>
+        <v>2.62</v>
       </c>
       <c r="BD15" t="n">
-        <v>42</v>
+        <v>2.64</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.4</v>
+        <v>2.74</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.4</v>
+        <v>2.74</v>
       </c>
       <c r="BG15" t="n">
-        <v>21</v>
+        <v>2.74</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>4.4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3506,7 +3506,7 @@
         <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R16" t="n">
         <v>1.46</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="n">
         <v>22</v>
@@ -3536,28 +3536,28 @@
         <v>55</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>24</v>
       </c>
       <c r="AE16" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
         <v>80</v>
@@ -3569,22 +3569,22 @@
         <v>16</v>
       </c>
       <c r="AL16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN16" t="n">
         <v>8</v>
       </c>
       <c r="AO16" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR16" t="n">
         <v>27</v>
@@ -3596,16 +3596,16 @@
         <v>8.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW16" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY16" t="n">
         <v>9</v>
@@ -3614,36 +3614,36 @@
         <v>19</v>
       </c>
       <c r="BA16" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BB16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE16" t="n">
         <v>40</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG16" t="n">
         <v>38</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,61 +3658,61 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.7</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
-        <v>2.06</v>
+        <v>3.65</v>
       </c>
       <c r="I17" t="n">
-        <v>2.14</v>
+        <v>3.75</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,123 +3721,123 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG17" t="n">
         <v>11</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AH17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV17" t="n">
         <v>14</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="AW17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY17" t="n">
         <v>10</v>
       </c>
-      <c r="AR17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="BB17" t="n">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="BC17" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BE17" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BF17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,61 +3852,61 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G18" t="n">
-        <v>2.42</v>
+        <v>2.82</v>
       </c>
       <c r="H18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
         <v>4.1</v>
       </c>
-      <c r="I18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>1.34</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3915,123 +3915,123 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,61 +4046,61 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="H19" t="n">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
       <c r="I19" t="n">
-        <v>1.88</v>
+        <v>2.52</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,116 +4109,116 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y19" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AA19" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AB19" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AD19" t="n">
         <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AF19" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AK19" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AO19" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AP19" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC19" t="n">
         <v>9.6</v>
       </c>
-      <c r="AS19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD19" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.1</v>
+        <v>9.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.24</v>
+        <v>3.7</v>
       </c>
       <c r="G20" t="n">
-        <v>1.27</v>
+        <v>3.95</v>
       </c>
       <c r="H20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>14.5</v>
       </c>
-      <c r="I20" t="n">
-        <v>17</v>
-      </c>
-      <c r="J20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>190</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>350</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>32</v>
-      </c>
       <c r="BA20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BC20" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="BD20" t="n">
         <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.6</v>
+        <v>25</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -4628,37 +4628,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1.87</v>
+        <v>5.4</v>
       </c>
       <c r="H22" t="n">
-        <v>4.5</v>
+        <v>1.79</v>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>1.88</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG22" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM22" t="n">
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>12.5</v>
+        <v>80</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AU22" t="n">
         <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AW22" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BB22" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,66 +4817,66 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.85</v>
+        <v>1.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.2</v>
+        <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>2.04</v>
+        <v>14.5</v>
       </c>
       <c r="I23" t="n">
-        <v>2.18</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>1.78</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,116 +4885,116 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>190</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AC23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>350</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU23" t="n">
         <v>14</v>
       </c>
-      <c r="AA23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR23" t="n">
+      <c r="AV23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY23" t="n">
         <v>11</v>
       </c>
-      <c r="AS23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT23" t="n">
+      <c r="AZ23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC23" t="n">
         <v>12</v>
       </c>
-      <c r="AU23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD23" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>8.199999999999999</v>
+        <v>2.42</v>
       </c>
       <c r="H24" t="n">
-        <v>1.41</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>2.68</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="n">
-        <v>1.59</v>
+        <v>2.76</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,42 +5205,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="G25" t="n">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="H25" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
         <v>4.8</v>
       </c>
       <c r="J25" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.88</v>
+        <v>1.96</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5261,10 +5261,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5273,116 +5273,116 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -5399,42 +5399,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="G26" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H26" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="I26" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5455,10 +5455,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5467,310 +5467,892 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-10 17:02:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Talleres</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Instituto</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-10 17:02:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Brazilian Serie A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SE Palmeiras</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-10 17:02:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Sao Paulo</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F30" t="n">
         <v>1.37</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G30" t="n">
         <v>1.45</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H30" t="n">
         <v>9.4</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I30" t="n">
         <v>13</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J30" t="n">
         <v>4.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K30" t="n">
         <v>5.6</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q30" t="n">
         <v>1.87</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-03-10 14:53:58</t>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH30"/>
+  <dimension ref="A1:BH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,16 +760,16 @@
         <v>1.81</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -787,16 +787,16 @@
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
@@ -808,7 +808,7 @@
         <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
         <v>980</v>
@@ -892,7 +892,7 @@
         <v>9.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
@@ -904,7 +904,7 @@
         <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
         <v>4.4</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Altinordu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Karaman Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.98</v>
+        <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>1.76</v>
       </c>
       <c r="O3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.24</v>
       </c>
-      <c r="P3" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>1.24</v>
       </c>
       <c r="T3" t="n">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erokspor A.S</t>
+          <t>Beyoglu Yeni Carsi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bandirmaspor</t>
+          <t>Sanliurfaspor</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="G4" t="n">
-        <v>1.62</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>980</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.26</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.46</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1193,10 +1193,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
       <c r="G5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I5" t="n">
         <v>2.16</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.8</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z5" t="n">
         <v>16</v>
       </c>
-      <c r="Z5" t="n">
-        <v>27</v>
-      </c>
       <c r="AA5" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO5" t="n">
         <v>15</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>36</v>
       </c>
       <c r="AP5" t="n">
         <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="AY5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>30</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Estonian Esiliiga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>FC Maardu</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>FC Elva</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.11</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.04</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Erokspor A.S</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Bandirmaspor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.95</v>
+        <v>1.45</v>
       </c>
       <c r="G7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR7" t="n">
         <v>4.1</v>
       </c>
-      <c r="H7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11</v>
-      </c>
       <c r="AS7" t="n">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.5</v>
+        <v>3.85</v>
       </c>
       <c r="AW7" t="n">
-        <v>24</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>24</v>
+        <v>3.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>15.5</v>
+        <v>3.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>3.75</v>
       </c>
       <c r="BA7" t="n">
-        <v>44</v>
+        <v>4.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>46</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>34</v>
+        <v>5.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="H8" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="I8" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S8" t="n">
         <v>3.5</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AB8" t="n">
         <v>12</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK8" t="n">
         <v>30</v>
       </c>
-      <c r="AF8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>38</v>
-      </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN8" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>26</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT8" t="n">
         <v>10.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY8" t="n">
         <v>11</v>
       </c>
-      <c r="AW8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
         <v>36</v>
       </c>
       <c r="BC8" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BD8" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BG8" t="n">
         <v>22</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="I9" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB9" t="n">
         <v>12</v>
       </c>
-      <c r="AA9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>16</v>
-      </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AJ9" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AK9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL9" t="n">
         <v>60</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>65</v>
       </c>
       <c r="AM9" t="n">
         <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AO9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD9" t="n">
         <v>14</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="BE9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF9" t="n">
         <v>13</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>12</v>
-      </c>
       <c r="BG9" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="G10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.55</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV10" t="n">
         <v>9.4</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AW10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AA10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="BD10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG10" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>20</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="H11" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE11" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO11" t="n">
+      <c r="BF11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG11" t="n">
         <v>26</v>
       </c>
-      <c r="AP11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>22</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H12" t="n">
         <v>2.18</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.45</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X12" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>7.6</v>
       </c>
       <c r="Z12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE12" t="n">
         <v>27</v>
       </c>
-      <c r="AA12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>42</v>
-      </c>
       <c r="AF12" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK12" t="n">
         <v>60</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>28</v>
-      </c>
       <c r="AL12" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AN12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>20</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="BA12" t="n">
         <v>46</v>
       </c>
-      <c r="AP12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR12" t="n">
+      <c r="BB12" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG12" t="n">
         <v>21</v>
       </c>
-      <c r="AS12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>26</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="G13" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.15</v>
       </c>
-      <c r="J13" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.02</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.79</v>
+        <v>2.52</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>44</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="P14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.64</v>
-      </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AK14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="n">
         <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AO14" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AP14" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.95</v>
+        <v>26</v>
       </c>
       <c r="AX14" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.9</v>
+        <v>46</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.8</v>
+        <v>32</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.95</v>
+        <v>44</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.1</v>
+        <v>38</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.7</v>
+        <v>30</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.9</v>
+        <v>22</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.92</v>
+        <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>2.18</v>
       </c>
       <c r="H15" t="n">
-        <v>2.46</v>
+        <v>3.65</v>
       </c>
       <c r="I15" t="n">
-        <v>2.78</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="X15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AR15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV15" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="AW15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY15" t="n">
         <v>10</v>
       </c>
-      <c r="AD15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AZ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD15" t="n">
         <v>30</v>
       </c>
-      <c r="AG15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>2.64</v>
-      </c>
       <c r="BE15" t="n">
-        <v>2.74</v>
+        <v>34</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.74</v>
+        <v>12.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.74</v>
+        <v>30</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="G16" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="H16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>980</v>
+      </c>
+      <c r="J16" t="n">
         <v>6.2</v>
       </c>
-      <c r="I16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.4</v>
-      </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>2.44</v>
       </c>
       <c r="O16" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>2.98</v>
+        <v>1.98</v>
       </c>
       <c r="T16" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="H17" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="I17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U17" t="n">
         <v>2.08</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.1</v>
-      </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AA17" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
         <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AK17" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AO17" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>23</v>
+        <v>4.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="AT17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>38</v>
+        <v>4.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
-        <v>25</v>
+        <v>4.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>40</v>
+        <v>5.3</v>
       </c>
       <c r="BF17" t="n">
         <v>16</v>
       </c>
       <c r="BG17" t="n">
-        <v>26</v>
+        <v>4.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="H18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I18" t="n">
         <v>2.72</v>
       </c>
-      <c r="I18" t="n">
-        <v>2.84</v>
-      </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
         <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
         <v>32</v>
       </c>
       <c r="AF18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AJ18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN18" t="n">
         <v>44</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AO18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC18" t="n">
         <v>32</v>
       </c>
-      <c r="AL18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>25</v>
-      </c>
       <c r="BD18" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
         <v>8.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>19</v>
+        <v>7.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="G19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I19" t="n">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="J19" t="n">
         <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X19" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>10</v>
       </c>
-      <c r="Z19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>9</v>
-      </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
       </c>
       <c r="AV19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>16.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BB19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BC19" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BE19" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.95</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
       <c r="T20" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR20" t="n">
         <v>14</v>
       </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AS20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA20" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BB20" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BC20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE20" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BF20" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="G21" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K21" t="n">
         <v>3</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.3</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.78</v>
-      </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H22" t="n">
         <v>4.7</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>5.4</v>
       </c>
-      <c r="H22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.88</v>
-      </c>
       <c r="J22" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P22" t="n">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X22" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF22" t="n">
         <v>11</v>
       </c>
-      <c r="Z22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>48</v>
-      </c>
       <c r="AG22" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="AI22" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="AJ22" t="n">
-        <v>150</v>
+        <v>980</v>
       </c>
       <c r="AK22" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="AL22" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="AN22" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="AO22" t="n">
-        <v>14.5</v>
+        <v>220</v>
       </c>
       <c r="AP22" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="AQ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR22" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AS22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX22" t="n">
         <v>9.6</v>
       </c>
-      <c r="AS22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4</v>
-      </c>
       <c r="AY22" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -4837,130 +4837,130 @@
         <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" t="n">
         <v>7.4</v>
       </c>
-      <c r="K23" t="n">
-        <v>7.6</v>
-      </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P23" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T23" t="n">
         <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X23" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z23" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE23" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AF23" t="n">
         <v>7.2</v>
       </c>
       <c r="AG23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AI23" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AK23" t="n">
         <v>14.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM23" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX23" t="n">
         <v>6.4</v>
@@ -4969,39 +4969,39 @@
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="BB23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="BF23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42</v>
+        <v>5.4</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="I24" t="n">
-        <v>4.9</v>
+        <v>1.88</v>
       </c>
       <c r="J24" t="n">
-        <v>2.76</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P24" t="n">
-        <v>1.34</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -5219,88 +5219,88 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G25" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
         <v>3.9</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P25" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
         <v>1.96</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X25" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD25" t="n">
         <v>19</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
         <v>1000</v>
@@ -5309,87 +5309,87 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AT25" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW25" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
         <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BE25" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BF25" t="n">
         <v>11</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H26" t="n">
         <v>2.04</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="U26" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="Y26" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF26" t="n">
         <v>32</v>
       </c>
-      <c r="AB26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP26" t="n">
+      <c r="AR26" t="n">
         <v>12</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>11</v>
       </c>
       <c r="AS26" t="n">
         <v>21</v>
       </c>
       <c r="AT26" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV26" t="n">
         <v>9.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY26" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC26" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE26" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF26" t="n">
-        <v>38</v>
+        <v>5.1</v>
       </c>
       <c r="BG26" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.7</v>
+        <v>1.61</v>
       </c>
       <c r="G27" t="n">
-        <v>5.1</v>
+        <v>1.62</v>
       </c>
       <c r="H27" t="n">
-        <v>1.96</v>
+        <v>6.2</v>
       </c>
       <c r="I27" t="n">
-        <v>2.68</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.32</v>
+        <v>4.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.72</v>
+        <v>1.79</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.24</v>
+        <v>2.72</v>
       </c>
       <c r="G28" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="H28" t="n">
-        <v>3.75</v>
+        <v>2.74</v>
       </c>
       <c r="I28" t="n">
-        <v>4.9</v>
+        <v>2.84</v>
       </c>
       <c r="J28" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>1.92</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>2.18</v>
       </c>
       <c r="G29" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="H29" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="I29" t="n">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.75</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -6175,184 +6175,1348 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-11 04:33:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-11 04:33:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Talleres</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Instituto</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-11 04:33:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SE Palmeiras</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X33" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-11 04:33:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Sao Paulo</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="F34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G34" t="n">
         <v>1.45</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I34" t="n">
+        <v>11</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>430</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>290</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU34" t="n">
         <v>9.4</v>
       </c>
-      <c r="I30" t="n">
+      <c r="AV34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-11 04:33:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-11 04:33:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X36" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF36" t="n">
         <v>13</v>
       </c>
-      <c r="J30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2026-03-10 17:02:27</t>
+      <c r="AG36" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -763,10 +763,10 @@
         <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -784,19 +784,19 @@
         <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
         <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
@@ -805,7 +805,7 @@
         <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
         <v>1.98</v>
@@ -823,7 +823,7 @@
         <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
@@ -865,28 +865,28 @@
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
         <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="AV2" t="n">
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
@@ -907,20 +907,20 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1360,10 +1360,10 @@
         <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
@@ -1372,7 +1372,7 @@
         <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.41</v>
@@ -1381,10 +1381,10 @@
         <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
         <v>1.86</v>
@@ -1429,80 +1429,80 @@
         <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AK5" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO5" t="n">
         <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
         <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF5" t="n">
         <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.45</v>
       </c>
       <c r="G7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="H7" t="n">
         <v>6.4</v>
@@ -1766,7 +1766,7 @@
         <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
         <v>1.9</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1945,13 +1945,13 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
@@ -1963,7 +1963,7 @@
         <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U8" t="n">
         <v>2.18</v>
@@ -1975,7 +1975,7 @@
         <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -1987,7 +1987,7 @@
         <v>44</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
         <v>7.8</v>
@@ -2074,7 +2074,7 @@
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BF8" t="n">
         <v>22</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
         <v>3.5</v>
@@ -2521,7 +2521,7 @@
         <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
@@ -2536,7 +2536,7 @@
         <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>4.1</v>
@@ -2742,10 +2742,10 @@
         <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W12" t="n">
         <v>1.32</v>
@@ -2844,10 +2844,10 @@
         <v>36</v>
       </c>
       <c r="BC12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BD12" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE12" t="n">
         <v>46</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
         <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q13" t="n">
         <v>2.52</v>
@@ -2972,13 +2972,13 @@
         <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
         <v>65</v>
@@ -2990,7 +2990,7 @@
         <v>70</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
         <v>60</v>
@@ -3002,7 +3002,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR13" t="n">
         <v>13.5</v>
@@ -3011,7 +3011,7 @@
         <v>34</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
         <v>6.6</v>
@@ -3023,19 +3023,19 @@
         <v>30</v>
       </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BB13" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BC13" t="n">
         <v>40</v>
@@ -3047,14 +3047,14 @@
         <v>44</v>
       </c>
       <c r="BF13" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BG13" t="n">
         <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I14" t="n">
         <v>2.58</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
@@ -3103,7 +3103,7 @@
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
@@ -3136,7 +3136,7 @@
         <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X14" t="n">
         <v>13</v>
@@ -3187,7 +3187,7 @@
         <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
         <v>25</v>
@@ -3241,14 +3241,14 @@
         <v>38</v>
       </c>
       <c r="BF14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG14" t="n">
         <v>22</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.75</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.7</v>
-      </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.36</v>
@@ -3306,7 +3306,7 @@
         <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
         <v>2.14</v>
@@ -3327,10 +3327,10 @@
         <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X15" t="n">
         <v>16.5</v>
@@ -3339,7 +3339,7 @@
         <v>15.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA15" t="n">
         <v>70</v>
@@ -3354,7 +3354,7 @@
         <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
@@ -3366,7 +3366,7 @@
         <v>16.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="AJ15" t="n">
         <v>27</v>
@@ -3378,7 +3378,7 @@
         <v>34</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
         <v>14</v>
@@ -3405,7 +3405,7 @@
         <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>36</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -3473,64 +3473,64 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="I16" t="n">
-        <v>980</v>
+        <v>14.5</v>
       </c>
       <c r="J16" t="n">
         <v>6.2</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>2.44</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W16" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,104 +3539,104 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G17" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H17" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
         <v>1.41</v>
@@ -3691,34 +3691,34 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
         <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X17" t="n">
         <v>16.5</v>
@@ -3730,16 +3730,16 @@
         <v>980</v>
       </c>
       <c r="AA17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
         <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
         <v>46</v>
@@ -3757,80 +3757,80 @@
         <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL17" t="n">
         <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
         <v>980</v>
       </c>
       <c r="AP17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AR17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX17" t="n">
         <v>13.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB17" t="n">
         <v>5</v>
       </c>
-      <c r="BB17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BC17" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF17" t="n">
         <v>16</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -3861,25 +3861,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H18" t="n">
         <v>2.42</v>
       </c>
       <c r="I18" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
         <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -3927,7 +3927,7 @@
         <v>40</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
         <v>7.8</v>
@@ -3978,7 +3978,7 @@
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT18" t="n">
         <v>9.4</v>
@@ -4002,29 +4002,29 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
       </c>
       <c r="BD18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF18" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>7.6</v>
       </c>
       <c r="BG18" t="n">
         <v>20</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -4058,13 +4058,13 @@
         <v>2.68</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I19" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J19" t="n">
         <v>3.4</v>
@@ -4073,7 +4073,7 @@
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H20" t="n">
         <v>2.48</v>
@@ -4288,7 +4288,7 @@
         <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
         <v>1.86</v>
@@ -4306,10 +4306,10 @@
         <v>12.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA20" t="n">
         <v>38</v>
@@ -4357,7 +4357,7 @@
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ20" t="n">
         <v>9</v>
@@ -4402,7 +4402,7 @@
         <v>42</v>
       </c>
       <c r="BE20" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF20" t="n">
         <v>34</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
         <v>980</v>
       </c>
       <c r="AK21" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AL21" t="n">
         <v>120</v>
@@ -4581,7 +4581,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BA21" t="n">
         <v>7.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -4646,13 +4646,13 @@
         <v>4.7</v>
       </c>
       <c r="I22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.61</v>
@@ -4661,10 +4661,10 @@
         <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O22" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P22" t="n">
         <v>1.47</v>
@@ -4679,13 +4679,13 @@
         <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
         <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W22" t="n">
         <v>1.86</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
         <v>17.5</v>
@@ -4858,10 +4858,10 @@
         <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
         <v>1.66</v>
@@ -4873,7 +4873,7 @@
         <v>2.66</v>
       </c>
       <c r="T23" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
         <v>1.67</v>
@@ -4882,7 +4882,7 @@
         <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X23" t="n">
         <v>23</v>
@@ -4906,16 +4906,16 @@
         <v>60</v>
       </c>
       <c r="AE23" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AF23" t="n">
         <v>7.2</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI23" t="n">
         <v>310</v>
@@ -4924,7 +4924,7 @@
         <v>9</v>
       </c>
       <c r="AK23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
         <v>50</v>
@@ -4933,34 +4933,34 @@
         <v>270</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AO23" t="n">
         <v>490</v>
       </c>
       <c r="AP23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AR23" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AS23" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
         <v>13.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AW23" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AX23" t="n">
         <v>6.4</v>
@@ -4969,10 +4969,10 @@
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BA23" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BB23" t="n">
         <v>8.199999999999999</v>
@@ -4981,20 +4981,20 @@
         <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BE23" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G24" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="I24" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
         <v>4</v>
@@ -5049,34 +5049,34 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
         <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V24" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
         <v>16.5</v>
@@ -5103,7 +5103,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AG24" t="n">
         <v>21</v>
@@ -5112,10 +5112,10 @@
         <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="n">
         <v>70</v>
@@ -5136,10 +5136,10 @@
         <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
         <v>17</v>
@@ -5157,38 +5157,38 @@
         <v>16.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY24" t="n">
         <v>16.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC24" t="n">
         <v>7.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="BE24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24" t="n">
         <v>50</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G25" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
         <v>5</v>
@@ -5258,19 +5258,19 @@
         <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
         <v>1.84</v>
       </c>
       <c r="U25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V25" t="n">
         <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X25" t="n">
         <v>15</v>
@@ -5285,7 +5285,7 @@
         <v>120</v>
       </c>
       <c r="AB25" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="AC25" t="n">
         <v>8.6</v>
@@ -5327,7 +5327,7 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
@@ -5336,7 +5336,7 @@
         <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
         <v>8.199999999999999</v>
@@ -5345,10 +5345,10 @@
         <v>8</v>
       </c>
       <c r="AV25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
         <v>10</v>
@@ -5360,29 +5360,29 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="BB25" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC25" t="n">
         <v>17.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="BF25" t="n">
         <v>11</v>
       </c>
       <c r="BG25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>3.95</v>
       </c>
       <c r="H26" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I26" t="n">
         <v>2.14</v>
@@ -5443,13 +5443,13 @@
         <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
         <v>2.88</v>
@@ -5479,7 +5479,7 @@
         <v>29</v>
       </c>
       <c r="AB26" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC26" t="n">
         <v>10</v>
@@ -5500,13 +5500,13 @@
         <v>17</v>
       </c>
       <c r="AI26" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ26" t="n">
         <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5515,7 +5515,7 @@
         <v>95</v>
       </c>
       <c r="AN26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO26" t="n">
         <v>14.5</v>
@@ -5554,29 +5554,29 @@
         <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC26" t="n">
         <v>36</v>
       </c>
       <c r="BD26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF26" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>5.1</v>
       </c>
       <c r="BG26" t="n">
         <v>10.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
         <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS27" t="n">
         <v>44</v>
@@ -5736,41 +5736,41 @@
         <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AX27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BB27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE27" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG27" t="n">
         <v>38</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>3.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6112,7 +6112,7 @@
         <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AT29" t="n">
         <v>8.800000000000001</v>
@@ -6136,7 +6136,7 @@
         <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB29" t="n">
         <v>25</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G30" t="n">
         <v>4.1</v>
@@ -6201,13 +6201,13 @@
         <v>2.08</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
         <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
@@ -6276,7 +6276,7 @@
         <v>22</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ30" t="n">
         <v>1000</v>
@@ -6294,7 +6294,7 @@
         <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP30" t="n">
         <v>12.5</v>
@@ -6330,16 +6330,16 @@
         <v>16</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB30" t="n">
         <v>6.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE30" t="n">
         <v>6.4</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6395,10 +6395,10 @@
         <v>2.48</v>
       </c>
       <c r="J31" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L31" t="n">
         <v>1.6</v>
@@ -6413,7 +6413,7 @@
         <v>1.57</v>
       </c>
       <c r="P31" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q31" t="n">
         <v>2.74</v>
@@ -6434,7 +6434,7 @@
         <v>1.68</v>
       </c>
       <c r="W31" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
         <v>8.199999999999999</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
         <v>4.4</v>
       </c>
       <c r="J32" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
         <v>3.2</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6777,10 +6777,10 @@
         <v>3.4</v>
       </c>
       <c r="H33" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I33" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
@@ -6819,7 +6819,7 @@
         <v>2.2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W33" t="n">
         <v>1.41</v>
@@ -6840,7 +6840,7 @@
         <v>15.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD33" t="n">
         <v>13.5</v>
@@ -6852,7 +6852,7 @@
         <v>26</v>
       </c>
       <c r="AG33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH33" t="n">
         <v>19.5</v>
@@ -6864,7 +6864,7 @@
         <v>60</v>
       </c>
       <c r="AK33" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AL33" t="n">
         <v>55</v>
@@ -6888,7 +6888,7 @@
         <v>12</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT33" t="n">
         <v>11.5</v>
@@ -6900,7 +6900,7 @@
         <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX33" t="n">
         <v>18.5</v>
@@ -6912,29 +6912,29 @@
         <v>14</v>
       </c>
       <c r="BA33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC33" t="n">
         <v>5</v>
       </c>
-      <c r="BB33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD33" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.9</v>
+        <v>24</v>
       </c>
       <c r="BG33" t="n">
         <v>14</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>1.41</v>
       </c>
       <c r="G34" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="H34" t="n">
         <v>9.199999999999999</v>
@@ -7061,7 +7061,7 @@
         <v>17</v>
       </c>
       <c r="AL34" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AM34" t="n">
         <v>200</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -7165,19 +7165,19 @@
         <v>3.8</v>
       </c>
       <c r="H35" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I35" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="J35" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="K35" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="M35" t="n">
         <v>1.16</v>
@@ -7186,7 +7186,7 @@
         <v>2.22</v>
       </c>
       <c r="O35" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P35" t="n">
         <v>1.41</v>
@@ -7204,10 +7204,10 @@
         <v>2.32</v>
       </c>
       <c r="U35" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V35" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W35" t="n">
         <v>1.35</v>
@@ -7246,13 +7246,13 @@
         <v>980</v>
       </c>
       <c r="AI35" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ35" t="n">
         <v>95</v>
       </c>
       <c r="AK35" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL35" t="n">
         <v>130</v>
@@ -7276,7 +7276,7 @@
         <v>10.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AT35" t="n">
         <v>7.6</v>
@@ -7285,10 +7285,10 @@
         <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW35" t="n">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX35" t="n">
         <v>7.2</v>
@@ -7297,32 +7297,32 @@
         <v>14.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BA35" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD35" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BE35" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF35" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>9.6</v>
       </c>
       <c r="BG35" t="n">
         <v>8.6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
         <v>3.9</v>
       </c>
       <c r="L36" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
@@ -7383,7 +7383,7 @@
         <v>1.36</v>
       </c>
       <c r="P36" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q36" t="n">
         <v>2.02</v>
@@ -7482,7 +7482,7 @@
         <v>7</v>
       </c>
       <c r="AW36" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AX36" t="n">
         <v>11</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G2" t="n">
         <v>2.02</v>
@@ -766,10 +766,10 @@
         <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -784,19 +784,19 @@
         <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
@@ -823,7 +823,7 @@
         <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
@@ -865,28 +865,28 @@
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
         <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV2" t="n">
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
@@ -907,20 +907,20 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1363,16 +1363,16 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
         <v>1.41</v>
@@ -1381,10 +1381,10 @@
         <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
         <v>1.86</v>
@@ -1429,10 +1429,10 @@
         <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="n">
         <v>60</v>
@@ -1447,10 +1447,10 @@
         <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR5" t="n">
         <v>10.5</v>
@@ -1462,47 +1462,47 @@
         <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE5" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BG5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="G7" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="H7" t="n">
         <v>6.4</v>
@@ -1742,7 +1742,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.28</v>
@@ -1778,7 +1778,7 @@
         <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
         <v>90</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
         <v>26</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.39</v>
@@ -2184,7 +2184,7 @@
         <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>11.5</v>
@@ -2217,7 +2217,7 @@
         <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO9" t="n">
         <v>23</v>
@@ -2268,7 +2268,7 @@
         <v>14</v>
       </c>
       <c r="BE9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF9" t="n">
         <v>13</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.92</v>
       </c>
-      <c r="I10" t="n">
-        <v>1.93</v>
-      </c>
       <c r="J10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.95</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
@@ -2333,7 +2333,7 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
@@ -2351,16 +2351,16 @@
         <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
         <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
         <v>15</v>
@@ -2390,7 +2390,7 @@
         <v>34</v>
       </c>
       <c r="AG10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH10" t="n">
         <v>19.5</v>
@@ -2411,10 +2411,10 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP10" t="n">
         <v>13</v>
@@ -2429,7 +2429,7 @@
         <v>19</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
         <v>7.8</v>
@@ -2441,7 +2441,7 @@
         <v>18</v>
       </c>
       <c r="AX10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2453,26 +2453,26 @@
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BE10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG10" t="n">
         <v>11.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>2.26</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I11" t="n">
         <v>3.7</v>
@@ -2533,7 +2533,7 @@
         <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>1.91</v>
@@ -2641,7 +2641,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
         <v>7.2</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2718,10 +2718,10 @@
         <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1.47</v>
@@ -2841,10 +2841,10 @@
         <v>46</v>
       </c>
       <c r="BB12" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BC12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BD12" t="n">
         <v>36</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O13" t="n">
         <v>1.49</v>
@@ -2972,13 +2972,13 @@
         <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
         <v>65</v>
@@ -3002,7 +3002,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR13" t="n">
         <v>13.5</v>
@@ -3032,10 +3032,10 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BB13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BC13" t="n">
         <v>40</v>
@@ -3047,14 +3047,14 @@
         <v>44</v>
       </c>
       <c r="BF13" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BG13" t="n">
         <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
         <v>2.54</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
         <v>3.75</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J15" t="n">
         <v>3.75</v>
@@ -3324,25 +3324,25 @@
         <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X15" t="n">
         <v>16.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z15" t="n">
         <v>28</v>
       </c>
       <c r="AA15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB15" t="n">
         <v>11</v>
@@ -3354,10 +3354,10 @@
         <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
@@ -3369,7 +3369,7 @@
         <v>48</v>
       </c>
       <c r="AJ15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK15" t="n">
         <v>21</v>
@@ -3384,10 +3384,10 @@
         <v>14</v>
       </c>
       <c r="AO15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>14.5</v>
@@ -3405,7 +3405,7 @@
         <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
         <v>36</v>
@@ -3414,35 +3414,35 @@
         <v>12.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
         <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE15" t="n">
         <v>34</v>
       </c>
       <c r="BF15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG15" t="n">
         <v>30</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>1.23</v>
       </c>
       <c r="G16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H16" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
         <v>14.5</v>
@@ -3524,7 +3524,7 @@
         <v>1.07</v>
       </c>
       <c r="W16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="X16" t="n">
         <v>42</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>2.56</v>
       </c>
       <c r="H17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I17" t="n">
         <v>3.45</v>
@@ -3682,10 +3682,10 @@
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3775,7 +3775,7 @@
         <v>980</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>11.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
         <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
         <v>1.58</v>
@@ -3921,10 +3921,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AB18" t="n">
         <v>11.5</v>
@@ -3978,7 +3978,7 @@
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT18" t="n">
         <v>9.4</v>
@@ -3993,7 +3993,7 @@
         <v>22</v>
       </c>
       <c r="AX18" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY18" t="n">
         <v>11.5</v>
@@ -4002,29 +4002,29 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
       </c>
       <c r="BD18" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BG18" t="n">
         <v>20</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I19" t="n">
         <v>2.82</v>
@@ -4103,7 +4103,7 @@
         <v>2.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W19" t="n">
         <v>1.49</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I20" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>3.45</v>
@@ -4276,19 +4276,19 @@
         <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R20" t="n">
         <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T20" t="n">
         <v>1.86</v>
@@ -4312,7 +4312,7 @@
         <v>15.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB20" t="n">
         <v>11.5</v>
@@ -4324,10 +4324,10 @@
         <v>11.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
         <v>13.5</v>
@@ -4336,7 +4336,7 @@
         <v>18.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ20" t="n">
         <v>60</v>
@@ -4354,7 +4354,7 @@
         <v>40</v>
       </c>
       <c r="AO20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
         <v>11</v>
@@ -4378,13 +4378,13 @@
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
         <v>19</v>
       </c>
       <c r="AY20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>16.5</v>
@@ -4402,7 +4402,7 @@
         <v>42</v>
       </c>
       <c r="BE20" t="n">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="BF20" t="n">
         <v>34</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>4.8</v>
       </c>
       <c r="J21" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
@@ -4494,7 +4494,7 @@
         <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X21" t="n">
         <v>6.6</v>
@@ -4509,7 +4509,7 @@
         <v>160</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC21" t="n">
         <v>7.6</v>
@@ -4560,7 +4560,7 @@
         <v>19.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT21" t="n">
         <v>5.2</v>
@@ -4572,7 +4572,7 @@
         <v>18.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -4584,29 +4584,29 @@
         <v>27</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
         <v>38</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L22" t="n">
         <v>1.61</v>
@@ -4661,31 +4661,31 @@
         <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O22" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="P22" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
         <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
         <v>1.86</v>
@@ -4718,7 +4718,7 @@
         <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
         <v>980</v>
@@ -4736,25 +4736,25 @@
         <v>70</v>
       </c>
       <c r="AM22" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN22" t="n">
         <v>980</v>
       </c>
       <c r="AO22" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
         <v>5.6</v>
@@ -4763,10 +4763,10 @@
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX22" t="n">
         <v>9.6</v>
@@ -4775,32 +4775,32 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF22" t="n">
         <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v>7.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
@@ -4864,7 +4864,7 @@
         <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R23" t="n">
         <v>1.55</v>
@@ -4882,7 +4882,7 @@
         <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="X23" t="n">
         <v>23</v>
@@ -4915,7 +4915,7 @@
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI23" t="n">
         <v>310</v>
@@ -4951,7 +4951,7 @@
         <v>18.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU23" t="n">
         <v>13.5</v>
@@ -4981,7 +4981,7 @@
         <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BE23" t="n">
         <v>18</v>
@@ -4990,11 +4990,11 @@
         <v>4.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G24" t="n">
         <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I24" t="n">
         <v>1.9</v>
@@ -5040,7 +5040,7 @@
         <v>3.8</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
         <v>1.39</v>
@@ -5049,7 +5049,7 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O24" t="n">
         <v>1.31</v>
@@ -5058,19 +5058,19 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V24" t="n">
         <v>2.1</v>
@@ -5091,7 +5091,7 @@
         <v>21</v>
       </c>
       <c r="AB24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC24" t="n">
         <v>9.199999999999999</v>
@@ -5172,7 +5172,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BC24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD24" t="n">
         <v>55</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="G25" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="H25" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>4.1</v>
@@ -5243,7 +5243,7 @@
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O25" t="n">
         <v>1.31</v>
@@ -5258,19 +5258,19 @@
         <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T25" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W25" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X25" t="n">
         <v>15</v>
@@ -5279,110 +5279,110 @@
         <v>21</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA25" t="n">
         <v>120</v>
       </c>
       <c r="AB25" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
         <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL25" t="n">
         <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AS25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU25" t="n">
         <v>8</v>
       </c>
       <c r="AV25" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB25" t="n">
         <v>17</v>
       </c>
-      <c r="BA25" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BC25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G26" t="n">
         <v>3.95</v>
       </c>
       <c r="H26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I26" t="n">
         <v>2.14</v>
@@ -5431,7 +5431,7 @@
         <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
@@ -5443,7 +5443,7 @@
         <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
         <v>1.78</v>
@@ -5452,7 +5452,7 @@
         <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
         <v>1.68</v>
@@ -5461,16 +5461,16 @@
         <v>2.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X26" t="n">
         <v>23</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z26" t="n">
         <v>16</v>
@@ -5485,7 +5485,7 @@
         <v>10</v>
       </c>
       <c r="AD26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE26" t="n">
         <v>24</v>
@@ -5515,7 +5515,7 @@
         <v>95</v>
       </c>
       <c r="AN26" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO26" t="n">
         <v>14.5</v>
@@ -5530,7 +5530,7 @@
         <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT26" t="n">
         <v>14.5</v>
@@ -5539,7 +5539,7 @@
         <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW26" t="n">
         <v>18</v>
@@ -5548,35 +5548,35 @@
         <v>24</v>
       </c>
       <c r="AY26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ26" t="n">
         <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG26" t="n">
         <v>10.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
         <v>1.62</v>
@@ -5619,10 +5619,10 @@
         <v>6.6</v>
       </c>
       <c r="J27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L27" t="n">
         <v>1.35</v>
@@ -5631,16 +5631,16 @@
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O27" t="n">
         <v>1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R27" t="n">
         <v>1.46</v>
@@ -5658,7 +5658,7 @@
         <v>1.18</v>
       </c>
       <c r="W27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X27" t="n">
         <v>18</v>
@@ -5670,13 +5670,13 @@
         <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
         <v>9.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
         <v>24</v>
@@ -5700,7 +5700,7 @@
         <v>15</v>
       </c>
       <c r="AK27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>34</v>
@@ -5715,7 +5715,7 @@
         <v>95</v>
       </c>
       <c r="AP27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ27" t="n">
         <v>21</v>
@@ -5736,7 +5736,7 @@
         <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>2.72</v>
       </c>
       <c r="G28" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H28" t="n">
         <v>2.74</v>
@@ -5813,7 +5813,7 @@
         <v>2.84</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
         <v>3.6</v>
@@ -5825,7 +5825,7 @@
         <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.3</v>
@@ -5852,7 +5852,7 @@
         <v>1.54</v>
       </c>
       <c r="W28" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X28" t="n">
         <v>16</v>
@@ -5909,10 +5909,10 @@
         <v>25</v>
       </c>
       <c r="AP28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR28" t="n">
         <v>17</v>
@@ -5921,7 +5921,7 @@
         <v>34</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU28" t="n">
         <v>7.4</v>
@@ -5948,7 +5948,7 @@
         <v>34</v>
       </c>
       <c r="BC28" t="n">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="BD28" t="n">
         <v>32</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6007,10 +6007,10 @@
         <v>3.8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L29" t="n">
         <v>1.44</v>
@@ -6094,7 +6094,7 @@
         <v>40</v>
       </c>
       <c r="AM29" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
         <v>18</v>
@@ -6112,10 +6112,10 @@
         <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU29" t="n">
         <v>7.4</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6195,16 +6195,16 @@
         <v>4.1</v>
       </c>
       <c r="H30" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I30" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="J30" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L30" t="n">
         <v>1.41</v>
@@ -6237,7 +6237,7 @@
         <v>2.08</v>
       </c>
       <c r="V30" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="W30" t="n">
         <v>1.32</v>
@@ -6246,7 +6246,7 @@
         <v>17</v>
       </c>
       <c r="Y30" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z30" t="n">
         <v>13.5</v>
@@ -6258,7 +6258,7 @@
         <v>14.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD30" t="n">
         <v>11</v>
@@ -6270,10 +6270,10 @@
         <v>30</v>
       </c>
       <c r="AG30" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI30" t="n">
         <v>40</v>
@@ -6330,19 +6330,19 @@
         <v>16</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB30" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD30" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF30" t="n">
         <v>38</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6389,16 +6389,16 @@
         <v>4.4</v>
       </c>
       <c r="H31" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I31" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J31" t="n">
         <v>2.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L31" t="n">
         <v>1.6</v>
@@ -6407,13 +6407,13 @@
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O31" t="n">
         <v>1.57</v>
       </c>
       <c r="P31" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q31" t="n">
         <v>2.74</v>
@@ -6428,7 +6428,7 @@
         <v>2.16</v>
       </c>
       <c r="U31" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V31" t="n">
         <v>1.68</v>
@@ -6452,7 +6452,7 @@
         <v>11</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD31" t="n">
         <v>13</v>
@@ -6464,10 +6464,10 @@
         <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
@@ -6482,28 +6482,28 @@
         <v>120</v>
       </c>
       <c r="AM31" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN31" t="n">
         <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR31" t="n">
         <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU31" t="n">
         <v>6.2</v>
@@ -6512,7 +6512,7 @@
         <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>18.5</v>
@@ -6521,32 +6521,32 @@
         <v>15.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BA31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG31" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC31" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>2.24</v>
       </c>
       <c r="G32" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H32" t="n">
         <v>3.9</v>
@@ -6598,16 +6598,16 @@
         <v>1.64</v>
       </c>
       <c r="M32" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N32" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P32" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q32" t="n">
         <v>2.88</v>
@@ -6628,7 +6628,7 @@
         <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X32" t="n">
         <v>9.199999999999999</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6801,10 +6801,10 @@
         <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R33" t="n">
         <v>1.38</v>
@@ -6816,7 +6816,7 @@
         <v>1.72</v>
       </c>
       <c r="U33" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V33" t="n">
         <v>1.68</v>
@@ -6852,7 +6852,7 @@
         <v>26</v>
       </c>
       <c r="AG33" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH33" t="n">
         <v>19.5</v>
@@ -6864,7 +6864,7 @@
         <v>60</v>
       </c>
       <c r="AK33" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AL33" t="n">
         <v>55</v>
@@ -6921,20 +6921,20 @@
         <v>5</v>
       </c>
       <c r="BD33" t="n">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BE33" t="n">
         <v>5.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="BG33" t="n">
         <v>14</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G34" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H34" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I34" t="n">
         <v>11</v>
       </c>
       <c r="J34" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K34" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
         <v>1.36</v>
@@ -6998,7 +6998,7 @@
         <v>2.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="R34" t="n">
         <v>1.39</v>
@@ -7010,34 +7010,34 @@
         <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V34" t="n">
         <v>1.1</v>
       </c>
       <c r="W34" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X34" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y34" t="n">
         <v>30</v>
       </c>
       <c r="Z34" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AA34" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AB34" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC34" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE34" t="n">
         <v>190</v>
@@ -7049,7 +7049,7 @@
         <v>11</v>
       </c>
       <c r="AH34" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI34" t="n">
         <v>160</v>
@@ -7064,7 +7064,7 @@
         <v>44</v>
       </c>
       <c r="AM34" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN34" t="n">
         <v>7.2</v>
@@ -7073,16 +7073,16 @@
         <v>290</v>
       </c>
       <c r="AP34" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ34" t="n">
         <v>23</v>
       </c>
       <c r="AR34" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT34" t="n">
         <v>7</v>
@@ -7091,10 +7091,10 @@
         <v>9.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AW34" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX34" t="n">
         <v>7</v>
@@ -7106,7 +7106,7 @@
         <v>23</v>
       </c>
       <c r="BA34" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB34" t="n">
         <v>10</v>
@@ -7115,20 +7115,20 @@
         <v>14</v>
       </c>
       <c r="BD34" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF34" t="n">
         <v>6</v>
       </c>
       <c r="BG34" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -7165,10 +7165,10 @@
         <v>3.8</v>
       </c>
       <c r="H35" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I35" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J35" t="n">
         <v>2.82</v>
@@ -7207,7 +7207,7 @@
         <v>1.62</v>
       </c>
       <c r="V35" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W35" t="n">
         <v>1.35</v>
@@ -7291,7 +7291,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AX35" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY35" t="n">
         <v>14.5</v>
@@ -7312,7 +7312,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF35" t="n">
         <v>9.199999999999999</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G2" t="n">
         <v>2.02</v>
@@ -790,7 +790,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
@@ -805,7 +805,7 @@
         <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.98</v>
@@ -901,7 +901,7 @@
         <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
         <v>15</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -951,64 +951,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="H3" t="n">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.76</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>1.24</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1017,104 +1017,104 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>980</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>1.91</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>1.31</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -1348,13 +1348,13 @@
         <v>1.95</v>
       </c>
       <c r="I5" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
@@ -1363,49 +1363,49 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="W5" t="n">
         <v>1.31</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
@@ -1414,95 +1414,95 @@
         <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI5" t="n">
         <v>34</v>
       </c>
-      <c r="AG5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>38</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK5" t="n">
         <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
         <v>44</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AP5" t="n">
         <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
         <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
         <v>30</v>
       </c>
       <c r="BG5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1581,10 +1581,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
         <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.9</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
         <v>1.74</v>
@@ -1972,7 +1972,7 @@
         <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -2038,7 +2038,7 @@
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
         <v>10.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2157,7 +2157,7 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
         <v>2.04</v>
@@ -2256,13 +2256,13 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB9" t="n">
         <v>14.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD9" t="n">
         <v>14</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>4.4</v>
       </c>
       <c r="G10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="I10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>3.9</v>
@@ -2333,7 +2333,7 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
@@ -2360,7 +2360,7 @@
         <v>2.08</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
         <v>15</v>
@@ -2393,13 +2393,13 @@
         <v>18</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AK10" t="n">
         <v>60</v>
@@ -2414,7 +2414,7 @@
         <v>65</v>
       </c>
       <c r="AO10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
         <v>13</v>
@@ -2453,16 +2453,16 @@
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD10" t="n">
         <v>14</v>
       </c>
       <c r="BE10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF10" t="n">
         <v>14</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>19</v>
       </c>
       <c r="Y11" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
         <v>27</v>
@@ -2620,7 +2620,7 @@
         <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
         <v>9.199999999999999</v>
@@ -2632,7 +2632,7 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX11" t="n">
         <v>12.5</v>
@@ -2641,22 +2641,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
         <v>19.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
         <v>14</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>4.1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I12" t="n">
         <v>2.22</v>
@@ -2712,7 +2712,7 @@
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.52</v>
@@ -2721,13 +2721,13 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
         <v>2.42</v>
@@ -2742,7 +2742,7 @@
         <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V12" t="n">
         <v>1.82</v>
@@ -2796,7 +2796,7 @@
         <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
         <v>80</v>
@@ -2841,16 +2841,16 @@
         <v>46</v>
       </c>
       <c r="BB12" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BC12" t="n">
         <v>50</v>
       </c>
       <c r="BD12" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF12" t="n">
         <v>34</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -2897,10 +2897,10 @@
         <v>3.45</v>
       </c>
       <c r="H13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I13" t="n">
         <v>2.56</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.58</v>
       </c>
       <c r="J13" t="n">
         <v>3.15</v>
@@ -2915,7 +2915,7 @@
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
         <v>1.49</v>
@@ -2924,7 +2924,7 @@
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.23</v>
@@ -2939,7 +2939,7 @@
         <v>1.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W13" t="n">
         <v>1.41</v>
@@ -2969,10 +2969,10 @@
         <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
@@ -3002,7 +3002,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR13" t="n">
         <v>13.5</v>
@@ -3023,7 +3023,7 @@
         <v>30</v>
       </c>
       <c r="AX13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
         <v>13.5</v>
@@ -3032,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BB13" t="n">
         <v>55</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
         <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>29</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -3288,34 +3288,34 @@
         <v>3.75</v>
       </c>
       <c r="I15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.85</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
@@ -3324,7 +3324,7 @@
         <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
@@ -3342,7 +3342,7 @@
         <v>28</v>
       </c>
       <c r="AA15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB15" t="n">
         <v>11</v>
@@ -3375,13 +3375,13 @@
         <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO15" t="n">
         <v>38</v>
@@ -3405,7 +3405,7 @@
         <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>36</v>
@@ -3420,13 +3420,13 @@
         <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB15" t="n">
         <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD15" t="n">
         <v>28</v>
@@ -3438,11 +3438,11 @@
         <v>12</v>
       </c>
       <c r="BG15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>1.3</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
         <v>14.5</v>
@@ -3497,22 +3497,22 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="Q16" t="n">
         <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="S16" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="T16" t="n">
         <v>1.97</v>
@@ -3593,10 +3593,10 @@
         <v>4.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.45</v>
+        <v>9.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AV16" t="n">
         <v>4.2</v>
@@ -3605,10 +3605,10 @@
         <v>4.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
         <v>4.1</v>
@@ -3617,10 +3617,10 @@
         <v>4.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
         <v>4.1</v>
@@ -3629,14 +3629,14 @@
         <v>4.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="BG16" t="n">
         <v>4.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
         <v>2.56</v>
       </c>
       <c r="H17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>3.45</v>
@@ -3682,10 +3682,10 @@
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3748,13 +3748,13 @@
         <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>34</v>
@@ -3781,7 +3781,7 @@
         <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="AS17" t="n">
         <v>42</v>
@@ -3796,10 +3796,10 @@
         <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY17" t="n">
         <v>9.199999999999999</v>
@@ -3808,29 +3808,29 @@
         <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>36</v>
+        <v>5.6</v>
       </c>
       <c r="BB17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF17" t="n">
         <v>5</v>
       </c>
-      <c r="BC17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>16</v>
-      </c>
       <c r="BG17" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
         <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I19" t="n">
         <v>2.82</v>
@@ -4103,10 +4103,10 @@
         <v>2.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X19" t="n">
         <v>20</v>
@@ -4169,13 +4169,13 @@
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
@@ -4199,7 +4199,7 @@
         <v>30</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC19" t="n">
         <v>6.6</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I20" t="n">
         <v>2.5</v>
@@ -4291,7 +4291,7 @@
         <v>3.95</v>
       </c>
       <c r="T20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
         <v>2.08</v>
@@ -4393,7 +4393,7 @@
         <v>38</v>
       </c>
       <c r="BB20" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BC20" t="n">
         <v>34</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>2.24</v>
       </c>
       <c r="G21" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.74</v>
@@ -4467,7 +4467,7 @@
         <v>1.18</v>
       </c>
       <c r="N21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.79</v>
@@ -4482,10 +4482,10 @@
         <v>1.12</v>
       </c>
       <c r="S21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U21" t="n">
         <v>1.55</v>
@@ -4527,7 +4527,7 @@
         <v>14.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AI21" t="n">
         <v>180</v>
@@ -4536,7 +4536,7 @@
         <v>980</v>
       </c>
       <c r="AK21" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AL21" t="n">
         <v>120</v>
@@ -4581,7 +4581,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>27</v>
+        <v>7.4</v>
       </c>
       <c r="BA21" t="n">
         <v>8.800000000000001</v>
@@ -4599,14 +4599,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="BG21" t="n">
         <v>9</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H22" t="n">
         <v>4.7</v>
@@ -4670,7 +4670,7 @@
         <v>1.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R22" t="n">
         <v>1.17</v>
@@ -4682,13 +4682,13 @@
         <v>2.26</v>
       </c>
       <c r="U22" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V22" t="n">
         <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X22" t="n">
         <v>9.6</v>
@@ -4730,7 +4730,7 @@
         <v>980</v>
       </c>
       <c r="AK22" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AL22" t="n">
         <v>70</v>
@@ -4751,13 +4751,13 @@
         <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS22" t="n">
         <v>10</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
@@ -4766,7 +4766,7 @@
         <v>16.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>9.6</v>
@@ -4775,22 +4775,22 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BA22" t="n">
         <v>10</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC22" t="n">
         <v>8</v>
       </c>
       <c r="BD22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF22" t="n">
         <v>21</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>1.25</v>
       </c>
       <c r="G23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I23" t="n">
         <v>17.5</v>
@@ -4915,7 +4915,7 @@
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI23" t="n">
         <v>310</v>
@@ -4966,7 +4966,7 @@
         <v>6.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
         <v>34</v>
@@ -4981,7 +4981,7 @@
         <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BE23" t="n">
         <v>18</v>
@@ -4990,11 +4990,11 @@
         <v>4.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I24" t="n">
         <v>1.9</v>
@@ -5067,7 +5067,7 @@
         <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U24" t="n">
         <v>2.1</v>
@@ -5094,7 +5094,7 @@
         <v>18</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
         <v>11</v>
@@ -5112,13 +5112,13 @@
         <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AJ24" t="n">
         <v>140</v>
       </c>
       <c r="AK24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL24" t="n">
         <v>70</v>
@@ -5127,7 +5127,7 @@
         <v>130</v>
       </c>
       <c r="AN24" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO24" t="n">
         <v>12.5</v>
@@ -5157,7 +5157,7 @@
         <v>16.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY24" t="n">
         <v>16.5</v>
@@ -5166,29 +5166,29 @@
         <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD24" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>55</v>
-      </c>
       <c r="BE24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF24" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>50</v>
       </c>
       <c r="BG24" t="n">
         <v>10</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G25" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="H25" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
         <v>4.1</v>
@@ -5261,16 +5261,16 @@
         <v>3.35</v>
       </c>
       <c r="T25" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U25" t="n">
         <v>2.06</v>
       </c>
       <c r="V25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="X25" t="n">
         <v>15</v>
@@ -5279,7 +5279,7 @@
         <v>21</v>
       </c>
       <c r="Z25" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA25" t="n">
         <v>120</v>
@@ -5291,10 +5291,10 @@
         <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF25" t="n">
         <v>11</v>
@@ -5303,25 +5303,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
         <v>19.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL25" t="n">
         <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
@@ -5336,7 +5336,7 @@
         <v>32</v>
       </c>
       <c r="AS25" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -5345,10 +5345,10 @@
         <v>8</v>
       </c>
       <c r="AV25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW25" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
         <v>9.800000000000001</v>
@@ -5357,10 +5357,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA25" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BB25" t="n">
         <v>17</v>
@@ -5369,20 +5369,20 @@
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF25" t="n">
         <v>10.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>3.65</v>
       </c>
       <c r="G26" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H26" t="n">
         <v>2.08</v>
@@ -5488,22 +5488,22 @@
         <v>11.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF26" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG26" t="n">
         <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
         <v>32</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK26" t="n">
         <v>55</v>
@@ -5521,7 +5521,7 @@
         <v>14.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>9.800000000000001</v>
@@ -5530,7 +5530,7 @@
         <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>14.5</v>
@@ -5545,7 +5545,7 @@
         <v>18</v>
       </c>
       <c r="AX26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
         <v>14</v>
@@ -5563,7 +5563,7 @@
         <v>6</v>
       </c>
       <c r="BD26" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="BE26" t="n">
         <v>6.4</v>
@@ -5572,11 +5572,11 @@
         <v>5.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H27" t="n">
         <v>6.2</v>
@@ -5622,7 +5622,7 @@
         <v>4.5</v>
       </c>
       <c r="K27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L27" t="n">
         <v>1.35</v>
@@ -5649,7 +5649,7 @@
         <v>3.05</v>
       </c>
       <c r="T27" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U27" t="n">
         <v>2.06</v>
@@ -5658,7 +5658,7 @@
         <v>1.18</v>
       </c>
       <c r="W27" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="X27" t="n">
         <v>18</v>
@@ -5670,10 +5670,10 @@
         <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC27" t="n">
         <v>10</v>
@@ -5715,13 +5715,13 @@
         <v>95</v>
       </c>
       <c r="AP27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS27" t="n">
         <v>44</v>
@@ -5736,10 +5736,10 @@
         <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY27" t="n">
         <v>9.4</v>
@@ -5748,7 +5748,7 @@
         <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5763,14 +5763,14 @@
         <v>90</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G29" t="n">
         <v>2.18</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2.2</v>
       </c>
       <c r="H29" t="n">
         <v>3.75</v>
@@ -6046,7 +6046,7 @@
         <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X29" t="n">
         <v>13</v>
@@ -6094,7 +6094,7 @@
         <v>40</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN29" t="n">
         <v>18</v>
@@ -6112,7 +6112,7 @@
         <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AT29" t="n">
         <v>8.6</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -6189,13 +6189,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G30" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H30" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="I30" t="n">
         <v>2.14</v>
@@ -6213,70 +6213,70 @@
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T30" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="U30" t="n">
         <v>2.08</v>
       </c>
       <c r="V30" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W30" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA30" t="n">
         <v>27</v>
       </c>
       <c r="AB30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD30" t="n">
         <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AF30" t="n">
         <v>30</v>
       </c>
       <c r="AG30" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AJ30" t="n">
         <v>1000</v>
@@ -6297,10 +6297,10 @@
         <v>17</v>
       </c>
       <c r="AP30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR30" t="n">
         <v>11</v>
@@ -6312,10 +6312,10 @@
         <v>12</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW30" t="n">
         <v>19.5</v>
@@ -6324,35 +6324,35 @@
         <v>22</v>
       </c>
       <c r="AY30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ30" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="BB30" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BD30" t="n">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BF30" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BG30" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>3.75</v>
       </c>
       <c r="G31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H31" t="n">
         <v>2.3</v>
@@ -6395,10 +6395,10 @@
         <v>2.46</v>
       </c>
       <c r="J31" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L31" t="n">
         <v>1.6</v>
@@ -6407,13 +6407,13 @@
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O31" t="n">
         <v>1.57</v>
       </c>
       <c r="P31" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q31" t="n">
         <v>2.74</v>
@@ -6428,7 +6428,7 @@
         <v>2.16</v>
       </c>
       <c r="U31" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V31" t="n">
         <v>1.68</v>
@@ -6473,13 +6473,13 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK31" t="n">
         <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM31" t="n">
         <v>240</v>
@@ -6491,7 +6491,7 @@
         <v>40</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ31" t="n">
         <v>6.2</v>
@@ -6500,7 +6500,7 @@
         <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT31" t="n">
         <v>9.199999999999999</v>
@@ -6512,7 +6512,7 @@
         <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX31" t="n">
         <v>18.5</v>
@@ -6524,29 +6524,29 @@
         <v>7.4</v>
       </c>
       <c r="BA31" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE31" t="n">
         <v>10</v>
       </c>
       <c r="BF31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -6586,82 +6586,82 @@
         <v>3.9</v>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K32" t="n">
         <v>3.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M32" t="n">
         <v>1.14</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O32" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P32" t="n">
         <v>1.47</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="R32" t="n">
         <v>1.16</v>
       </c>
       <c r="S32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T32" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U32" t="n">
         <v>1.68</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W32" t="n">
         <v>1.73</v>
       </c>
       <c r="X32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y32" t="n">
         <v>10.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA32" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG32" t="n">
         <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI32" t="n">
         <v>130</v>
@@ -6685,28 +6685,28 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ32" t="n">
         <v>9</v>
       </c>
       <c r="AR32" t="n">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="AS32" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="AW32" t="n">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -6715,32 +6715,32 @@
         <v>11</v>
       </c>
       <c r="AZ32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA32" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BB32" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BC32" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BD32" t="n">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="BE32" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BG32" t="n">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G33" t="n">
         <v>3.4</v>
@@ -6780,13 +6780,13 @@
         <v>2.34</v>
       </c>
       <c r="I33" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
         <v>1.39</v>
@@ -6795,34 +6795,34 @@
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
         <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
         <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U33" t="n">
         <v>2.22</v>
       </c>
       <c r="V33" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W33" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X33" t="n">
         <v>18</v>
@@ -6864,7 +6864,7 @@
         <v>60</v>
       </c>
       <c r="AK33" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AL33" t="n">
         <v>55</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -6968,19 +6968,19 @@
         <v>1.43</v>
       </c>
       <c r="G34" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H34" t="n">
         <v>9</v>
       </c>
       <c r="I34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J34" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K34" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L34" t="n">
         <v>1.36</v>
@@ -6992,37 +6992,37 @@
         <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P34" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R34" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T34" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U34" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V34" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W34" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X34" t="n">
         <v>19</v>
       </c>
       <c r="Y34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z34" t="n">
         <v>90</v>
@@ -7031,7 +7031,7 @@
         <v>420</v>
       </c>
       <c r="AB34" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC34" t="n">
         <v>11.5</v>
@@ -7043,7 +7043,7 @@
         <v>190</v>
       </c>
       <c r="AF34" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG34" t="n">
         <v>11</v>
@@ -7079,10 +7079,10 @@
         <v>23</v>
       </c>
       <c r="AR34" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT34" t="n">
         <v>7</v>
@@ -7091,13 +7091,13 @@
         <v>9.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW34" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX34" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY34" t="n">
         <v>9.199999999999999</v>
@@ -7106,7 +7106,7 @@
         <v>23</v>
       </c>
       <c r="BA34" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB34" t="n">
         <v>10</v>
@@ -7115,20 +7115,20 @@
         <v>14</v>
       </c>
       <c r="BD34" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE34" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF34" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="G35" t="n">
         <v>3.8</v>
       </c>
       <c r="H35" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I35" t="n">
         <v>2.72</v>
@@ -7174,7 +7174,7 @@
         <v>2.82</v>
       </c>
       <c r="K35" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L35" t="n">
         <v>1.68</v>
@@ -7204,7 +7204,7 @@
         <v>2.32</v>
       </c>
       <c r="U35" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V35" t="n">
         <v>1.58</v>
@@ -7225,7 +7225,7 @@
         <v>980</v>
       </c>
       <c r="AB35" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC35" t="n">
         <v>7.6</v>
@@ -7285,44 +7285,44 @@
         <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX35" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY35" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC35" t="n">
         <v>9</v>
       </c>
-      <c r="BB35" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC35" t="n">
+      <c r="BD35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG35" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BD35" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G36" t="n">
         <v>2.14</v>
@@ -7362,13 +7362,13 @@
         <v>3.8</v>
       </c>
       <c r="I36" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>3.6</v>
       </c>
       <c r="K36" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L36" t="n">
         <v>1.43</v>
@@ -7377,10 +7377,10 @@
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P36" t="n">
         <v>1.87</v>
@@ -7392,16 +7392,16 @@
         <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T36" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U36" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V36" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W36" t="n">
         <v>1.88</v>
@@ -7473,7 +7473,7 @@
         <v>10.5</v>
       </c>
       <c r="AT36" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU36" t="n">
         <v>7.4</v>
@@ -7482,7 +7482,7 @@
         <v>7</v>
       </c>
       <c r="AW36" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AX36" t="n">
         <v>11</v>
@@ -7503,7 +7503,7 @@
         <v>8</v>
       </c>
       <c r="BD36" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BE36" t="n">
         <v>11</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -760,16 +760,16 @@
         <v>1.81</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -790,13 +790,13 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
@@ -808,13 +808,13 @@
         <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="n">
         <v>980</v>
@@ -880,7 +880,7 @@
         <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
         <v>13.5</v>
@@ -892,7 +892,7 @@
         <v>9.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -951,67 +951,67 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="V3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="X3" t="n">
         <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1035,7 +1035,7 @@
         <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW3" t="n">
+      <c r="BC3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD3" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="G4" t="n">
         <v>3.6</v>
@@ -1157,7 +1157,7 @@
         <v>2.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="K4" t="n">
         <v>3.8</v>
@@ -1169,22 +1169,22 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
         <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="T4" t="n">
         <v>1.87</v>
@@ -1193,7 +1193,7 @@
         <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W4" t="n">
         <v>1.38</v>
@@ -1253,37 +1253,37 @@
         <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.95</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
         <v>4.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.65</v>
+        <v>9.6</v>
       </c>
       <c r="AW4" t="n">
         <v>4.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.85</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
         <v>4.6</v>
@@ -1304,11 +1304,11 @@
         <v>4.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>3.6</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I5" t="n">
         <v>2.1</v>
@@ -1363,7 +1363,7 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
@@ -1372,25 +1372,25 @@
         <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R5" t="n">
         <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
         <v>1.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
         <v>19</v>
@@ -1402,13 +1402,13 @@
         <v>14.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AB5" t="n">
         <v>17</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>12.5</v>
@@ -1417,7 +1417,7 @@
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
@@ -1429,49 +1429,49 @@
         <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="n">
         <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM5" t="n">
         <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO5" t="n">
         <v>13.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
         <v>20</v>
       </c>
       <c r="AT5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5" t="n">
         <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
@@ -1480,29 +1480,29 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC5" t="n">
         <v>32</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="BG5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
         <v>9.6</v>
@@ -1545,7 +1545,7 @@
         <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
         <v>6.8</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H7" t="n">
         <v>6.4</v>
       </c>
       <c r="I7" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>1.28</v>
@@ -1754,31 +1754,31 @@
         <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
         <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1838,13 +1838,13 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -1853,44 +1853,44 @@
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="BC7" t="n">
         <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H8" t="n">
         <v>2.82</v>
       </c>
       <c r="I8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.4</v>
@@ -1951,7 +1951,7 @@
         <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
@@ -1963,16 +1963,16 @@
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
         <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
         <v>48</v>
       </c>
       <c r="AO9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP9" t="n">
         <v>11</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G10" t="n">
         <v>4.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
@@ -2348,16 +2348,16 @@
         <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
         <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="W10" t="n">
         <v>1.27</v>
@@ -2375,13 +2375,13 @@
         <v>22</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC10" t="n">
         <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2390,7 +2390,7 @@
         <v>34</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
@@ -2405,28 +2405,28 @@
         <v>60</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>8</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
         <v>15</v>
@@ -2438,7 +2438,7 @@
         <v>9.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX10" t="n">
         <v>26</v>
@@ -2453,26 +2453,26 @@
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BE10" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
         <v>50</v>
       </c>
       <c r="BD12" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BE12" t="n">
         <v>44</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
         <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T13" t="n">
         <v>2.06</v>
@@ -2960,7 +2960,7 @@
         <v>10</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD13" t="n">
         <v>12</v>
@@ -3008,7 +3008,7 @@
         <v>13.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT13" t="n">
         <v>9.6</v>
@@ -3032,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB13" t="n">
         <v>55</v>
@@ -3047,14 +3047,14 @@
         <v>44</v>
       </c>
       <c r="BF13" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BG13" t="n">
         <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="n">
         <v>2.54</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
         <v>3.75</v>
@@ -3291,7 +3291,7 @@
         <v>3.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
         <v>3.85</v>
@@ -3318,19 +3318,19 @@
         <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
         <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X15" t="n">
         <v>16.5</v>
@@ -3378,13 +3378,13 @@
         <v>32</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
         <v>13.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP15" t="n">
         <v>15.5</v>
@@ -3438,11 +3438,11 @@
         <v>12</v>
       </c>
       <c r="BG15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -3473,64 +3473,64 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K16" t="n">
         <v>8.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="R16" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
         <v>4</v>
       </c>
       <c r="X16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,22 +3539,22 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
         <v>21</v>
       </c>
       <c r="AD16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
         <v>42</v>
@@ -3581,28 +3581,28 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV16" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AW16" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
@@ -3611,10 +3611,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB16" t="n">
         <v>8.6</v>
@@ -3623,20 +3623,20 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>2.56</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I17" t="n">
         <v>3.45</v>
@@ -3682,10 +3682,10 @@
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3694,13 +3694,13 @@
         <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P17" t="n">
         <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
         <v>1.37</v>
@@ -3775,13 +3775,13 @@
         <v>980</v>
       </c>
       <c r="AP17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS17" t="n">
         <v>42</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
         <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="G19" t="n">
         <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I19" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J19" t="n">
         <v>3.4</v>
@@ -4073,13 +4073,13 @@
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
         <v>1.27</v>
@@ -4097,13 +4097,13 @@
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
         <v>2.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W19" t="n">
         <v>1.48</v>
@@ -4163,7 +4163,7 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
         <v>10</v>
@@ -4175,7 +4175,7 @@
         <v>7</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
@@ -4184,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX19" t="n">
         <v>6</v>
@@ -4193,7 +4193,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA19" t="n">
         <v>30</v>
@@ -4208,7 +4208,7 @@
         <v>7</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF19" t="n">
         <v>17.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -4252,10 +4252,10 @@
         <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H20" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I20" t="n">
         <v>2.5</v>
@@ -4279,10 +4279,10 @@
         <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R20" t="n">
         <v>1.31</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.24</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H21" t="n">
         <v>4.2</v>
@@ -4485,7 +4485,7 @@
         <v>7.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="U21" t="n">
         <v>1.55</v>
@@ -4494,7 +4494,7 @@
         <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X21" t="n">
         <v>6.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="G22" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.61</v>
@@ -4661,7 +4661,7 @@
         <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
         <v>1.57</v>
@@ -4685,19 +4685,19 @@
         <v>1.69</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X22" t="n">
         <v>9.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AA22" t="n">
         <v>180</v>
@@ -4730,7 +4730,7 @@
         <v>980</v>
       </c>
       <c r="AK22" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AL22" t="n">
         <v>70</v>
@@ -4751,10 +4751,10 @@
         <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="AS22" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT22" t="n">
         <v>5.7</v>
@@ -4766,10 +4766,10 @@
         <v>16.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
@@ -4778,29 +4778,29 @@
         <v>23</v>
       </c>
       <c r="BA22" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="BC22" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF22" t="n">
         <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>1.27</v>
       </c>
       <c r="H23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
         <v>17.5</v>
@@ -4855,22 +4855,22 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R23" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
         <v>2.38</v>
@@ -4900,43 +4900,43 @@
         <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD23" t="n">
         <v>60</v>
       </c>
       <c r="AE23" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AF23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AI23" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK23" t="n">
         <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM23" t="n">
         <v>270</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AO23" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AP23" t="n">
         <v>22</v>
@@ -4945,34 +4945,34 @@
         <v>36</v>
       </c>
       <c r="AR23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AS23" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU23" t="n">
         <v>13.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AW23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ23" t="n">
         <v>34</v>
       </c>
       <c r="BA23" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BB23" t="n">
         <v>8.199999999999999</v>
@@ -4981,20 +4981,20 @@
         <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BE23" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BF23" t="n">
         <v>4.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>16</v>
+        <v>5.1</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>4.7</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
         <v>3.95</v>
@@ -5055,7 +5055,7 @@
         <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
         <v>1.95</v>
@@ -5073,49 +5073,49 @@
         <v>2.1</v>
       </c>
       <c r="V24" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB24" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AG24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AJ24" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AK24" t="n">
         <v>65</v>
@@ -5124,71 +5124,71 @@
         <v>70</v>
       </c>
       <c r="AM24" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="n">
         <v>70</v>
       </c>
       <c r="AO24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP24" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR24" t="n">
         <v>10</v>
       </c>
       <c r="AS24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW24" t="n">
         <v>17</v>
       </c>
-      <c r="AT24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AX24" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AY24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BC24" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G25" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H25" t="n">
         <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J25" t="n">
         <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
         <v>1.39</v>
@@ -5270,7 +5270,7 @@
         <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X25" t="n">
         <v>15</v>
@@ -5336,7 +5336,7 @@
         <v>32</v>
       </c>
       <c r="AS25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -5348,7 +5348,7 @@
         <v>17</v>
       </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX25" t="n">
         <v>9.800000000000001</v>
@@ -5357,7 +5357,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA25" t="n">
         <v>15</v>
@@ -5372,17 +5372,17 @@
         <v>12.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BF25" t="n">
         <v>10.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G26" t="n">
         <v>3.9</v>
       </c>
       <c r="H26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I26" t="n">
         <v>2.14</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K26" t="n">
         <v>3.9</v>
@@ -5449,7 +5449,7 @@
         <v>1.78</v>
       </c>
       <c r="R26" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
         <v>2.9</v>
@@ -5473,16 +5473,16 @@
         <v>11.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD26" t="n">
         <v>11.5</v>
@@ -5515,7 +5515,7 @@
         <v>95</v>
       </c>
       <c r="AN26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
         <v>14.5</v>
@@ -5530,7 +5530,7 @@
         <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AT26" t="n">
         <v>14.5</v>
@@ -5554,29 +5554,29 @@
         <v>14.5</v>
       </c>
       <c r="BA26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC26" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>6</v>
-      </c>
       <c r="BD26" t="n">
-        <v>38</v>
+        <v>5.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G27" t="n">
         <v>1.61</v>
@@ -5622,7 +5622,7 @@
         <v>4.5</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L27" t="n">
         <v>1.35</v>
@@ -5649,16 +5649,16 @@
         <v>3.05</v>
       </c>
       <c r="T27" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U27" t="n">
         <v>2.06</v>
       </c>
       <c r="V27" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W27" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="X27" t="n">
         <v>18</v>
@@ -5673,7 +5673,7 @@
         <v>180</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC27" t="n">
         <v>10</v>
@@ -5721,7 +5721,7 @@
         <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS27" t="n">
         <v>44</v>
@@ -5748,7 +5748,7 @@
         <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5757,20 +5757,20 @@
         <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE27" t="n">
         <v>90</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG27" t="n">
         <v>80</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
         <v>13</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
         <v>12.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G29" t="n">
         <v>2.18</v>
@@ -6007,10 +6007,10 @@
         <v>3.8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
         <v>1.44</v>
@@ -6019,28 +6019,28 @@
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>1.35</v>
       </c>
       <c r="P29" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q29" t="n">
         <v>2.08</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T29" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U29" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V29" t="n">
         <v>1.35</v>
@@ -6061,7 +6061,7 @@
         <v>75</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC29" t="n">
         <v>7.8</v>
@@ -6070,7 +6070,7 @@
         <v>15.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF29" t="n">
         <v>13</v>
@@ -6079,7 +6079,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI29" t="n">
         <v>60</v>
@@ -6088,7 +6088,7 @@
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
         <v>40</v>
@@ -6097,7 +6097,7 @@
         <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO29" t="n">
         <v>50</v>
@@ -6112,7 +6112,7 @@
         <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AT29" t="n">
         <v>8.6</v>
@@ -6133,10 +6133,10 @@
         <v>10</v>
       </c>
       <c r="AZ29" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BB29" t="n">
         <v>25</v>
@@ -6145,20 +6145,20 @@
         <v>21</v>
       </c>
       <c r="BD29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF29" t="n">
         <v>16.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -6198,13 +6198,13 @@
         <v>2.08</v>
       </c>
       <c r="I30" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.41</v>
@@ -6222,7 +6222,7 @@
         <v>1.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R30" t="n">
         <v>1.34</v>
@@ -6231,13 +6231,13 @@
         <v>3.65</v>
       </c>
       <c r="T30" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U30" t="n">
         <v>2.08</v>
       </c>
       <c r="V30" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W30" t="n">
         <v>1.34</v>
@@ -6258,7 +6258,7 @@
         <v>14</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
         <v>11</v>
@@ -6270,7 +6270,7 @@
         <v>30</v>
       </c>
       <c r="AG30" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AH30" t="n">
         <v>19.5</v>
@@ -6297,7 +6297,7 @@
         <v>17</v>
       </c>
       <c r="AP30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>8.4</v>
@@ -6327,7 +6327,7 @@
         <v>13</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA30" t="n">
         <v>30</v>
@@ -6339,7 +6339,7 @@
         <v>26</v>
       </c>
       <c r="BD30" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BE30" t="n">
         <v>40</v>
@@ -6348,11 +6348,11 @@
         <v>27</v>
       </c>
       <c r="BG30" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
         <v>1.68</v>
       </c>
       <c r="W31" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X31" t="n">
         <v>8.199999999999999</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G32" t="n">
         <v>2.36</v>
@@ -6586,7 +6586,7 @@
         <v>3.9</v>
       </c>
       <c r="I32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.05</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G33" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H33" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I33" t="n">
         <v>2.44</v>
@@ -6786,7 +6786,7 @@
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
         <v>1.39</v>
@@ -6804,7 +6804,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
@@ -6816,7 +6816,7 @@
         <v>1.73</v>
       </c>
       <c r="U33" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V33" t="n">
         <v>1.69</v>
@@ -6840,7 +6840,7 @@
         <v>15.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD33" t="n">
         <v>13.5</v>
@@ -6858,22 +6858,22 @@
         <v>19.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AJ33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK33" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AL33" t="n">
         <v>55</v>
       </c>
       <c r="AM33" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN33" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AO33" t="n">
         <v>21</v>
@@ -6882,13 +6882,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS33" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="AT33" t="n">
         <v>11.5</v>
@@ -6900,7 +6900,7 @@
         <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.8</v>
+        <v>19.5</v>
       </c>
       <c r="AX33" t="n">
         <v>18.5</v>
@@ -6909,32 +6909,32 @@
         <v>12</v>
       </c>
       <c r="AZ33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC33" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC33" t="n">
-        <v>5</v>
-      </c>
       <c r="BD33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF33" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>5</v>
       </c>
       <c r="BG33" t="n">
         <v>14</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G34" t="n">
         <v>1.46</v>
       </c>
       <c r="H34" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I34" t="n">
         <v>10.5</v>
@@ -6995,10 +6995,10 @@
         <v>1.29</v>
       </c>
       <c r="P34" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R34" t="n">
         <v>1.41</v>
@@ -7007,22 +7007,22 @@
         <v>3.15</v>
       </c>
       <c r="T34" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V34" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X34" t="n">
         <v>19</v>
       </c>
       <c r="Y34" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z34" t="n">
         <v>90</v>
@@ -7037,16 +7037,16 @@
         <v>11.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AE34" t="n">
         <v>190</v>
       </c>
       <c r="AF34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH34" t="n">
         <v>29</v>
@@ -7061,7 +7061,7 @@
         <v>17</v>
       </c>
       <c r="AL34" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AM34" t="n">
         <v>190</v>
@@ -7070,28 +7070,28 @@
         <v>7.2</v>
       </c>
       <c r="AO34" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AP34" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS34" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU34" t="n">
         <v>9.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW34" t="n">
         <v>10</v>
@@ -7100,7 +7100,7 @@
         <v>7.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ34" t="n">
         <v>23</v>
@@ -7115,7 +7115,7 @@
         <v>14</v>
       </c>
       <c r="BD34" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE34" t="n">
         <v>10</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -7162,13 +7162,13 @@
         <v>3.35</v>
       </c>
       <c r="G35" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H35" t="n">
         <v>2.52</v>
       </c>
       <c r="I35" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J35" t="n">
         <v>2.82</v>
@@ -7183,7 +7183,7 @@
         <v>1.16</v>
       </c>
       <c r="N35" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O35" t="n">
         <v>1.7</v>
@@ -7198,19 +7198,19 @@
         <v>1.13</v>
       </c>
       <c r="S35" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="T35" t="n">
         <v>2.32</v>
       </c>
       <c r="U35" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V35" t="n">
         <v>1.58</v>
       </c>
       <c r="W35" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X35" t="n">
         <v>7.4</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G36" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H36" t="n">
         <v>3.8</v>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J36" t="n">
         <v>3.6</v>
@@ -7383,19 +7383,19 @@
         <v>1.35</v>
       </c>
       <c r="P36" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S36" t="n">
         <v>3.7</v>
       </c>
       <c r="T36" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U36" t="n">
         <v>2.06</v>
@@ -7404,7 +7404,7 @@
         <v>1.32</v>
       </c>
       <c r="W36" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X36" t="n">
         <v>16</v>
@@ -7467,10 +7467,10 @@
         <v>12</v>
       </c>
       <c r="AR36" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT36" t="n">
         <v>8</v>
@@ -7479,10 +7479,10 @@
         <v>7.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX36" t="n">
         <v>11</v>
@@ -7491,19 +7491,19 @@
         <v>9.4</v>
       </c>
       <c r="AZ36" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA36" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="BB36" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BC36" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD36" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE36" t="n">
         <v>11</v>
@@ -7512,11 +7512,11 @@
         <v>7.2</v>
       </c>
       <c r="BG36" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.33</v>
@@ -784,43 +784,43 @@
         <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
         <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
         <v>980</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
         <v>11.5</v>
@@ -847,7 +847,7 @@
         <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
         <v>980</v>
@@ -862,43 +862,43 @@
         <v>14</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="AV2" t="n">
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
         <v>6.8</v>
@@ -907,10 +907,10 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
         <v>9.199999999999999</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
         <v>9.800000000000001</v>
@@ -1274,7 +1274,7 @@
         <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
         <v>18</v>
@@ -1283,32 +1283,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF4" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
         <v>18</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>1.77</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
         <v>2.98</v>
@@ -1384,7 +1384,7 @@
         <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
         <v>1.9</v>
@@ -1462,7 +1462,7 @@
         <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
         <v>9.199999999999999</v>
@@ -1471,7 +1471,7 @@
         <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
@@ -1480,7 +1480,7 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
         <v>7.2</v>
@@ -1489,7 +1489,7 @@
         <v>32</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
         <v>7.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
         <v>9.6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.49</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H7" t="n">
         <v>6.4</v>
@@ -1742,7 +1742,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.28</v>
@@ -1757,22 +1757,22 @@
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.9</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.89</v>
       </c>
       <c r="V7" t="n">
         <v>1.11</v>
@@ -1817,7 +1817,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK7" t="n">
         <v>1000</v>
@@ -1835,7 +1835,7 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>4</v>
@@ -1850,19 +1850,19 @@
         <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.1</v>
+        <v>19.5</v>
       </c>
       <c r="AW7" t="n">
         <v>4.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
@@ -1871,7 +1871,7 @@
         <v>4.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BC7" t="n">
         <v>11.5</v>
@@ -1883,14 +1883,14 @@
         <v>4.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
         <v>4.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="I8" t="n">
         <v>2.86</v>
@@ -1945,7 +1945,7 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
         <v>1.32</v>
@@ -1963,16 +1963,16 @@
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
         <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -2023,7 +2023,7 @@
         <v>90</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>26</v>
@@ -2044,7 +2044,7 @@
         <v>10.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
         <v>11.5</v>
@@ -2080,11 +2080,11 @@
         <v>22</v>
       </c>
       <c r="BG8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -2124,13 +2124,13 @@
         <v>2.36</v>
       </c>
       <c r="I9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>1.45</v>
@@ -2169,7 +2169,7 @@
         <v>1.4</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y9" t="n">
         <v>9.199999999999999</v>
@@ -2217,7 +2217,7 @@
         <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO9" t="n">
         <v>24</v>
@@ -2250,35 +2250,35 @@
         <v>21</v>
       </c>
       <c r="AY9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
         <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
         <v>32</v>
       </c>
       <c r="BD9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF9" t="n">
         <v>14</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>13</v>
       </c>
       <c r="BG9" t="n">
         <v>20</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H10" t="n">
         <v>1.86</v>
@@ -2324,58 +2324,58 @@
         <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
         <v>1.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
         <v>2.14</v>
       </c>
       <c r="W10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z10" t="n">
         <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC10" t="n">
         <v>8.6</v>
@@ -2387,22 +2387,22 @@
         <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
         <v>110</v>
       </c>
       <c r="AK10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
         <v>70</v>
@@ -2411,7 +2411,7 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="n">
         <v>13</v>
@@ -2426,25 +2426,25 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT10" t="n">
         <v>15</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>17.5</v>
@@ -2453,26 +2453,26 @@
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
         <v>13</v>
       </c>
       <c r="BE10" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
         <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.55</v>
       </c>
-      <c r="I11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.39</v>
@@ -2545,16 +2545,16 @@
         <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
         <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X11" t="n">
         <v>19</v>
@@ -2596,7 +2596,7 @@
         <v>980</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
         <v>980</v>
@@ -2632,7 +2632,7 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AX11" t="n">
         <v>12.5</v>
@@ -2644,16 +2644,16 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC11" t="n">
         <v>19.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE11" t="n">
         <v>8.199999999999999</v>
@@ -2662,11 +2662,11 @@
         <v>14</v>
       </c>
       <c r="BG11" t="n">
-        <v>26</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="G12" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
         <v>1.52</v>
@@ -2745,25 +2745,25 @@
         <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC12" t="n">
         <v>7.4</v>
@@ -2778,7 +2778,7 @@
         <v>27</v>
       </c>
       <c r="AG12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH12" t="n">
         <v>22</v>
@@ -2802,10 +2802,10 @@
         <v>80</v>
       </c>
       <c r="AO12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
         <v>7.2</v>
@@ -2814,7 +2814,7 @@
         <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT12" t="n">
         <v>11</v>
@@ -2826,13 +2826,13 @@
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AZ12" t="n">
         <v>20</v>
@@ -2841,16 +2841,16 @@
         <v>46</v>
       </c>
       <c r="BB12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC12" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BD12" t="n">
         <v>34</v>
       </c>
       <c r="BE12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF12" t="n">
         <v>34</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
         <v>3.45</v>
@@ -2900,7 +2900,7 @@
         <v>2.52</v>
       </c>
       <c r="I13" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J13" t="n">
         <v>3.15</v>
@@ -2918,7 +2918,7 @@
         <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
@@ -2930,7 +2930,7 @@
         <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
         <v>2.06</v>
@@ -2942,7 +2942,7 @@
         <v>1.64</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
         <v>9.199999999999999</v>
@@ -2954,7 +2954,7 @@
         <v>14.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB13" t="n">
         <v>10</v>
@@ -2966,7 +2966,7 @@
         <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF13" t="n">
         <v>21</v>
@@ -2978,13 +2978,13 @@
         <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
         <v>65</v>
       </c>
       <c r="AK13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL13" t="n">
         <v>70</v>
@@ -2999,19 +2999,19 @@
         <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR13" t="n">
         <v>13.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU13" t="n">
         <v>6.6</v>
@@ -3023,16 +3023,16 @@
         <v>30</v>
       </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY13" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB13" t="n">
         <v>55</v>
@@ -3044,17 +3044,17 @@
         <v>55</v>
       </c>
       <c r="BE13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BF13" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BG13" t="n">
         <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
         <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I14" t="n">
         <v>2.54</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.58</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
@@ -3109,43 +3109,43 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.36</v>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
         <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
         <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
         <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA14" t="n">
         <v>38</v>
@@ -3154,7 +3154,7 @@
         <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
         <v>12</v>
@@ -3214,10 +3214,10 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY14" t="n">
         <v>12.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G15" t="n">
         <v>2.1</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.14</v>
-      </c>
       <c r="H15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.75</v>
       </c>
       <c r="K15" t="n">
         <v>3.85</v>
@@ -3303,7 +3303,7 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
@@ -3312,28 +3312,28 @@
         <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
         <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
         <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X15" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Y15" t="n">
         <v>16.5</v>
@@ -3342,7 +3342,7 @@
         <v>28</v>
       </c>
       <c r="AA15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB15" t="n">
         <v>11</v>
@@ -3363,7 +3363,7 @@
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
         <v>48</v>
@@ -3384,7 +3384,7 @@
         <v>13.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AP15" t="n">
         <v>15.5</v>
@@ -3402,7 +3402,7 @@
         <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
         <v>14</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="G16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I16" t="n">
         <v>13.5</v>
       </c>
       <c r="J16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K16" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.22</v>
@@ -3497,40 +3497,40 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R16" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="U16" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
         <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="X16" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y16" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,37 +3539,37 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG16" t="n">
         <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AK16" t="n">
         <v>16.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3581,40 +3581,40 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AT16" t="n">
         <v>9</v>
       </c>
       <c r="AU16" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
         <v>8.6</v>
@@ -3623,20 +3623,20 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
         <v>2.98</v>
@@ -3682,10 +3682,10 @@
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3718,7 +3718,7 @@
         <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X17" t="n">
         <v>16.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -3867,19 +3867,19 @@
         <v>3.45</v>
       </c>
       <c r="H18" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I18" t="n">
         <v>2.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
         <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -3909,7 +3909,7 @@
         <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W18" t="n">
         <v>1.41</v>
@@ -3981,7 +3981,7 @@
         <v>7.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
         <v>6.4</v>
@@ -3990,7 +3990,7 @@
         <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX18" t="n">
         <v>18.5</v>
@@ -3999,7 +3999,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
         <v>8</v>
@@ -4011,20 +4011,20 @@
         <v>32</v>
       </c>
       <c r="BD18" t="n">
-        <v>44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BG18" t="n">
         <v>20</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H19" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="I19" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="J19" t="n">
         <v>3.4</v>
@@ -4073,25 +4073,25 @@
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
         <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -4103,10 +4103,10 @@
         <v>2.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W19" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X19" t="n">
         <v>20</v>
@@ -4160,22 +4160,22 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AQ19" t="n">
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="AT19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
@@ -4184,22 +4184,22 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BA19" t="n">
         <v>30</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC19" t="n">
         <v>6.6</v>
@@ -4208,17 +4208,17 @@
         <v>7</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>2.46</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J20" t="n">
         <v>3.45</v>
@@ -4276,7 +4276,7 @@
         <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P20" t="n">
         <v>1.83</v>
@@ -4288,16 +4288,16 @@
         <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U20" t="n">
         <v>2.08</v>
       </c>
       <c r="V20" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
         <v>1.44</v>
@@ -4312,7 +4312,7 @@
         <v>15.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB20" t="n">
         <v>11.5</v>
@@ -4408,11 +4408,11 @@
         <v>34</v>
       </c>
       <c r="BG20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G21" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>2.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="L21" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
         <v>1.18</v>
@@ -4476,13 +4476,13 @@
         <v>1.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
         <v>1.12</v>
       </c>
       <c r="S21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="T21" t="n">
         <v>2.56</v>
@@ -4491,10 +4491,10 @@
         <v>1.55</v>
       </c>
       <c r="V21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X21" t="n">
         <v>6.6</v>
@@ -4509,7 +4509,7 @@
         <v>160</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC21" t="n">
         <v>7.6</v>
@@ -4521,7 +4521,7 @@
         <v>120</v>
       </c>
       <c r="AF21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG21" t="n">
         <v>14.5</v>
@@ -4533,10 +4533,10 @@
         <v>180</v>
       </c>
       <c r="AJ21" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AK21" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AL21" t="n">
         <v>120</v>
@@ -4560,7 +4560,7 @@
         <v>19.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT21" t="n">
         <v>5.2</v>
@@ -4572,7 +4572,7 @@
         <v>18.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -4581,32 +4581,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF21" t="n">
         <v>8.6</v>
       </c>
-      <c r="BE21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>8</v>
-      </c>
       <c r="BG21" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G22" t="n">
         <v>2.1</v>
@@ -4652,7 +4652,7 @@
         <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L22" t="n">
         <v>1.61</v>
@@ -4718,7 +4718,7 @@
         <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>11.5</v>
+        <v>980</v>
       </c>
       <c r="AH22" t="n">
         <v>980</v>
@@ -4754,7 +4754,7 @@
         <v>30</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT22" t="n">
         <v>5.7</v>
@@ -4766,7 +4766,7 @@
         <v>16.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX22" t="n">
         <v>9.4</v>
@@ -4775,32 +4775,32 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF22" t="n">
         <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="G23" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.3</v>
@@ -4855,13 +4855,13 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P23" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q23" t="n">
         <v>1.64</v>
@@ -4882,7 +4882,7 @@
         <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="X23" t="n">
         <v>23</v>
@@ -4891,25 +4891,25 @@
         <v>46</v>
       </c>
       <c r="Z23" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AA23" t="n">
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AE23" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AF23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AG23" t="n">
         <v>12</v>
@@ -4918,7 +4918,7 @@
         <v>44</v>
       </c>
       <c r="AI23" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AJ23" t="n">
         <v>8.800000000000001</v>
@@ -4927,13 +4927,13 @@
         <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AO23" t="n">
         <v>480</v>
@@ -4945,10 +4945,10 @@
         <v>36</v>
       </c>
       <c r="AR23" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AT23" t="n">
         <v>8.6</v>
@@ -4957,10 +4957,10 @@
         <v>13.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AW23" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
         <v>6.6</v>
@@ -4972,7 +4972,7 @@
         <v>34</v>
       </c>
       <c r="BA23" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BB23" t="n">
         <v>8.199999999999999</v>
@@ -4981,20 +4981,20 @@
         <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BE23" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
         <v>3.9</v>
       </c>
       <c r="K24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
         <v>1.39</v>
@@ -5049,7 +5049,7 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
         <v>1.31</v>
@@ -5061,7 +5061,7 @@
         <v>1.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
         <v>3.3</v>
@@ -5073,7 +5073,7 @@
         <v>2.1</v>
       </c>
       <c r="V24" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
@@ -5163,13 +5163,13 @@
         <v>17</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC24" t="n">
         <v>12.5</v>
@@ -5178,17 +5178,17 @@
         <v>12.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG24" t="n">
         <v>10.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -5219,25 +5219,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="G25" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.95</v>
       </c>
-      <c r="K25" t="n">
-        <v>4</v>
-      </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
@@ -5246,10 +5246,10 @@
         <v>3.9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q25" t="n">
         <v>1.96</v>
@@ -5258,46 +5258,46 @@
         <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V25" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W25" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="X25" t="n">
         <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA25" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC25" t="n">
         <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG25" t="n">
         <v>9.800000000000001</v>
@@ -5309,10 +5309,10 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AK25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="n">
         <v>36</v>
@@ -5321,68 +5321,68 @@
         <v>110</v>
       </c>
       <c r="AN25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF25" t="n">
         <v>12</v>
       </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
         <v>4.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P26" t="n">
         <v>2.18</v>
@@ -5473,22 +5473,22 @@
         <v>11.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD26" t="n">
         <v>11.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF26" t="n">
         <v>36</v>
@@ -5515,7 +5515,7 @@
         <v>95</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO26" t="n">
         <v>14.5</v>
@@ -5530,7 +5530,7 @@
         <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>14.5</v>
@@ -5554,29 +5554,29 @@
         <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.2</v>
+        <v>27</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.5</v>
+        <v>38</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BG26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.59</v>
       </c>
       <c r="G27" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H27" t="n">
         <v>6.2</v>
@@ -5655,10 +5655,10 @@
         <v>2.06</v>
       </c>
       <c r="V27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W27" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X27" t="n">
         <v>18</v>
@@ -5715,7 +5715,7 @@
         <v>95</v>
       </c>
       <c r="AP27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ27" t="n">
         <v>21</v>
@@ -5736,13 +5736,13 @@
         <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AX27" t="n">
         <v>9</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
         <v>20</v>
@@ -5760,17 +5760,17 @@
         <v>29</v>
       </c>
       <c r="BE27" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G28" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H28" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I28" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="J28" t="n">
         <v>3.55</v>
@@ -5840,7 +5840,7 @@
         <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T28" t="n">
         <v>1.72</v>
@@ -5849,10 +5849,10 @@
         <v>2.26</v>
       </c>
       <c r="V28" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W28" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X28" t="n">
         <v>16</v>
@@ -5867,7 +5867,7 @@
         <v>44</v>
       </c>
       <c r="AB28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC28" t="n">
         <v>8</v>
@@ -5879,7 +5879,7 @@
         <v>32</v>
       </c>
       <c r="AF28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG28" t="n">
         <v>12.5</v>
@@ -5912,7 +5912,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>17</v>
@@ -5954,7 +5954,7 @@
         <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF28" t="n">
         <v>19</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -6001,16 +6001,16 @@
         <v>2.18</v>
       </c>
       <c r="H29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K29" t="n">
         <v>3.65</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.7</v>
       </c>
       <c r="L29" t="n">
         <v>1.44</v>
@@ -6028,22 +6028,22 @@
         <v>1.88</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R29" t="n">
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T29" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U29" t="n">
         <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W29" t="n">
         <v>1.84</v>
@@ -6061,7 +6061,7 @@
         <v>75</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC29" t="n">
         <v>7.8</v>
@@ -6079,7 +6079,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI29" t="n">
         <v>60</v>
@@ -6112,7 +6112,7 @@
         <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT29" t="n">
         <v>8.6</v>
@@ -6136,7 +6136,7 @@
         <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB29" t="n">
         <v>25</v>
@@ -6145,7 +6145,7 @@
         <v>21</v>
       </c>
       <c r="BD29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE29" t="n">
         <v>40</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
         <v>20</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G31" t="n">
         <v>4.3</v>
       </c>
       <c r="H31" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I31" t="n">
         <v>2.46</v>
@@ -6398,7 +6398,7 @@
         <v>2.9</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
         <v>1.6</v>
@@ -6407,13 +6407,13 @@
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O31" t="n">
         <v>1.57</v>
       </c>
       <c r="P31" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q31" t="n">
         <v>2.74</v>
@@ -6488,7 +6488,7 @@
         <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
         <v>7.2</v>
@@ -6521,7 +6521,7 @@
         <v>15.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
         <v>9.4</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
         <v>1.32</v>
       </c>
       <c r="W32" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X32" t="n">
         <v>8.4</v>
@@ -6715,7 +6715,7 @@
         <v>11</v>
       </c>
       <c r="AZ32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA32" t="n">
         <v>40</v>
@@ -6724,10 +6724,10 @@
         <v>20</v>
       </c>
       <c r="BC32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD32" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE32" t="n">
         <v>12.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G33" t="n">
         <v>3.35</v>
@@ -6795,16 +6795,16 @@
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O33" t="n">
         <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
@@ -6816,34 +6816,34 @@
         <v>1.73</v>
       </c>
       <c r="U33" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V33" t="n">
         <v>1.69</v>
       </c>
       <c r="W33" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X33" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA33" t="n">
         <v>36</v>
       </c>
       <c r="AB33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE33" t="n">
         <v>28</v>
@@ -6852,10 +6852,10 @@
         <v>26</v>
       </c>
       <c r="AG33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI33" t="n">
         <v>980</v>
@@ -6879,10 +6879,10 @@
         <v>21</v>
       </c>
       <c r="AP33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR33" t="n">
         <v>14</v>
@@ -6891,13 +6891,13 @@
         <v>27</v>
       </c>
       <c r="AT33" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU33" t="n">
         <v>7.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW33" t="n">
         <v>19.5</v>
@@ -6912,29 +6912,29 @@
         <v>14.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.3</v>
+        <v>30</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.6</v>
+        <v>28</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.3</v>
+        <v>22</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.6</v>
+        <v>26</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="BG33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
         <v>1.1</v>
       </c>
       <c r="W34" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X34" t="n">
         <v>19</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
         <v>6.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U35" t="n">
         <v>1.64</v>
@@ -7306,7 +7306,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC35" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="BD35" t="n">
         <v>9.4</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -7359,13 +7359,13 @@
         <v>2.12</v>
       </c>
       <c r="H36" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I36" t="n">
         <v>4.1</v>
       </c>
       <c r="J36" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K36" t="n">
         <v>3.85</v>
@@ -7422,7 +7422,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD36" t="n">
         <v>980</v>
@@ -7494,7 +7494,7 @@
         <v>7.8</v>
       </c>
       <c r="BA36" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="BB36" t="n">
         <v>20</v>
@@ -7503,10 +7503,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BD36" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF36" t="n">
         <v>7.2</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -763,16 +763,16 @@
         <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>1.33</v>
@@ -781,19 +781,19 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
         <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
         <v>3.1</v>
@@ -805,10 +805,10 @@
         <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
@@ -826,7 +826,7 @@
         <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
         <v>980</v>
@@ -865,16 +865,16 @@
         <v>65</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
         <v>3.85</v>
@@ -886,7 +886,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
         <v>6.8</v>
@@ -910,17 +910,17 @@
         <v>5.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
         <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U3" t="n">
         <v>1.99</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
@@ -1369,16 +1369,16 @@
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
         <v>1.77</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
         <v>1.71</v>
@@ -1387,10 +1387,10 @@
         <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
         <v>19</v>
@@ -1399,10 +1399,10 @@
         <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB5" t="n">
         <v>17</v>
@@ -1411,13 +1411,13 @@
         <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
@@ -1429,22 +1429,22 @@
         <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AK5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL5" t="n">
         <v>55</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>50</v>
       </c>
       <c r="AM5" t="n">
         <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AO5" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
         <v>15.5</v>
@@ -1456,7 +1456,7 @@
         <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AT5" t="n">
         <v>12.5</v>
@@ -1474,35 +1474,35 @@
         <v>22</v>
       </c>
       <c r="AY5" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5" t="n">
         <v>32</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6</v>
+        <v>3.65</v>
       </c>
       <c r="H6" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1581,10 +1581,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G7" t="n">
         <v>1.49</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.59</v>
-      </c>
       <c r="H7" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="I7" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
         <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1805,10 +1805,10 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1817,7 +1817,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AK7" t="n">
         <v>1000</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1844,22 +1844,22 @@
         <v>4.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.6</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AV7" t="n">
-        <v>19.5</v>
+        <v>4.1</v>
       </c>
       <c r="AW7" t="n">
         <v>4.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AY7" t="n">
         <v>3.5</v>
@@ -1874,7 +1874,7 @@
         <v>3.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>11.5</v>
+        <v>3.85</v>
       </c>
       <c r="BD7" t="n">
         <v>4.2</v>
@@ -1883,14 +1883,14 @@
         <v>4.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BG7" t="n">
         <v>4.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT8" t="n">
         <v>10.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="J9" t="n">
         <v>3.45</v>
@@ -2133,7 +2133,7 @@
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2145,7 +2145,7 @@
         <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
         <v>2.18</v>
@@ -2163,52 +2163,52 @@
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
         <v>32</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK9" t="n">
         <v>980</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>44</v>
       </c>
       <c r="AL9" t="n">
         <v>60</v>
@@ -2217,22 +2217,22 @@
         <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP9" t="n">
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT9" t="n">
         <v>11</v>
@@ -2244,41 +2244,41 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
         <v>21</v>
       </c>
       <c r="AY9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD9" t="n">
         <v>13</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BE9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF9" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="BG9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -2309,67 +2309,67 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H10" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="I10" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
         <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
         <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
         <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W10" t="n">
         <v>1.26</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA10" t="n">
         <v>20</v>
@@ -2381,7 +2381,7 @@
         <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2396,13 +2396,13 @@
         <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL10" t="n">
         <v>70</v>
@@ -2411,10 +2411,10 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP10" t="n">
         <v>13.5</v>
@@ -2426,10 +2426,10 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU10" t="n">
         <v>8</v>
@@ -2438,13 +2438,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW10" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AX10" t="n">
         <v>30</v>
       </c>
       <c r="AY10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>17.5</v>
@@ -2453,16 +2453,16 @@
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF10" t="n">
         <v>13</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -2509,16 +2509,16 @@
         <v>2.24</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
         <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
         <v>1.39</v>
@@ -2545,16 +2545,16 @@
         <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="U11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V11" t="n">
         <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X11" t="n">
         <v>19</v>
@@ -2566,7 +2566,7 @@
         <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB11" t="n">
         <v>11</v>
@@ -2578,7 +2578,7 @@
         <v>15.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
         <v>15.5</v>
@@ -2587,31 +2587,31 @@
         <v>11.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO11" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AP11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ11" t="n">
         <v>12.5</v>
@@ -2620,7 +2620,7 @@
         <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT11" t="n">
         <v>9.199999999999999</v>
@@ -2644,10 +2644,10 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BC11" t="n">
         <v>19.5</v>
@@ -2656,17 +2656,17 @@
         <v>8</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -2724,13 +2724,13 @@
         <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P12" t="n">
         <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -2739,19 +2739,19 @@
         <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
         <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W12" t="n">
         <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12" t="n">
         <v>7.8</v>
@@ -2793,7 +2793,7 @@
         <v>60</v>
       </c>
       <c r="AL12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2802,7 +2802,7 @@
         <v>80</v>
       </c>
       <c r="AO12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
         <v>9.199999999999999</v>
@@ -2856,11 +2856,11 @@
         <v>34</v>
       </c>
       <c r="BG12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>2.52</v>
       </c>
       <c r="I13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J13" t="n">
         <v>3.15</v>
@@ -2972,7 +2972,7 @@
         <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
@@ -3011,10 +3011,10 @@
         <v>34</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
         <v>11.5</v>
@@ -3029,7 +3029,7 @@
         <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
         <v>46</v>
@@ -3038,7 +3038,7 @@
         <v>55</v>
       </c>
       <c r="BC13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD13" t="n">
         <v>55</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -3091,10 +3091,10 @@
         <v>3.25</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I14" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
@@ -3115,16 +3115,16 @@
         <v>1.36</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
         <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T14" t="n">
         <v>1.84</v>
@@ -3142,25 +3142,25 @@
         <v>12</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
         <v>15.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB14" t="n">
         <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
         <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF14" t="n">
         <v>21</v>
@@ -3184,10 +3184,10 @@
         <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO14" t="n">
         <v>25</v>
@@ -3196,7 +3196,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR14" t="n">
         <v>14.5</v>
@@ -3205,16 +3205,16 @@
         <v>32</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX14" t="n">
         <v>19</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -3285,58 +3285,58 @@
         <v>2.1</v>
       </c>
       <c r="H15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.8</v>
       </c>
-      <c r="I15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="U15" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
         <v>1.9</v>
       </c>
       <c r="X15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
         <v>28</v>
@@ -3345,28 +3345,28 @@
         <v>75</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ15" t="n">
         <v>26</v>
@@ -3375,34 +3375,34 @@
         <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO15" t="n">
         <v>42</v>
       </c>
       <c r="AP15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS15" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AT15" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV15" t="n">
         <v>14</v>
@@ -3417,32 +3417,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BB15" t="n">
         <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE15" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF15" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
         <v>1.35</v>
       </c>
       <c r="H16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I16" t="n">
         <v>10.5</v>
       </c>
-      <c r="I16" t="n">
-        <v>13.5</v>
-      </c>
       <c r="J16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R16" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="T16" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V16" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X16" t="n">
         <v>36</v>
@@ -3539,13 +3539,13 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AD16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
@@ -3557,7 +3557,7 @@
         <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3566,7 +3566,7 @@
         <v>10.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
@@ -3581,28 +3581,28 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT16" t="n">
         <v>9</v>
       </c>
       <c r="AU16" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
@@ -3611,32 +3611,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H17" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3700,25 +3700,25 @@
         <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
         <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X17" t="n">
         <v>16.5</v>
@@ -3760,7 +3760,7 @@
         <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL17" t="n">
         <v>50</v>
@@ -3787,7 +3787,7 @@
         <v>42</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU17" t="n">
         <v>7.4</v>
@@ -3796,41 +3796,41 @@
         <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX17" t="n">
         <v>14.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE17" t="n">
         <v>6</v>
       </c>
       <c r="BF17" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BG17" t="n">
         <v>5.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -3870,19 +3870,19 @@
         <v>2.4</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
         <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
         <v>3.1</v>
@@ -3903,7 +3903,7 @@
         <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
         <v>1.98</v>
@@ -3918,7 +3918,7 @@
         <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z18" t="n">
         <v>16.5</v>
@@ -3978,7 +3978,7 @@
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
@@ -4002,29 +4002,29 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BG18" t="n">
         <v>20</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>2.66</v>
       </c>
       <c r="G19" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I19" t="n">
         <v>2.86</v>
@@ -4079,7 +4079,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>1.27</v>
@@ -4088,13 +4088,13 @@
         <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
         <v>1.64</v>
@@ -4103,7 +4103,7 @@
         <v>2.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W19" t="n">
         <v>1.51</v>
@@ -4160,7 +4160,7 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
         <v>14</v>
@@ -4169,7 +4169,7 @@
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -4187,38 +4187,38 @@
         <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BA19" t="n">
         <v>30</v>
       </c>
       <c r="BB19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC19" t="n">
         <v>7</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BD19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF19" t="n">
         <v>6.6</v>
       </c>
-      <c r="BD19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG19" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>2.46</v>
       </c>
       <c r="I20" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>3.45</v>
@@ -4279,7 +4279,7 @@
         <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q20" t="n">
         <v>2.14</v>
@@ -4297,13 +4297,13 @@
         <v>2.08</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W20" t="n">
         <v>1.44</v>
       </c>
       <c r="X20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="n">
         <v>9.800000000000001</v>
@@ -4312,7 +4312,7 @@
         <v>15.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB20" t="n">
         <v>11.5</v>
@@ -4333,7 +4333,7 @@
         <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="n">
         <v>140</v>
@@ -4387,7 +4387,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
         <v>38</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G21" t="n">
         <v>2.36</v>
@@ -4458,7 +4458,7 @@
         <v>2.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="L21" t="n">
         <v>1.75</v>
@@ -4476,7 +4476,7 @@
         <v>1.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
         <v>1.12</v>
@@ -4485,13 +4485,13 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="U21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
         <v>1.73</v>
@@ -4557,7 +4557,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR21" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AS21" t="n">
         <v>9.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -4649,13 +4649,13 @@
         <v>5.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
         <v>3.35</v>
       </c>
       <c r="L22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M22" t="n">
         <v>1.13</v>
@@ -4664,7 +4664,7 @@
         <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P22" t="n">
         <v>1.5</v>
@@ -4679,13 +4679,13 @@
         <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
         <v>1.69</v>
       </c>
       <c r="V22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
         <v>1.9</v>
@@ -4763,7 +4763,7 @@
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AW22" t="n">
         <v>9.4</v>
@@ -4787,7 +4787,7 @@
         <v>7.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BE22" t="n">
         <v>10</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>1.24</v>
       </c>
       <c r="G23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H23" t="n">
         <v>15</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="J23" t="n">
         <v>7.2</v>
@@ -4849,31 +4849,31 @@
         <v>7.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
         <v>2.44</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R23" t="n">
         <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
         <v>1.67</v>
@@ -4882,10 +4882,10 @@
         <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="X23" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Y23" t="n">
         <v>46</v>
@@ -4897,16 +4897,16 @@
         <v>990</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
         <v>16.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE23" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AF23" t="n">
         <v>7.2</v>
@@ -4936,31 +4936,31 @@
         <v>4.4</v>
       </c>
       <c r="AO23" t="n">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="AP23" t="n">
         <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS23" t="n">
         <v>16.5</v>
       </c>
-      <c r="AS23" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AT23" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AW23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
         <v>6.6</v>
@@ -4969,10 +4969,10 @@
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BA23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB23" t="n">
         <v>8.199999999999999</v>
@@ -4981,20 +4981,20 @@
         <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>1.85</v>
       </c>
       <c r="I24" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="J24" t="n">
         <v>3.9</v>
@@ -5046,16 +5046,16 @@
         <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
         <v>1.95</v>
@@ -5064,22 +5064,22 @@
         <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T24" t="n">
         <v>1.84</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V24" t="n">
         <v>2.12</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y24" t="n">
         <v>9.199999999999999</v>
@@ -5103,7 +5103,7 @@
         <v>19.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AG24" t="n">
         <v>19</v>
@@ -5127,7 +5127,7 @@
         <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO24" t="n">
         <v>13</v>
@@ -5142,10 +5142,10 @@
         <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU24" t="n">
         <v>7.6</v>
@@ -5154,13 +5154,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX24" t="n">
         <v>30</v>
       </c>
       <c r="AY24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ24" t="n">
         <v>17</v>
@@ -5169,26 +5169,26 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC24" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BE24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF24" t="n">
         <v>13</v>
       </c>
-      <c r="BF24" t="n">
-        <v>12</v>
-      </c>
       <c r="BG24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="G25" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H25" t="n">
         <v>4.4</v>
@@ -5231,10 +5231,10 @@
         <v>4.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
         <v>1.4</v>
@@ -5243,13 +5243,13 @@
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P25" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
         <v>1.96</v>
@@ -5258,37 +5258,37 @@
         <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T25" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W25" t="n">
         <v>2.1</v>
       </c>
-      <c r="V25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.08</v>
-      </c>
       <c r="X25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z25" t="n">
         <v>34</v>
       </c>
       <c r="AA25" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25" t="n">
         <v>17.5</v>
@@ -5300,19 +5300,19 @@
         <v>11.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL25" t="n">
         <v>36</v>
@@ -5324,65 +5324,65 @@
         <v>13</v>
       </c>
       <c r="AO25" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP25" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV25" t="n">
         <v>15.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY25" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA25" t="n">
-        <v>48</v>
+        <v>13.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD25" t="n">
         <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="H26" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I26" t="n">
         <v>2.14</v>
@@ -5443,28 +5443,28 @@
         <v>1.26</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R26" t="n">
         <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T26" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U26" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V26" t="n">
         <v>1.87</v>
       </c>
       <c r="W26" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
         <v>23</v>
@@ -5473,13 +5473,13 @@
         <v>11.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA26" t="n">
         <v>29</v>
       </c>
       <c r="AB26" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AC26" t="n">
         <v>10</v>
@@ -5491,37 +5491,37 @@
         <v>22</v>
       </c>
       <c r="AF26" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP26" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>9.800000000000001</v>
@@ -5530,53 +5530,53 @@
         <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT26" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AU26" t="n">
         <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AY26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ26" t="n">
         <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.4</v>
+        <v>55</v>
       </c>
       <c r="BC26" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BD26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -5613,16 +5613,16 @@
         <v>1.6</v>
       </c>
       <c r="H27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J27" t="n">
         <v>4.5</v>
       </c>
       <c r="K27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L27" t="n">
         <v>1.35</v>
@@ -5634,7 +5634,7 @@
         <v>4.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P27" t="n">
         <v>2.18</v>
@@ -5649,13 +5649,13 @@
         <v>3.05</v>
       </c>
       <c r="T27" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U27" t="n">
         <v>2.06</v>
       </c>
       <c r="V27" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W27" t="n">
         <v>2.66</v>
@@ -5670,10 +5670,10 @@
         <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC27" t="n">
         <v>10</v>
@@ -5682,13 +5682,13 @@
         <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF27" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH27" t="n">
         <v>22</v>
@@ -5703,10 +5703,10 @@
         <v>16</v>
       </c>
       <c r="AL27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN27" t="n">
         <v>8</v>
@@ -5721,22 +5721,22 @@
         <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT27" t="n">
         <v>8.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW27" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX27" t="n">
         <v>9</v>
@@ -5748,7 +5748,7 @@
         <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5757,20 +5757,20 @@
         <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE27" t="n">
         <v>40</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG27" t="n">
         <v>38</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -5801,94 +5801,94 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G28" t="n">
         <v>2.78</v>
       </c>
       <c r="H28" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="I28" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.55</v>
       </c>
-      <c r="K28" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L28" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q28" t="n">
-        <v>1.92</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="T28" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="U28" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="V28" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W28" t="n">
         <v>1.56</v>
       </c>
       <c r="X28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG28" t="n">
         <v>13</v>
       </c>
-      <c r="Z28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH28" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="n">
         <v>44</v>
@@ -5897,52 +5897,52 @@
         <v>32</v>
       </c>
       <c r="AL28" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM28" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN28" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO28" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AP28" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS28" t="n">
         <v>34</v>
       </c>
       <c r="AT28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AX28" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB28" t="n">
         <v>34</v>
@@ -5951,20 +5951,20 @@
         <v>25</v>
       </c>
       <c r="BD28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE28" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BF28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BG28" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G29" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I29" t="n">
         <v>3.8</v>
       </c>
-      <c r="I29" t="n">
-        <v>3.9</v>
-      </c>
       <c r="J29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K29" t="n">
         <v>3.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.65</v>
       </c>
       <c r="L29" t="n">
         <v>1.44</v>
@@ -6025,7 +6025,7 @@
         <v>1.35</v>
       </c>
       <c r="P29" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
@@ -6037,16 +6037,16 @@
         <v>3.85</v>
       </c>
       <c r="T29" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U29" t="n">
         <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X29" t="n">
         <v>13</v>
@@ -6061,7 +6061,7 @@
         <v>75</v>
       </c>
       <c r="AB29" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC29" t="n">
         <v>7.8</v>
@@ -6070,7 +6070,7 @@
         <v>15.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF29" t="n">
         <v>13</v>
@@ -6088,7 +6088,7 @@
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL29" t="n">
         <v>40</v>
@@ -6112,7 +6112,7 @@
         <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AT29" t="n">
         <v>8.6</v>
@@ -6121,7 +6121,7 @@
         <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW29" t="n">
         <v>42</v>
@@ -6133,10 +6133,10 @@
         <v>10</v>
       </c>
       <c r="AZ29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB29" t="n">
         <v>25</v>
@@ -6145,10 +6145,10 @@
         <v>21</v>
       </c>
       <c r="BD29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF29" t="n">
         <v>16.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G30" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H30" t="n">
         <v>2.08</v>
@@ -6201,10 +6201,10 @@
         <v>2.16</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L30" t="n">
         <v>1.41</v>
@@ -6264,7 +6264,7 @@
         <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF30" t="n">
         <v>1000</v>
@@ -6327,13 +6327,13 @@
         <v>13</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BA30" t="n">
         <v>30</v>
       </c>
       <c r="BB30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC30" t="n">
         <v>26</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G31" t="n">
         <v>4.3</v>
       </c>
       <c r="H31" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I31" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J31" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L31" t="n">
         <v>1.6</v>
@@ -6431,7 +6431,7 @@
         <v>1.73</v>
       </c>
       <c r="V31" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W31" t="n">
         <v>1.31</v>
@@ -6443,7 +6443,7 @@
         <v>7.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -6491,7 +6491,7 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ31" t="n">
         <v>6.2</v>
@@ -6500,7 +6500,7 @@
         <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT31" t="n">
         <v>9.199999999999999</v>
@@ -6512,7 +6512,7 @@
         <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX31" t="n">
         <v>18.5</v>
@@ -6524,29 +6524,29 @@
         <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF31" t="n">
         <v>10</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
         <v>3.05</v>
       </c>
       <c r="K32" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L32" t="n">
         <v>1.65</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
         <v>2.44</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
         <v>3.75</v>
@@ -6795,13 +6795,13 @@
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O33" t="n">
         <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
         <v>1.9</v>
@@ -6816,7 +6816,7 @@
         <v>1.73</v>
       </c>
       <c r="U33" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V33" t="n">
         <v>1.69</v>
@@ -6849,7 +6849,7 @@
         <v>28</v>
       </c>
       <c r="AF33" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG33" t="n">
         <v>15.5</v>
@@ -6876,7 +6876,7 @@
         <v>980</v>
       </c>
       <c r="AO33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP33" t="n">
         <v>14</v>
@@ -6930,11 +6930,11 @@
         <v>20</v>
       </c>
       <c r="BG33" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -6968,19 +6968,19 @@
         <v>1.42</v>
       </c>
       <c r="G34" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I34" t="n">
         <v>10.5</v>
       </c>
       <c r="J34" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K34" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L34" t="n">
         <v>1.36</v>
@@ -7010,13 +7010,13 @@
         <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V34" t="n">
         <v>1.1</v>
       </c>
       <c r="W34" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="X34" t="n">
         <v>19</v>
@@ -7043,7 +7043,7 @@
         <v>190</v>
       </c>
       <c r="AF34" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG34" t="n">
         <v>10.5</v>
@@ -7073,13 +7073,13 @@
         <v>280</v>
       </c>
       <c r="AP34" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ34" t="n">
         <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS34" t="n">
         <v>10.5</v>
@@ -7094,7 +7094,7 @@
         <v>8.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX34" t="n">
         <v>7.2</v>
@@ -7118,17 +7118,17 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE34" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF34" t="n">
         <v>6.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
         <v>2.34</v>
       </c>
       <c r="U35" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V35" t="n">
         <v>1.58</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O36" t="n">
         <v>1.35</v>
@@ -7422,7 +7422,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD36" t="n">
         <v>980</v>
@@ -7467,7 +7467,7 @@
         <v>12</v>
       </c>
       <c r="AR36" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS36" t="n">
         <v>11</v>
@@ -7491,7 +7491,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ36" t="n">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="BA36" t="n">
         <v>11</v>
@@ -7500,13 +7500,13 @@
         <v>20</v>
       </c>
       <c r="BC36" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BD36" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BE36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF36" t="n">
         <v>7.2</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 15:15:29</t>
+          <t>2026-03-11 17:30:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -766,16 +766,16 @@
         <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -787,19 +787,19 @@
         <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
         <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
         <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
         <v>2.12</v>
@@ -808,43 +808,43 @@
         <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y2" t="n">
         <v>19</v>
       </c>
-      <c r="Y2" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Z2" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>980</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
         <v>25</v>
@@ -856,40 +856,40 @@
         <v>980</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU2" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.7</v>
       </c>
       <c r="AV2" t="n">
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
         <v>8.800000000000001</v>
@@ -898,29 +898,29 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -957,13 +957,13 @@
         <v>1.7</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>4.7</v>
@@ -993,7 +993,7 @@
         <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
         <v>1.99</v>
@@ -1005,7 +1005,7 @@
         <v>2.42</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
         <v>27</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC3" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12</v>
       </c>
       <c r="AD3" t="n">
         <v>29</v>
@@ -1029,10 +1029,10 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>25</v>
@@ -1044,10 +1044,10 @@
         <v>16.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1065,10 +1065,10 @@
         <v>18.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -1080,41 +1080,41 @@
         <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AY3" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB3" t="n">
         <v>5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4</v>
       </c>
       <c r="BC3" t="n">
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G4" t="n">
         <v>3.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I4" t="n">
         <v>2.7</v>
       </c>
       <c r="J4" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
         <v>3.8</v>
@@ -1175,7 +1175,7 @@
         <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
         <v>1.98</v>
@@ -1196,19 +1196,19 @@
         <v>1.59</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AA4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB4" t="n">
         <v>14</v>
@@ -1220,37 +1220,37 @@
         <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
         <v>26</v>
       </c>
       <c r="AG4" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP4" t="n">
         <v>10.5</v>
@@ -1262,7 +1262,7 @@
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="AT4" t="n">
         <v>9.800000000000001</v>
@@ -1274,7 +1274,7 @@
         <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AX4" t="n">
         <v>18</v>
@@ -1286,29 +1286,29 @@
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG4" t="n">
         <v>18</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>4.6</v>
@@ -1348,10 +1348,10 @@
         <v>1.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
@@ -1378,7 +1378,7 @@
         <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T5" t="n">
         <v>1.71</v>
@@ -1387,7 +1387,7 @@
         <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W5" t="n">
         <v>1.28</v>
@@ -1402,7 +1402,7 @@
         <v>13.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB5" t="n">
         <v>17</v>
@@ -1438,7 +1438,7 @@
         <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
         <v>48</v>
@@ -1480,29 +1480,29 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC5" t="n">
         <v>32</v>
       </c>
       <c r="BD5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF5" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -1545,7 +1545,7 @@
         <v>2.28</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
         <v>4.9</v>
@@ -1584,7 +1584,7 @@
         <v>1.78</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>11.5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
         <v>5.3</v>
@@ -1769,10 +1769,10 @@
         <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -1808,7 +1808,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1817,10 +1817,10 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14.5</v>
+        <v>180</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1838,59 +1838,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AR7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX7" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV7" t="n">
+      <c r="AY7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BC7" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BF7" t="n">
         <v>5.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I8" t="n">
         <v>2.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.86</v>
       </c>
       <c r="J8" t="n">
         <v>3.55</v>
@@ -1939,7 +1939,7 @@
         <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
@@ -1969,13 +1969,13 @@
         <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -1987,7 +1987,7 @@
         <v>44</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
         <v>7.8</v>
@@ -2008,7 +2008,7 @@
         <v>17</v>
       </c>
       <c r="AI8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
         <v>42</v>
@@ -2017,7 +2017,7 @@
         <v>30</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
         <v>90</v>
@@ -2038,7 +2038,7 @@
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
         <v>10.5</v>
@@ -2053,7 +2053,7 @@
         <v>27</v>
       </c>
       <c r="AX8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
         <v>11</v>
@@ -2074,7 +2074,7 @@
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="BF8" t="n">
         <v>22</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I9" t="n">
         <v>2.28</v>
@@ -2172,7 +2172,7 @@
         <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
         <v>13.5</v>
@@ -2202,13 +2202,13 @@
         <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
         <v>75</v>
       </c>
       <c r="AK9" t="n">
-        <v>980</v>
+        <v>170</v>
       </c>
       <c r="AL9" t="n">
         <v>60</v>
@@ -2226,7 +2226,7 @@
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>12</v>
@@ -2235,10 +2235,10 @@
         <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
         <v>10</v>
@@ -2253,10 +2253,10 @@
         <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB9" t="n">
         <v>14</v>
@@ -2268,17 +2268,17 @@
         <v>13</v>
       </c>
       <c r="BE9" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="BF9" t="n">
         <v>40</v>
       </c>
       <c r="BG9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -2309,70 +2309,70 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="I10" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="J10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
         <v>1.92</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
         <v>3.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W10" t="n">
         <v>1.26</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB10" t="n">
         <v>17</v>
@@ -2384,40 +2384,40 @@
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF10" t="n">
         <v>36</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
       </c>
       <c r="AI10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1000</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>120</v>
-      </c>
       <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
         <v>65</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>70</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="n">
         <v>12.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>8</v>
@@ -2426,13 +2426,13 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT10" t="n">
         <v>14</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
         <v>9.199999999999999</v>
@@ -2444,7 +2444,7 @@
         <v>30</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>17.5</v>
@@ -2453,26 +2453,26 @@
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="BD10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE10" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="BG10" t="n">
         <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G11" t="n">
         <v>2.2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.24</v>
       </c>
       <c r="H11" t="n">
         <v>3.7</v>
@@ -2515,7 +2515,7 @@
         <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
         <v>3.65</v>
@@ -2548,22 +2548,22 @@
         <v>1.74</v>
       </c>
       <c r="U11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V11" t="n">
         <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="n">
         <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA11" t="n">
         <v>70</v>
@@ -2575,52 +2575,52 @@
         <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF11" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
         <v>13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
         <v>9.199999999999999</v>
@@ -2632,7 +2632,7 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX11" t="n">
         <v>12.5</v>
@@ -2641,32 +2641,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BC11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BF11" t="n">
         <v>13.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
@@ -2715,55 +2715,55 @@
         <v>3.45</v>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="V12" t="n">
         <v>1.79</v>
       </c>
       <c r="W12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z12" t="n">
         <v>12.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
         <v>7.4</v>
@@ -2772,46 +2772,46 @@
         <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF12" t="n">
         <v>27</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK12" t="n">
         <v>55</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>60</v>
-      </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AO12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS12" t="n">
         <v>26</v>
@@ -2823,44 +2823,44 @@
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BB12" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BC12" t="n">
         <v>42</v>
       </c>
       <c r="BD12" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BE12" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="BF12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G13" t="n">
         <v>3.45</v>
@@ -2918,19 +2918,19 @@
         <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q13" t="n">
         <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T13" t="n">
         <v>2.06</v>
@@ -2945,7 +2945,7 @@
         <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
         <v>8.4</v>
@@ -2987,7 +2987,7 @@
         <v>46</v>
       </c>
       <c r="AL13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
@@ -3032,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB13" t="n">
         <v>55</v>
@@ -3044,7 +3044,7 @@
         <v>55</v>
       </c>
       <c r="BE13" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BF13" t="n">
         <v>50</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I14" t="n">
         <v>2.52</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.56</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
@@ -3112,7 +3112,7 @@
         <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P14" t="n">
         <v>1.86</v>
@@ -3127,19 +3127,19 @@
         <v>3.85</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
         <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
         <v>10</v>
@@ -3151,13 +3151,13 @@
         <v>36</v>
       </c>
       <c r="AB14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD14" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>28</v>
@@ -3172,13 +3172,13 @@
         <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL14" t="n">
         <v>50</v>
@@ -3196,7 +3196,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR14" t="n">
         <v>14.5</v>
@@ -3214,7 +3214,7 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX14" t="n">
         <v>19</v>
@@ -3223,13 +3223,13 @@
         <v>12.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC14" t="n">
         <v>32</v>
@@ -3238,17 +3238,17 @@
         <v>44</v>
       </c>
       <c r="BE14" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BF14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -3279,28 +3279,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
         <v>3.95</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
         <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
         <v>4.1</v>
@@ -3312,7 +3312,7 @@
         <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
@@ -3321,7 +3321,7 @@
         <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U15" t="n">
         <v>2.22</v>
@@ -3330,7 +3330,7 @@
         <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X15" t="n">
         <v>16</v>
@@ -3348,7 +3348,7 @@
         <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
         <v>15.5</v>
@@ -3363,7 +3363,7 @@
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
         <v>55</v>
@@ -3387,7 +3387,7 @@
         <v>42</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
         <v>13.5</v>
@@ -3396,7 +3396,7 @@
         <v>25</v>
       </c>
       <c r="AS15" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AT15" t="n">
         <v>9.6</v>
@@ -3405,10 +3405,10 @@
         <v>7.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX15" t="n">
         <v>12.5</v>
@@ -3417,32 +3417,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="BF15" t="n">
         <v>13.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="G16" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="H16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K16" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.23</v>
@@ -3497,40 +3497,40 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
         <v>1.51</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S16" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V16" t="n">
         <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="X16" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,13 +3539,13 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
@@ -3554,67 +3554,67 @@
         <v>10</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK16" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AR16" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BB16" t="n">
         <v>9</v>
@@ -3623,20 +3623,20 @@
         <v>10</v>
       </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
         <v>3.95</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
         <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
         <v>1.98</v>
@@ -3709,7 +3709,7 @@
         <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U17" t="n">
         <v>2.22</v>
@@ -3730,7 +3730,7 @@
         <v>980</v>
       </c>
       <c r="AA17" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
         <v>12</v>
@@ -3766,7 +3766,7 @@
         <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
         <v>24</v>
@@ -3775,7 +3775,7 @@
         <v>980</v>
       </c>
       <c r="AP17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>11.5</v>
@@ -3784,7 +3784,7 @@
         <v>16.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT17" t="n">
         <v>9.800000000000001</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -3870,46 +3870,46 @@
         <v>2.4</v>
       </c>
       <c r="I18" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J18" t="n">
         <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T18" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W18" t="n">
         <v>1.41</v>
@@ -3918,25 +3918,25 @@
         <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
         <v>16.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
         <v>7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF18" t="n">
         <v>22</v>
@@ -3945,10 +3945,10 @@
         <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>980</v>
+        <v>290</v>
       </c>
       <c r="AJ18" t="n">
         <v>60</v>
@@ -3966,7 +3966,7 @@
         <v>44</v>
       </c>
       <c r="AO18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
@@ -3990,7 +3990,7 @@
         <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AX18" t="n">
         <v>18.5</v>
@@ -4002,29 +4002,29 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG18" t="n">
         <v>20</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>2.66</v>
       </c>
       <c r="G19" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="I19" t="n">
         <v>2.86</v>
@@ -4070,7 +4070,7 @@
         <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.31</v>
@@ -4085,7 +4085,7 @@
         <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
         <v>1.81</v>
@@ -4109,10 +4109,10 @@
         <v>1.51</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -4127,7 +4127,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
@@ -4136,10 +4136,10 @@
         <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
@@ -4169,13 +4169,13 @@
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
@@ -4184,41 +4184,41 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA19" t="n">
         <v>30</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF19" t="n">
         <v>7</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.6</v>
       </c>
       <c r="BG19" t="n">
         <v>16.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G20" t="n">
         <v>3.25</v>
@@ -4279,7 +4279,7 @@
         <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q20" t="n">
         <v>2.14</v>
@@ -4294,7 +4294,7 @@
         <v>1.86</v>
       </c>
       <c r="U20" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V20" t="n">
         <v>1.66</v>
@@ -4336,7 +4336,7 @@
         <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AJ20" t="n">
         <v>60</v>
@@ -4378,13 +4378,13 @@
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX20" t="n">
         <v>19</v>
       </c>
       <c r="AY20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
         <v>17</v>
@@ -4402,17 +4402,17 @@
         <v>42</v>
       </c>
       <c r="BE20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BF20" t="n">
         <v>34</v>
       </c>
       <c r="BG20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>2.24</v>
       </c>
       <c r="G21" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K21" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.75</v>
@@ -4467,10 +4467,10 @@
         <v>1.18</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O21" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="P21" t="n">
         <v>1.34</v>
@@ -4479,13 +4479,13 @@
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
         <v>1.53</v>
@@ -4494,13 +4494,13 @@
         <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Z21" t="n">
         <v>980</v>
@@ -4509,7 +4509,7 @@
         <v>160</v>
       </c>
       <c r="AB21" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AC21" t="n">
         <v>7.6</v>
@@ -4551,28 +4551,28 @@
         <v>240</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR21" t="n">
         <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
         <v>18.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -4581,32 +4581,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC21" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BD21" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BE21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF21" t="n">
         <v>10</v>
       </c>
-      <c r="BF21" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG21" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
         <v>18</v>
       </c>
       <c r="AW22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX22" t="n">
         <v>9.4</v>
@@ -4775,7 +4775,7 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA22" t="n">
         <v>9.6</v>
@@ -4787,7 +4787,7 @@
         <v>7.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="BE22" t="n">
         <v>10</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -4834,70 +4834,70 @@
         <v>1.24</v>
       </c>
       <c r="G23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I23" t="n">
         <v>17.5</v>
       </c>
       <c r="J23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.29</v>
       </c>
       <c r="M23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P23" t="n">
         <v>2.44</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R23" t="n">
         <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V23" t="n">
         <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="X23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y23" t="n">
         <v>46</v>
       </c>
       <c r="Z23" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AA23" t="n">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC23" t="n">
         <v>16.5</v>
@@ -4906,7 +4906,7 @@
         <v>60</v>
       </c>
       <c r="AE23" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AF23" t="n">
         <v>7.2</v>
@@ -4915,86 +4915,86 @@
         <v>12</v>
       </c>
       <c r="AH23" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI23" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AK23" t="n">
         <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM23" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AN23" t="n">
         <v>4.4</v>
       </c>
       <c r="AO23" t="n">
-        <v>560</v>
+        <v>470</v>
       </c>
       <c r="AP23" t="n">
         <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AR23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS23" t="n">
         <v>17.5</v>
       </c>
-      <c r="AS23" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AT23" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU23" t="n">
         <v>14.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AX23" t="n">
         <v>6.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
         <v>36</v>
       </c>
       <c r="BA23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC23" t="n">
         <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE23" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G24" t="n">
         <v>4.7</v>
       </c>
-      <c r="G24" t="n">
-        <v>4.9</v>
-      </c>
       <c r="H24" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I24" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J24" t="n">
         <v>3.9</v>
@@ -5046,16 +5046,16 @@
         <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
         <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
         <v>1.95</v>
@@ -5064,25 +5064,25 @@
         <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T24" t="n">
         <v>1.84</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V24" t="n">
         <v>2.12</v>
       </c>
       <c r="W24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X24" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z24" t="n">
         <v>11.5</v>
@@ -5121,13 +5121,13 @@
         <v>65</v>
       </c>
       <c r="AL24" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO24" t="n">
         <v>13</v>
@@ -5145,7 +5145,7 @@
         <v>18.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AU24" t="n">
         <v>7.6</v>
@@ -5160,7 +5160,7 @@
         <v>30</v>
       </c>
       <c r="AY24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ24" t="n">
         <v>17</v>
@@ -5169,26 +5169,26 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BD24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="BF24" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="BG24" t="n">
         <v>11</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G25" t="n">
         <v>1.89</v>
       </c>
-      <c r="G25" t="n">
-        <v>1.9</v>
-      </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
@@ -5240,7 +5240,7 @@
         <v>1.4</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
         <v>3.95</v>
@@ -5258,22 +5258,22 @@
         <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
         <v>1.87</v>
       </c>
       <c r="U25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V25" t="n">
         <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X25" t="n">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="Y25" t="n">
         <v>17</v>
@@ -5321,34 +5321,34 @@
         <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO25" t="n">
         <v>65</v>
       </c>
       <c r="AP25" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
         <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV25" t="n">
         <v>15.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -5363,7 +5363,7 @@
         <v>13.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC25" t="n">
         <v>18</v>
@@ -5372,17 +5372,17 @@
         <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BF25" t="n">
         <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G26" t="n">
         <v>3.75</v>
@@ -5425,7 +5425,7 @@
         <v>2.14</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K26" t="n">
         <v>3.9</v>
@@ -5446,7 +5446,7 @@
         <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R26" t="n">
         <v>1.46</v>
@@ -5455,40 +5455,40 @@
         <v>2.96</v>
       </c>
       <c r="T26" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W26" t="n">
         <v>1.36</v>
       </c>
       <c r="X26" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Y26" t="n">
         <v>11.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB26" t="n">
         <v>15.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF26" t="n">
         <v>27</v>
@@ -5503,37 +5503,37 @@
         <v>34</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK26" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT26" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AU26" t="n">
         <v>7.8</v>
@@ -5542,41 +5542,41 @@
         <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BB26" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BC26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="BF26" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BG26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H27" t="n">
         <v>6.4</v>
       </c>
       <c r="I27" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
         <v>4.5</v>
@@ -5655,13 +5655,13 @@
         <v>2.06</v>
       </c>
       <c r="V27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W27" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X27" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" t="n">
         <v>23</v>
@@ -5670,19 +5670,19 @@
         <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27" t="n">
         <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
         <v>9.800000000000001</v>
@@ -5706,16 +5706,16 @@
         <v>32</v>
       </c>
       <c r="AM27" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO27" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP27" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>21</v>
@@ -5724,7 +5724,7 @@
         <v>46</v>
       </c>
       <c r="AS27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT27" t="n">
         <v>8.6</v>
@@ -5736,41 +5736,41 @@
         <v>22</v>
       </c>
       <c r="AW27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
         <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE27" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5807,13 +5807,13 @@
         <v>2.78</v>
       </c>
       <c r="H28" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J28" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
         <v>3.55</v>
@@ -5831,7 +5831,7 @@
         <v>1.34</v>
       </c>
       <c r="P28" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q28" t="n">
         <v>2.04</v>
@@ -5849,13 +5849,13 @@
         <v>2.18</v>
       </c>
       <c r="V28" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W28" t="n">
         <v>1.56</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y28" t="n">
         <v>11.5</v>
@@ -5864,46 +5864,46 @@
         <v>18.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB28" t="n">
         <v>11.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF28" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
         <v>17.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL28" t="n">
         <v>44</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>46</v>
       </c>
       <c r="AM28" t="n">
         <v>95</v>
       </c>
       <c r="AN28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO28" t="n">
         <v>28</v>
@@ -5912,16 +5912,16 @@
         <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS28" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU28" t="n">
         <v>7.2</v>
@@ -5933,38 +5933,38 @@
         <v>28</v>
       </c>
       <c r="AX28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
         <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB28" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BC28" t="n">
         <v>25</v>
       </c>
       <c r="BD28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE28" t="n">
         <v>36</v>
       </c>
       <c r="BF28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G29" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H29" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="J29" t="n">
         <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L29" t="n">
         <v>1.44</v>
@@ -6022,13 +6022,13 @@
         <v>3.65</v>
       </c>
       <c r="O29" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P29" t="n">
         <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R29" t="n">
         <v>1.33</v>
@@ -6043,10 +6043,10 @@
         <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X29" t="n">
         <v>13</v>
@@ -6055,22 +6055,22 @@
         <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA29" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC29" t="n">
         <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF29" t="n">
         <v>13</v>
@@ -6079,7 +6079,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI29" t="n">
         <v>60</v>
@@ -6097,10 +6097,10 @@
         <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP29" t="n">
         <v>12</v>
@@ -6109,10 +6109,10 @@
         <v>12.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AT29" t="n">
         <v>8.6</v>
@@ -6133,13 +6133,13 @@
         <v>10</v>
       </c>
       <c r="AZ29" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC29" t="n">
         <v>21</v>
@@ -6148,17 +6148,17 @@
         <v>36</v>
       </c>
       <c r="BE29" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BF29" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG29" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G30" t="n">
         <v>3.9</v>
       </c>
       <c r="H30" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I30" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K30" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L30" t="n">
         <v>1.41</v>
@@ -6228,16 +6228,16 @@
         <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U30" t="n">
         <v>2.08</v>
       </c>
       <c r="V30" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="W30" t="n">
         <v>1.34</v>
@@ -6261,7 +6261,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE30" t="n">
         <v>30</v>
@@ -6324,13 +6324,13 @@
         <v>22</v>
       </c>
       <c r="AY30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB30" t="n">
         <v>34</v>
@@ -6339,7 +6339,7 @@
         <v>26</v>
       </c>
       <c r="BD30" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BE30" t="n">
         <v>40</v>
@@ -6348,11 +6348,11 @@
         <v>27</v>
       </c>
       <c r="BG30" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -6386,16 +6386,16 @@
         <v>3.75</v>
       </c>
       <c r="G31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H31" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I31" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J31" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>3.2</v>
@@ -6404,10 +6404,10 @@
         <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N31" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O31" t="n">
         <v>1.57</v>
@@ -6416,13 +6416,13 @@
         <v>1.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R31" t="n">
         <v>1.17</v>
       </c>
       <c r="S31" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T31" t="n">
         <v>2.16</v>
@@ -6431,7 +6431,7 @@
         <v>1.73</v>
       </c>
       <c r="V31" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W31" t="n">
         <v>1.31</v>
@@ -6455,7 +6455,7 @@
         <v>7.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
@@ -6500,7 +6500,7 @@
         <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT31" t="n">
         <v>9.199999999999999</v>
@@ -6512,41 +6512,41 @@
         <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX31" t="n">
         <v>18.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB31" t="n">
         <v>10</v>
       </c>
       <c r="BC31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
       </c>
       <c r="BE31" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF31" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF31" t="n">
-        <v>10</v>
-      </c>
       <c r="BG31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H32" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J32" t="n">
         <v>3.05</v>
@@ -6613,7 +6613,7 @@
         <v>2.94</v>
       </c>
       <c r="R32" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S32" t="n">
         <v>6.6</v>
@@ -6625,16 +6625,16 @@
         <v>1.68</v>
       </c>
       <c r="V32" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X32" t="n">
         <v>8.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z32" t="n">
         <v>38</v>
@@ -6646,7 +6646,7 @@
         <v>6.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD32" t="n">
         <v>25</v>
@@ -6667,7 +6667,7 @@
         <v>130</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK32" t="n">
         <v>1000</v>
@@ -6691,13 +6691,13 @@
         <v>9</v>
       </c>
       <c r="AR32" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS32" t="n">
         <v>36</v>
       </c>
       <c r="AT32" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU32" t="n">
         <v>6.6</v>
@@ -6730,7 +6730,7 @@
         <v>50</v>
       </c>
       <c r="BE32" t="n">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="BF32" t="n">
         <v>23</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -6771,43 +6771,43 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G33" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H33" t="n">
         <v>2.4</v>
       </c>
       <c r="I33" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J33" t="n">
         <v>3.55</v>
       </c>
       <c r="K33" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L33" t="n">
         <v>1.39</v>
       </c>
       <c r="M33" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S33" t="n">
         <v>3.25</v>
@@ -6819,67 +6819,67 @@
         <v>2.24</v>
       </c>
       <c r="V33" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W33" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X33" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y33" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD33" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE33" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF33" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG33" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI33" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AJ33" t="n">
         <v>55</v>
       </c>
       <c r="AK33" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AL33" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM33" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN33" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AO33" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>10</v>
@@ -6894,47 +6894,47 @@
         <v>12</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AX33" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA33" t="n">
         <v>30</v>
       </c>
       <c r="BB33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC33" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BD33" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BE33" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BF33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG33" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G34" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H34" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I34" t="n">
         <v>10.5</v>
@@ -6980,7 +6980,7 @@
         <v>4.9</v>
       </c>
       <c r="K34" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L34" t="n">
         <v>1.36</v>
@@ -7010,13 +7010,13 @@
         <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V34" t="n">
         <v>1.1</v>
       </c>
       <c r="W34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X34" t="n">
         <v>19</v>
@@ -7028,7 +7028,7 @@
         <v>90</v>
       </c>
       <c r="AA34" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AB34" t="n">
         <v>8</v>
@@ -7091,7 +7091,7 @@
         <v>9.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="AW34" t="n">
         <v>10.5</v>
@@ -7115,7 +7115,7 @@
         <v>14</v>
       </c>
       <c r="BD34" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE34" t="n">
         <v>10.5</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -7171,13 +7171,13 @@
         <v>2.7</v>
       </c>
       <c r="J35" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K35" t="n">
         <v>3.05</v>
       </c>
       <c r="L35" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="M35" t="n">
         <v>1.16</v>
@@ -7189,7 +7189,7 @@
         <v>1.7</v>
       </c>
       <c r="P35" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q35" t="n">
         <v>3.1</v>
@@ -7204,7 +7204,7 @@
         <v>2.34</v>
       </c>
       <c r="U35" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V35" t="n">
         <v>1.58</v>
@@ -7228,7 +7228,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD35" t="n">
         <v>980</v>
@@ -7240,16 +7240,16 @@
         <v>980</v>
       </c>
       <c r="AG35" t="n">
-        <v>20</v>
+        <v>980</v>
       </c>
       <c r="AH35" t="n">
         <v>980</v>
       </c>
       <c r="AI35" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ35" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK35" t="n">
         <v>75</v>
@@ -7267,10 +7267,10 @@
         <v>70</v>
       </c>
       <c r="AP35" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR35" t="n">
         <v>10.5</v>
@@ -7288,41 +7288,41 @@
         <v>11.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX35" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY35" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BD35" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BE35" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF35" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -7377,13 +7377,13 @@
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
         <v>1.35</v>
       </c>
       <c r="P36" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q36" t="n">
         <v>2.04</v>
@@ -7467,7 +7467,7 @@
         <v>12</v>
       </c>
       <c r="AR36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS36" t="n">
         <v>11</v>
@@ -7503,20 +7503,20 @@
         <v>18.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG36" t="n">
         <v>4.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -790,7 +790,7 @@
         <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -799,7 +799,7 @@
         <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
         <v>2.12</v>
@@ -811,22 +811,22 @@
         <v>1.98</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AA2" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
         <v>980</v>
@@ -847,7 +847,7 @@
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
         <v>980</v>
@@ -856,37 +856,37 @@
         <v>980</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AV2" t="n">
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -898,29 +898,29 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC2" t="n">
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
         <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H3" t="n">
         <v>5.8</v>
@@ -969,7 +969,7 @@
         <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -987,10 +987,10 @@
         <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T3" t="n">
         <v>1.83</v>
@@ -1002,7 +1002,7 @@
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X3" t="n">
         <v>19</v>
@@ -1026,13 +1026,13 @@
         <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
         <v>25</v>
@@ -1047,10 +1047,10 @@
         <v>17.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>8.800000000000001</v>
@@ -1065,13 +1065,13 @@
         <v>18.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
         <v>8.4</v>
@@ -1080,41 +1080,41 @@
         <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
         <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -1157,10 +1157,10 @@
         <v>2.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>1.41</v>
@@ -1175,7 +1175,7 @@
         <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
         <v>1.98</v>
@@ -1193,7 +1193,7 @@
         <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
         <v>1.39</v>
@@ -1202,7 +1202,7 @@
         <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
         <v>17</v>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
         <v>13.5</v>
@@ -1229,7 +1229,7 @@
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
         <v>46</v>
@@ -1244,7 +1244,7 @@
         <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
         <v>42</v>
@@ -1286,29 +1286,29 @@
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
         <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
         <v>1.71</v>
@@ -1393,116 +1393,116 @@
         <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="Y5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC5" t="n">
         <v>11</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AD5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO5" t="n">
         <v>13.5</v>
       </c>
-      <c r="AA5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>12</v>
-      </c>
       <c r="AP5" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>18.5</v>
+        <v>3.9</v>
       </c>
       <c r="AT5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY5" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>14.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="I6" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1581,10 +1581,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1602,7 +1602,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.07</v>
+        <v>1.37</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
         <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -1784,7 +1784,7 @@
         <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1799,7 +1799,7 @@
         <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
@@ -1811,13 +1811,13 @@
         <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AK7" t="n">
         <v>30</v>
@@ -1838,16 +1838,16 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AS7" t="n">
         <v>5.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AU7" t="n">
         <v>5.8</v>
@@ -1865,13 +1865,13 @@
         <v>3.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA7" t="n">
         <v>5.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC7" t="n">
         <v>4.3</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G8" t="n">
         <v>2.82</v>
@@ -1945,7 +1945,7 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.32</v>
@@ -1963,28 +1963,28 @@
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
         <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
         <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Z8" t="n">
         <v>18.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AB8" t="n">
         <v>12</v>
@@ -2005,13 +2005,13 @@
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>40</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AK8" t="n">
         <v>30</v>
@@ -2023,13 +2023,13 @@
         <v>90</v>
       </c>
       <c r="AN8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO8" t="n">
         <v>25</v>
       </c>
-      <c r="AO8" t="n">
-        <v>26</v>
-      </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
@@ -2038,7 +2038,7 @@
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="AT8" t="n">
         <v>10.5</v>
@@ -2050,41 +2050,41 @@
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BF8" t="n">
         <v>11</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>22</v>
-      </c>
       <c r="BG8" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -2118,10 +2118,10 @@
         <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
         <v>2.28</v>
@@ -2169,7 +2169,7 @@
         <v>1.37</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
         <v>9</v>
@@ -2187,7 +2187,7 @@
         <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
         <v>27</v>
@@ -2208,7 +2208,7 @@
         <v>75</v>
       </c>
       <c r="AK9" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AL9" t="n">
         <v>60</v>
@@ -2253,32 +2253,32 @@
         <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD9" t="n">
         <v>14</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>13</v>
       </c>
       <c r="BE9" t="n">
         <v>60</v>
       </c>
       <c r="BF9" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -2366,13 +2366,13 @@
         <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z10" t="n">
         <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB10" t="n">
         <v>17</v>
@@ -2384,7 +2384,7 @@
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AF10" t="n">
         <v>36</v>
@@ -2402,7 +2402,7 @@
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AL10" t="n">
         <v>65</v>
@@ -2414,10 +2414,10 @@
         <v>80</v>
       </c>
       <c r="AO10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>8</v>
@@ -2444,35 +2444,35 @@
         <v>30</v>
       </c>
       <c r="AY10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
         <v>50</v>
       </c>
       <c r="BD10" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BE10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF10" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
         <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>2.18</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
         <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
         <v>1.39</v>
@@ -2536,16 +2536,16 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
         <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U11" t="n">
         <v>2.26</v>
@@ -2557,7 +2557,7 @@
         <v>1.83</v>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y11" t="n">
         <v>15.5</v>
@@ -2569,7 +2569,7 @@
         <v>70</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
         <v>8.4</v>
@@ -2590,13 +2590,13 @@
         <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
         <v>36</v>
@@ -2605,7 +2605,7 @@
         <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO11" t="n">
         <v>40</v>
@@ -2620,19 +2620,19 @@
         <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
         <v>12.5</v>
@@ -2641,32 +2641,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BB11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
       </c>
       <c r="BD11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE11" t="n">
         <v>28</v>
       </c>
-      <c r="BE11" t="n">
-        <v>24</v>
-      </c>
       <c r="BF11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG11" t="n">
         <v>32</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G12" t="n">
         <v>3.9</v>
@@ -2706,7 +2706,7 @@
         <v>2.24</v>
       </c>
       <c r="I12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
@@ -2721,7 +2721,7 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.43</v>
@@ -2733,16 +2733,16 @@
         <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.98</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.97</v>
       </c>
       <c r="V12" t="n">
         <v>1.79</v>
@@ -2751,7 +2751,7 @@
         <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y12" t="n">
         <v>8.199999999999999</v>
@@ -2775,22 +2775,22 @@
         <v>26</v>
       </c>
       <c r="AF12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG12" t="n">
         <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
         <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="n">
         <v>65</v>
@@ -2799,7 +2799,7 @@
         <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO12" t="n">
         <v>23</v>
@@ -2835,10 +2835,10 @@
         <v>14</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB12" t="n">
         <v>60</v>
@@ -2853,14 +2853,14 @@
         <v>80</v>
       </c>
       <c r="BF12" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BG12" t="n">
         <v>20</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -2897,10 +2897,10 @@
         <v>3.45</v>
       </c>
       <c r="H13" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J13" t="n">
         <v>3.15</v>
@@ -2909,22 +2909,22 @@
         <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P13" t="n">
         <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
@@ -2933,19 +2933,19 @@
         <v>4.9</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
         <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y13" t="n">
         <v>8.4</v>
@@ -2957,7 +2957,7 @@
         <v>36</v>
       </c>
       <c r="AB13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
         <v>7</v>
@@ -2972,7 +2972,7 @@
         <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
@@ -3002,7 +3002,7 @@
         <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR13" t="n">
         <v>13.5</v>
@@ -3014,7 +3014,7 @@
         <v>9.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
         <v>11.5</v>
@@ -3029,10 +3029,10 @@
         <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB13" t="n">
         <v>55</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I14" t="n">
         <v>2.48</v>
       </c>
-      <c r="I14" t="n">
-        <v>2.52</v>
-      </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.45</v>
@@ -3109,16 +3109,16 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
         <v>1.33</v>
@@ -3133,22 +3133,22 @@
         <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
         <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB14" t="n">
         <v>12</v>
@@ -3160,7 +3160,7 @@
         <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF14" t="n">
         <v>21</v>
@@ -3169,28 +3169,28 @@
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM14" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN14" t="n">
         <v>38</v>
       </c>
       <c r="AO14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP14" t="n">
         <v>11.5</v>
@@ -3199,7 +3199,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
         <v>32</v>
@@ -3217,22 +3217,22 @@
         <v>25</v>
       </c>
       <c r="AX14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY14" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BB14" t="n">
         <v>50</v>
       </c>
       <c r="BC14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD14" t="n">
         <v>44</v>
@@ -3244,11 +3244,11 @@
         <v>34</v>
       </c>
       <c r="BG14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I15" t="n">
         <v>3.95</v>
@@ -3306,16 +3306,16 @@
         <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P15" t="n">
         <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
         <v>3.3</v>
@@ -3339,7 +3339,7 @@
         <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA15" t="n">
         <v>75</v>
@@ -3348,7 +3348,7 @@
         <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
         <v>15.5</v>
@@ -3366,16 +3366,16 @@
         <v>17</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
         <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
         <v>90</v>
@@ -3399,7 +3399,7 @@
         <v>60</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU15" t="n">
         <v>7.6</v>
@@ -3417,13 +3417,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA15" t="n">
         <v>48</v>
       </c>
       <c r="BB15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC15" t="n">
         <v>19.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -3479,16 +3479,16 @@
         <v>1.32</v>
       </c>
       <c r="H16" t="n">
+        <v>9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K16" t="n">
         <v>8.6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>11</v>
-      </c>
-      <c r="J16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>1.23</v>
@@ -3512,13 +3512,13 @@
         <v>1.61</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V16" t="n">
         <v>1.1</v>
@@ -3542,10 +3542,10 @@
         <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
@@ -3557,7 +3557,7 @@
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3569,7 +3569,7 @@
         <v>16.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT16" t="n">
         <v>8.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AV16" t="n">
         <v>28</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
         <v>9</v>
       </c>
       <c r="BC16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
         <v>3.95</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -3667,43 +3667,43 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="K17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
         <v>3.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
         <v>1.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
         <v>3.15</v>
@@ -3712,7 +3712,7 @@
         <v>1.69</v>
       </c>
       <c r="U17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V17" t="n">
         <v>1.41</v>
@@ -3742,13 +3742,13 @@
         <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AF17" t="n">
         <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>19.5</v>
@@ -3757,7 +3757,7 @@
         <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
         <v>29</v>
@@ -3766,37 +3766,37 @@
         <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
         <v>980</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS17" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
         <v>14.5</v>
@@ -3808,29 +3808,29 @@
         <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB17" t="n">
         <v>26</v>
       </c>
       <c r="BC17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG17" t="n">
         <v>5.8</v>
       </c>
-      <c r="BD17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -3861,55 +3861,55 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>3.45</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I18" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
         <v>1.41</v>
@@ -3918,113 +3918,113 @@
         <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z18" t="n">
         <v>16.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL18" t="n">
         <v>290</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>55</v>
-      </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AT18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV18" t="n">
         <v>9.6</v>
       </c>
-      <c r="AU18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10</v>
-      </c>
       <c r="AW18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX18" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY18" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG18" t="n">
         <v>20</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G19" t="n">
         <v>2.98</v>
@@ -4091,7 +4091,7 @@
         <v>1.81</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
         <v>3.05</v>
@@ -4118,7 +4118,7 @@
         <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
         <v>1000</v>
@@ -4133,7 +4133,7 @@
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -4145,7 +4145,7 @@
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
         <v>1000</v>
@@ -4154,13 +4154,13 @@
         <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
         <v>14</v>
@@ -4172,7 +4172,7 @@
         <v>9</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
@@ -4187,7 +4187,7 @@
         <v>23</v>
       </c>
       <c r="AX19" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
@@ -4199,7 +4199,7 @@
         <v>30</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC19" t="n">
         <v>14.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
         <v>3.25</v>
@@ -4288,7 +4288,7 @@
         <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T20" t="n">
         <v>1.86</v>
@@ -4312,7 +4312,7 @@
         <v>15.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB20" t="n">
         <v>11.5</v>
@@ -4336,28 +4336,28 @@
         <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>9</v>
@@ -4366,7 +4366,7 @@
         <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
@@ -4381,19 +4381,19 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY20" t="n">
         <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA20" t="n">
         <v>38</v>
       </c>
       <c r="BB20" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BC20" t="n">
         <v>34</v>
@@ -4408,11 +4408,11 @@
         <v>34</v>
       </c>
       <c r="BG20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.24</v>
       </c>
       <c r="G21" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H21" t="n">
         <v>4.2</v>
@@ -4467,58 +4467,58 @@
         <v>1.18</v>
       </c>
       <c r="N21" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="O21" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="P21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R21" t="n">
         <v>1.11</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
         <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X21" t="n">
         <v>6.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z21" t="n">
-        <v>980</v>
+        <v>75</v>
       </c>
       <c r="AA21" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
         <v>23</v>
       </c>
       <c r="AE21" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
         <v>12.5</v>
@@ -4527,10 +4527,10 @@
         <v>14.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AI21" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
         <v>38</v>
@@ -4539,19 +4539,19 @@
         <v>46</v>
       </c>
       <c r="AL21" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AM21" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="AO21" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ21" t="n">
         <v>8</v>
@@ -4560,13 +4560,13 @@
         <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT21" t="n">
         <v>5.1</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
         <v>18.5</v>
@@ -4581,13 +4581,13 @@
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BC21" t="n">
         <v>36</v>
@@ -4596,7 +4596,7 @@
         <v>11</v>
       </c>
       <c r="BE21" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="BF21" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>1.97</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H22" t="n">
         <v>4.8</v>
@@ -4661,7 +4661,7 @@
         <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O22" t="n">
         <v>1.58</v>
@@ -4688,7 +4688,7 @@
         <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X22" t="n">
         <v>9.6</v>
@@ -4700,7 +4700,7 @@
         <v>46</v>
       </c>
       <c r="AA22" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
         <v>6.4</v>
@@ -4712,40 +4712,40 @@
         <v>980</v>
       </c>
       <c r="AE22" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="AH22" t="n">
         <v>980</v>
       </c>
       <c r="AI22" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AJ22" t="n">
-        <v>980</v>
+        <v>140</v>
       </c>
       <c r="AK22" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AL22" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
         <v>980</v>
       </c>
       <c r="AO22" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
         <v>30</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT22" t="n">
         <v>5.7</v>
@@ -4766,7 +4766,7 @@
         <v>18</v>
       </c>
       <c r="AW22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>9.4</v>
@@ -4775,32 +4775,32 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BE22" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BF22" t="n">
         <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -4837,22 +4837,22 @@
         <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="I23" t="n">
         <v>17.5</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K23" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.29</v>
       </c>
       <c r="M23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
         <v>5.2</v>
@@ -4861,22 +4861,22 @@
         <v>1.21</v>
       </c>
       <c r="P23" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R23" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T23" t="n">
         <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V23" t="n">
         <v>1.06</v>
@@ -4885,7 +4885,7 @@
         <v>4.8</v>
       </c>
       <c r="X23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y23" t="n">
         <v>46</v>
@@ -4894,10 +4894,10 @@
         <v>170</v>
       </c>
       <c r="AA23" t="n">
-        <v>980</v>
+        <v>830</v>
       </c>
       <c r="AB23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
         <v>16.5</v>
@@ -4906,7 +4906,7 @@
         <v>60</v>
       </c>
       <c r="AE23" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AF23" t="n">
         <v>7.2</v>
@@ -4918,10 +4918,10 @@
         <v>42</v>
       </c>
       <c r="AI23" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK23" t="n">
         <v>14</v>
@@ -4930,16 +4930,16 @@
         <v>250</v>
       </c>
       <c r="AM23" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AN23" t="n">
         <v>4.4</v>
       </c>
       <c r="AO23" t="n">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ23" t="n">
         <v>36</v>
@@ -4948,19 +4948,19 @@
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
         <v>14.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AW23" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
         <v>6.6</v>
@@ -4969,10 +4969,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BA23" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BB23" t="n">
         <v>8.4</v>
@@ -4987,14 +4987,14 @@
         <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5028,112 +5028,112 @@
         <v>4.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H24" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="I24" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="J24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4</v>
       </c>
       <c r="L24" t="n">
         <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1.95</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V24" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="W24" t="n">
         <v>1.27</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z24" t="n">
         <v>11.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB24" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="n">
         <v>36</v>
       </c>
       <c r="AG24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AK24" t="n">
         <v>65</v>
       </c>
       <c r="AL24" t="n">
-        <v>320</v>
+        <v>70</v>
       </c>
       <c r="AM24" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
         <v>70</v>
       </c>
       <c r="AO24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>8.199999999999999</v>
@@ -5142,53 +5142,53 @@
         <v>10</v>
       </c>
       <c r="AS24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW24" t="n">
         <v>18.5</v>
       </c>
-      <c r="AT24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AX24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB24" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BC24" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BD24" t="n">
-        <v>13.5</v>
+        <v>46</v>
       </c>
       <c r="BE24" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BF24" t="n">
         <v>55</v>
       </c>
       <c r="BG24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5222,13 @@
         <v>1.88</v>
       </c>
       <c r="G25" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H25" t="n">
         <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
         <v>3.9</v>
@@ -5243,10 +5243,10 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P25" t="n">
         <v>2</v>
@@ -5255,13 +5255,13 @@
         <v>1.96</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
         <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U25" t="n">
         <v>2.1</v>
@@ -5270,13 +5270,13 @@
         <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X25" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Y25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z25" t="n">
         <v>34</v>
@@ -5306,7 +5306,7 @@
         <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AJ25" t="n">
         <v>21</v>
@@ -5321,25 +5321,25 @@
         <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO25" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="AP25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ25" t="n">
         <v>14</v>
       </c>
       <c r="AR25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
         <v>8</v>
@@ -5348,7 +5348,7 @@
         <v>15.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -5357,13 +5357,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BB25" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BC25" t="n">
         <v>18</v>
@@ -5372,7 +5372,7 @@
         <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BF25" t="n">
         <v>11.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H26" t="n">
         <v>2.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J26" t="n">
         <v>3.85</v>
@@ -5431,7 +5431,7 @@
         <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
@@ -5443,25 +5443,25 @@
         <v>1.26</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
         <v>1.81</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
         <v>2.96</v>
       </c>
       <c r="T26" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U26" t="n">
         <v>2.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W26" t="n">
         <v>1.36</v>
@@ -5470,19 +5470,19 @@
         <v>19</v>
       </c>
       <c r="Y26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
         <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB26" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
         <v>10.5</v>
@@ -5491,22 +5491,22 @@
         <v>21</v>
       </c>
       <c r="AF26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG26" t="n">
         <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ26" t="n">
         <v>70</v>
       </c>
       <c r="AK26" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL26" t="n">
         <v>48</v>
@@ -5536,7 +5536,7 @@
         <v>14.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV26" t="n">
         <v>10</v>
@@ -5545,16 +5545,16 @@
         <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB26" t="n">
         <v>28</v>
@@ -5563,20 +5563,20 @@
         <v>34</v>
       </c>
       <c r="BD26" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE26" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BF26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG26" t="n">
         <v>12</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5640,13 +5640,13 @@
         <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R27" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S27" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
         <v>1.89</v>
@@ -5661,10 +5661,10 @@
         <v>2.64</v>
       </c>
       <c r="X27" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
@@ -5673,7 +5673,7 @@
         <v>180</v>
       </c>
       <c r="AB27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC27" t="n">
         <v>9.800000000000001</v>
@@ -5682,7 +5682,7 @@
         <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AF27" t="n">
         <v>9.800000000000001</v>
@@ -5691,13 +5691,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK27" t="n">
         <v>16</v>
@@ -5706,10 +5706,10 @@
         <v>32</v>
       </c>
       <c r="AM27" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO27" t="n">
         <v>90</v>
@@ -5736,16 +5736,16 @@
         <v>22</v>
       </c>
       <c r="AW27" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA27" t="n">
         <v>55</v>
@@ -5754,23 +5754,23 @@
         <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE27" t="n">
         <v>60</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>2.7</v>
       </c>
       <c r="G28" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H28" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I28" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>3.5</v>
@@ -5831,10 +5831,10 @@
         <v>1.34</v>
       </c>
       <c r="P28" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R28" t="n">
         <v>1.36</v>
@@ -5858,7 +5858,7 @@
         <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
         <v>18.5</v>
@@ -5870,43 +5870,43 @@
         <v>11.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD28" t="n">
         <v>12.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF28" t="n">
         <v>17.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
         <v>44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK28" t="n">
         <v>30</v>
       </c>
       <c r="AL28" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM28" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP28" t="n">
         <v>12.5</v>
@@ -5918,7 +5918,7 @@
         <v>17</v>
       </c>
       <c r="AS28" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AT28" t="n">
         <v>10.5</v>
@@ -5930,31 +5930,31 @@
         <v>11.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY28" t="n">
         <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BB28" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BC28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD28" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BF28" t="n">
         <v>23</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G29" t="n">
         <v>2.14</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2.16</v>
       </c>
       <c r="H29" t="n">
         <v>3.9</v>
@@ -6007,7 +6007,7 @@
         <v>3.95</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
         <v>3.65</v>
@@ -6034,10 +6034,10 @@
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T29" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U29" t="n">
         <v>2.08</v>
@@ -6046,7 +6046,7 @@
         <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X29" t="n">
         <v>13</v>
@@ -6073,22 +6073,22 @@
         <v>48</v>
       </c>
       <c r="AF29" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG29" t="n">
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI29" t="n">
         <v>60</v>
       </c>
       <c r="AJ29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
         <v>40</v>
@@ -6100,7 +6100,7 @@
         <v>17.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP29" t="n">
         <v>12</v>
@@ -6115,7 +6115,7 @@
         <v>65</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU29" t="n">
         <v>7.4</v>
@@ -6127,7 +6127,7 @@
         <v>42</v>
       </c>
       <c r="AX29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY29" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G30" t="n">
         <v>3.9</v>
       </c>
       <c r="H30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="J30" t="n">
         <v>3.7</v>
       </c>
       <c r="K30" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.41</v>
@@ -6213,16 +6213,16 @@
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O30" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R30" t="n">
         <v>1.34</v>
@@ -6231,13 +6231,13 @@
         <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U30" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V30" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="W30" t="n">
         <v>1.34</v>
@@ -6246,7 +6246,7 @@
         <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z30" t="n">
         <v>13</v>
@@ -6255,7 +6255,7 @@
         <v>27</v>
       </c>
       <c r="AB30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC30" t="n">
         <v>8.199999999999999</v>
@@ -6264,10 +6264,10 @@
         <v>11.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG30" t="n">
         <v>20</v>
@@ -6276,31 +6276,31 @@
         <v>19.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
         <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM30" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AO30" t="n">
         <v>17</v>
       </c>
       <c r="AP30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR30" t="n">
         <v>11</v>
@@ -6309,7 +6309,7 @@
         <v>21</v>
       </c>
       <c r="AT30" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AU30" t="n">
         <v>7.6</v>
@@ -6327,7 +6327,7 @@
         <v>14</v>
       </c>
       <c r="AZ30" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA30" t="n">
         <v>32</v>
@@ -6339,7 +6339,7 @@
         <v>26</v>
       </c>
       <c r="BD30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BE30" t="n">
         <v>40</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="G31" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="H31" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="I31" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="J31" t="n">
         <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L31" t="n">
         <v>1.6</v>
@@ -6407,7 +6407,7 @@
         <v>1.13</v>
       </c>
       <c r="N31" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O31" t="n">
         <v>1.57</v>
@@ -6422,34 +6422,34 @@
         <v>1.17</v>
       </c>
       <c r="S31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V31" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W31" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X31" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC31" t="n">
         <v>7.2</v>
@@ -6458,28 +6458,28 @@
         <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG31" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK31" t="n">
         <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AM31" t="n">
         <v>240</v>
@@ -6494,16 +6494,16 @@
         <v>7.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR31" t="n">
         <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="AT31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU31" t="n">
         <v>6.2</v>
@@ -6512,41 +6512,41 @@
         <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="AX31" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>9.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="BB31" t="n">
         <v>10</v>
       </c>
       <c r="BC31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
       </c>
       <c r="BE31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>3.95</v>
       </c>
       <c r="I32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.05</v>
@@ -6598,19 +6598,19 @@
         <v>1.65</v>
       </c>
       <c r="M32" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N32" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="O32" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="P32" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="R32" t="n">
         <v>1.15</v>
@@ -6619,10 +6619,10 @@
         <v>6.6</v>
       </c>
       <c r="T32" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="U32" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V32" t="n">
         <v>1.31</v>
@@ -6631,25 +6631,25 @@
         <v>1.75</v>
       </c>
       <c r="X32" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y32" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA32" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
@@ -6658,25 +6658,25 @@
         <v>12</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH32" t="n">
         <v>50</v>
       </c>
       <c r="AI32" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ32" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL32" t="n">
         <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AN32" t="n">
         <v>1000</v>
@@ -6685,10 +6685,10 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ32" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR32" t="n">
         <v>17.5</v>
@@ -6697,13 +6697,13 @@
         <v>36</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU32" t="n">
         <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW32" t="n">
         <v>48</v>
@@ -6712,25 +6712,25 @@
         <v>11</v>
       </c>
       <c r="AY32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA32" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB32" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BC32" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BD32" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BE32" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF32" t="n">
         <v>23</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -6774,73 +6774,73 @@
         <v>3.25</v>
       </c>
       <c r="G33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H33" t="n">
         <v>2.4</v>
       </c>
       <c r="I33" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K33" t="n">
         <v>3.55</v>
       </c>
-      <c r="K33" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L33" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R33" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T33" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U33" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W33" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X33" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
         <v>34</v>
       </c>
       <c r="AB33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD33" t="n">
         <v>11.5</v>
@@ -6852,7 +6852,7 @@
         <v>23</v>
       </c>
       <c r="AG33" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH33" t="n">
         <v>17</v>
@@ -6861,10 +6861,10 @@
         <v>38</v>
       </c>
       <c r="AJ33" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL33" t="n">
         <v>48</v>
@@ -6873,22 +6873,22 @@
         <v>90</v>
       </c>
       <c r="AN33" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AO33" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AP33" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ33" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR33" t="n">
         <v>14</v>
       </c>
       <c r="AS33" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AT33" t="n">
         <v>12</v>
@@ -6900,7 +6900,7 @@
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX33" t="n">
         <v>20</v>
@@ -6909,32 +6909,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB33" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BC33" t="n">
         <v>32</v>
       </c>
       <c r="BD33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE33" t="n">
         <v>44</v>
       </c>
       <c r="BF33" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BG33" t="n">
         <v>17</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G34" t="n">
         <v>1.45</v>
@@ -6989,16 +6989,16 @@
         <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O34" t="n">
         <v>1.29</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R34" t="n">
         <v>1.41</v>
@@ -7010,22 +7010,22 @@
         <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V34" t="n">
         <v>1.1</v>
       </c>
       <c r="W34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y34" t="n">
         <v>32</v>
       </c>
       <c r="Z34" t="n">
-        <v>90</v>
+        <v>540</v>
       </c>
       <c r="AA34" t="n">
         <v>410</v>
@@ -7037,7 +7037,7 @@
         <v>11.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AE34" t="n">
         <v>190</v>
@@ -7052,7 +7052,7 @@
         <v>29</v>
       </c>
       <c r="AI34" t="n">
-        <v>160</v>
+        <v>470</v>
       </c>
       <c r="AJ34" t="n">
         <v>12.5</v>
@@ -7061,7 +7061,7 @@
         <v>17</v>
       </c>
       <c r="AL34" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AM34" t="n">
         <v>190</v>
@@ -7079,10 +7079,10 @@
         <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS34" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT34" t="n">
         <v>6.8</v>
@@ -7094,7 +7094,7 @@
         <v>17</v>
       </c>
       <c r="AW34" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX34" t="n">
         <v>7.2</v>
@@ -7103,10 +7103,10 @@
         <v>9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA34" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB34" t="n">
         <v>10</v>
@@ -7115,20 +7115,20 @@
         <v>14</v>
       </c>
       <c r="BD34" t="n">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BE34" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BF34" t="n">
         <v>6.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -7162,16 +7162,16 @@
         <v>3.35</v>
       </c>
       <c r="G35" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H35" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I35" t="n">
         <v>2.7</v>
       </c>
       <c r="J35" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K35" t="n">
         <v>3.05</v>
@@ -7189,13 +7189,13 @@
         <v>1.7</v>
       </c>
       <c r="P35" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q35" t="n">
         <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S35" t="n">
         <v>6.8</v>
@@ -7210,7 +7210,7 @@
         <v>1.58</v>
       </c>
       <c r="W35" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X35" t="n">
         <v>7.4</v>
@@ -7273,7 +7273,7 @@
         <v>6</v>
       </c>
       <c r="AR35" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS35" t="n">
         <v>34</v>
@@ -7297,7 +7297,7 @@
         <v>14.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BA35" t="n">
         <v>9.6</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G36" t="n">
         <v>2.12</v>
@@ -7380,37 +7380,37 @@
         <v>3.55</v>
       </c>
       <c r="O36" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W36" t="n">
         <v>1.89</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.9</v>
       </c>
       <c r="X36" t="n">
         <v>16</v>
       </c>
       <c r="Y36" t="n">
-        <v>980</v>
+        <v>13.5</v>
       </c>
       <c r="Z36" t="n">
         <v>980</v>
@@ -7467,10 +7467,10 @@
         <v>12</v>
       </c>
       <c r="AR36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT36" t="n">
         <v>8</v>
@@ -7482,13 +7482,13 @@
         <v>14.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AX36" t="n">
         <v>11</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ36" t="n">
         <v>17</v>
@@ -7497,26 +7497,26 @@
         <v>11</v>
       </c>
       <c r="BB36" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC36" t="n">
         <v>20</v>
       </c>
-      <c r="BC36" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD36" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BE36" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF36" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -763,16 +763,16 @@
         <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
         <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>1.36</v>
@@ -787,10 +787,10 @@
         <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -802,10 +802,10 @@
         <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
         <v>1.98</v>
@@ -814,10 +814,10 @@
         <v>30</v>
       </c>
       <c r="Y2" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
@@ -829,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
@@ -841,25 +841,25 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
@@ -868,25 +868,25 @@
         <v>8.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS2" t="n">
         <v>8.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -895,22 +895,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="BA2" t="n">
         <v>44</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
         <v>10.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -978,13 +978,13 @@
         <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
         <v>1.43</v>
@@ -996,19 +996,19 @@
         <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Z3" t="n">
         <v>65</v>
@@ -1023,13 +1023,13 @@
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1053,13 +1053,13 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>18.5</v>
@@ -1068,53 +1068,53 @@
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
         <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="AX3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
         <v>14</v>
       </c>
       <c r="BD3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE3" t="n">
         <v>6.4</v>
       </c>
-      <c r="BE3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
         <v>2.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.41</v>
@@ -1169,34 +1169,34 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
         <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
         <v>1.98</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
         <v>3.55</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V4" t="n">
         <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
@@ -1229,13 +1229,13 @@
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK4" t="n">
         <v>42</v>
@@ -1247,16 +1247,16 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR4" t="n">
         <v>13</v>
@@ -1289,26 +1289,26 @@
         <v>6.6</v>
       </c>
       <c r="BB4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
         <v>19.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -1351,13 +1351,13 @@
         <v>1.98</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1369,7 +1369,7 @@
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
         <v>1.77</v>
@@ -1378,7 +1378,7 @@
         <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
         <v>1.71</v>
@@ -1393,116 +1393,116 @@
         <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AB5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE5" t="n">
         <v>20</v>
       </c>
-      <c r="AC5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>23</v>
-      </c>
       <c r="AF5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL5" t="n">
         <v>55</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>120</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO5" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AS5" t="n">
-        <v>3.9</v>
+        <v>18.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.55</v>
+        <v>14.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.35</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.65</v>
+        <v>16.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.9</v>
+        <v>14.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.8</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>40</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.1</v>
+        <v>38</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.2</v>
+        <v>9.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
         <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>1000</v>
@@ -1641,13 +1641,13 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.35</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS6" t="n">
         <v>1.38</v>
@@ -1656,7 +1656,7 @@
         <v>1.36</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AV6" t="n">
         <v>1.34</v>
@@ -1668,7 +1668,7 @@
         <v>1.37</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.31</v>
@@ -1683,7 +1683,7 @@
         <v>1.38</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BE6" t="n">
         <v>1.38</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>1.49</v>
       </c>
       <c r="H7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
         <v>11.5</v>
@@ -1751,7 +1751,7 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.26</v>
@@ -1772,7 +1772,7 @@
         <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -1784,7 +1784,7 @@
         <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1805,13 +1805,13 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AG7" t="n">
         <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,22 +1838,22 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AU7" t="n">
         <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW7" t="n">
         <v>5.1</v>
@@ -1862,35 +1862,35 @@
         <v>4.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
         <v>5.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
         <v>2.74</v>
@@ -1975,16 +1975,16 @@
         <v>1.54</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
         <v>18.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AB8" t="n">
         <v>12</v>
@@ -2005,13 +2005,13 @@
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AI8" t="n">
         <v>40</v>
       </c>
       <c r="AJ8" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
         <v>30</v>
@@ -2023,13 +2023,13 @@
         <v>90</v>
       </c>
       <c r="AN8" t="n">
-        <v>980</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
         <v>25</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
@@ -2038,10 +2038,10 @@
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="AT8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -2050,41 +2050,41 @@
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="AX8" t="n">
         <v>16.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="BC8" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BD8" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>16.5</v>
+        <v>44</v>
       </c>
       <c r="BF8" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I9" t="n">
         <v>2.28</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
         <v>3.55</v>
@@ -2157,19 +2157,19 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W9" t="n">
         <v>1.37</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
         <v>9</v>
@@ -2226,10 +2226,10 @@
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
         <v>27</v>
@@ -2253,32 +2253,32 @@
         <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
         <v>38</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="BD9" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="BE9" t="n">
         <v>60</v>
       </c>
       <c r="BF9" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="BG9" t="n">
         <v>20</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G10" t="n">
         <v>4.6</v>
       </c>
-      <c r="G10" t="n">
-        <v>4.8</v>
-      </c>
       <c r="H10" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
@@ -2342,7 +2342,7 @@
         <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
         <v>1.37</v>
@@ -2354,31 +2354,31 @@
         <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
         <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB10" t="n">
         <v>17</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
         <v>10.5</v>
@@ -2387,13 +2387,13 @@
         <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG10" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AI10" t="n">
         <v>34</v>
@@ -2411,49 +2411,49 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AO10" t="n">
         <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
         <v>14</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AX10" t="n">
         <v>30</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC10" t="n">
         <v>50</v>
@@ -2462,17 +2462,17 @@
         <v>28</v>
       </c>
       <c r="BE10" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BF10" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G11" t="n">
         <v>2.18</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.22</v>
-      </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J11" t="n">
         <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>1.39</v>
@@ -2527,43 +2527,43 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
         <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA11" t="n">
         <v>70</v>
@@ -2572,7 +2572,7 @@
         <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
         <v>15</v>
@@ -2584,7 +2584,7 @@
         <v>14.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
         <v>17.5</v>
@@ -2605,25 +2605,25 @@
         <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU11" t="n">
         <v>7.6</v>
@@ -2632,7 +2632,7 @@
         <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AX11" t="n">
         <v>12.5</v>
@@ -2644,16 +2644,16 @@
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE11" t="n">
         <v>28</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -2739,10 +2739,10 @@
         <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V12" t="n">
         <v>1.79</v>
@@ -2772,7 +2772,7 @@
         <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF12" t="n">
         <v>25</v>
@@ -2784,7 +2784,7 @@
         <v>19.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ12" t="n">
         <v>75</v>
@@ -2832,7 +2832,7 @@
         <v>24</v>
       </c>
       <c r="AY12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ12" t="n">
         <v>17.5</v>
@@ -2844,7 +2844,7 @@
         <v>60</v>
       </c>
       <c r="BC12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BD12" t="n">
         <v>55</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
         <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
@@ -2918,13 +2918,13 @@
         <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
@@ -2939,13 +2939,13 @@
         <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W13" t="n">
         <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
         <v>8.4</v>
@@ -3017,7 +3017,7 @@
         <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
         <v>30</v>
@@ -3029,10 +3029,10 @@
         <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB13" t="n">
         <v>55</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -3109,16 +3109,16 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
         <v>1.33</v>
@@ -3187,7 +3187,7 @@
         <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO14" t="n">
         <v>23</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -3285,16 +3285,16 @@
         <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.41</v>
@@ -3327,7 +3327,7 @@
         <v>2.22</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
         <v>1.89</v>
@@ -3345,10 +3345,10 @@
         <v>75</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD15" t="n">
         <v>15.5</v>
@@ -3390,7 +3390,7 @@
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3411,13 +3411,13 @@
         <v>40</v>
       </c>
       <c r="AX15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
         <v>48</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
         <v>2.32</v>
       </c>
       <c r="T16" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U16" t="n">
         <v>1.84</v>
@@ -3527,7 +3527,7 @@
         <v>4.1</v>
       </c>
       <c r="X16" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
         <v>44</v>
@@ -3584,13 +3584,13 @@
         <v>5.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT16" t="n">
         <v>8.6</v>
@@ -3602,7 +3602,7 @@
         <v>28</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
@@ -3611,10 +3611,10 @@
         <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
         <v>9</v>
@@ -3623,20 +3623,20 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
         <v>3.95</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -3679,28 +3679,28 @@
         <v>3.45</v>
       </c>
       <c r="J17" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>3.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
         <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R17" t="n">
         <v>1.38</v>
@@ -3709,16 +3709,16 @@
         <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V17" t="n">
         <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X17" t="n">
         <v>16.5</v>
@@ -3736,7 +3736,7 @@
         <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
         <v>15.5</v>
@@ -3748,13 +3748,13 @@
         <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
         <v>19.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ17" t="n">
         <v>900</v>
@@ -3763,13 +3763,13 @@
         <v>29</v>
       </c>
       <c r="AL17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
         <v>980</v>
@@ -3778,59 +3778,59 @@
         <v>12.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
         <v>17</v>
       </c>
       <c r="AS17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY17" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
         <v>26</v>
       </c>
       <c r="BC17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF17" t="n">
         <v>6</v>
       </c>
-      <c r="BD17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE17" t="n">
+      <c r="BG17" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>3.45</v>
       </c>
       <c r="H18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I18" t="n">
         <v>2.6</v>
@@ -3876,10 +3876,10 @@
         <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -3900,16 +3900,16 @@
         <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T18" t="n">
         <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
         <v>1.41</v>
@@ -3951,7 +3951,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="n">
-        <v>130</v>
+        <v>320</v>
       </c>
       <c r="AK18" t="n">
         <v>95</v>
@@ -3969,16 +3969,16 @@
         <v>24</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
         <v>10.5</v>
@@ -4002,10 +4002,10 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
         <v>18</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
         <v>2.5</v>
       </c>
       <c r="I19" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
         <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -4091,10 +4091,10 @@
         <v>1.81</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
         <v>1.64</v>
@@ -4103,10 +4103,10 @@
         <v>2.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
         <v>26</v>
@@ -4130,10 +4130,10 @@
         <v>18</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -4172,7 +4172,7 @@
         <v>9</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
@@ -4187,7 +4187,7 @@
         <v>23</v>
       </c>
       <c r="AX19" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
@@ -4199,7 +4199,7 @@
         <v>30</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC19" t="n">
         <v>14.5</v>
@@ -4208,17 +4208,17 @@
         <v>18</v>
       </c>
       <c r="BE19" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG19" t="n">
         <v>16.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
         <v>2.46</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J20" t="n">
         <v>3.45</v>
@@ -4267,7 +4267,7 @@
         <v>3.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
@@ -4291,16 +4291,16 @@
         <v>3.95</v>
       </c>
       <c r="T20" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U20" t="n">
         <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
         <v>12</v>
@@ -4309,7 +4309,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="n">
         <v>34</v>
@@ -4339,7 +4339,7 @@
         <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="n">
         <v>38</v>
@@ -4354,7 +4354,7 @@
         <v>38</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
         <v>11.5</v>
@@ -4384,7 +4384,7 @@
         <v>19.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>16.5</v>
@@ -4393,7 +4393,7 @@
         <v>38</v>
       </c>
       <c r="BB20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC20" t="n">
         <v>34</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G21" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
         <v>4.7</v>
@@ -4467,73 +4467,73 @@
         <v>1.18</v>
       </c>
       <c r="N21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O21" t="n">
         <v>1.84</v>
       </c>
       <c r="P21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="R21" t="n">
         <v>1.11</v>
       </c>
       <c r="S21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="T21" t="n">
         <v>2.66</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
         <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X21" t="n">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AA21" t="n">
         <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
         <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AI21" t="n">
         <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AK21" t="n">
         <v>46</v>
@@ -4551,62 +4551,62 @@
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR21" t="n">
         <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.1</v>
+        <v>3.25</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
         <v>18.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BA21" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BF21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BG21" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R22" t="n">
         <v>1.17</v>
@@ -4748,10 +4748,10 @@
         <v>7.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="AS22" t="n">
         <v>10.5</v>
@@ -4763,7 +4763,7 @@
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AW22" t="n">
         <v>10</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -4837,16 +4837,16 @@
         <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
         <v>7.2</v>
       </c>
       <c r="K23" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.29</v>
@@ -4858,10 +4858,10 @@
         <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
         <v>1.66</v>
@@ -4900,13 +4900,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD23" t="n">
         <v>60</v>
       </c>
       <c r="AE23" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AF23" t="n">
         <v>7.2</v>
@@ -4927,31 +4927,31 @@
         <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="AM23" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN23" t="n">
         <v>4.4</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AP23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR23" t="n">
         <v>36</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>19</v>
       </c>
       <c r="AS23" t="n">
         <v>21</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU23" t="n">
         <v>14.5</v>
@@ -4969,7 +4969,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BA23" t="n">
         <v>19.5</v>
@@ -4981,20 +4981,20 @@
         <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE23" t="n">
         <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG23" t="n">
         <v>19.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G24" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I24" t="n">
         <v>1.88</v>
       </c>
-      <c r="I24" t="n">
-        <v>1.91</v>
-      </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
         <v>1.39</v>
@@ -5055,7 +5055,7 @@
         <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
         <v>1.99</v>
@@ -5067,16 +5067,16 @@
         <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -5085,7 +5085,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA24" t="n">
         <v>21</v>
@@ -5094,40 +5094,40 @@
         <v>16.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="n">
         <v>36</v>
       </c>
       <c r="AG24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AK24" t="n">
         <v>65</v>
       </c>
       <c r="AL24" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM24" t="n">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN24" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO24" t="n">
         <v>13.5</v>
@@ -5136,31 +5136,31 @@
         <v>12.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AR24" t="n">
         <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW24" t="n">
         <v>18.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ24" t="n">
         <v>18</v>
@@ -5169,26 +5169,26 @@
         <v>32</v>
       </c>
       <c r="BB24" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BC24" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BD24" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE24" t="n">
         <v>50</v>
       </c>
       <c r="BF24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BG24" t="n">
         <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -5219,76 +5219,76 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="G25" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="H25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I25" t="n">
         <v>4.5</v>
       </c>
-      <c r="I25" t="n">
-        <v>4.6</v>
-      </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="O25" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X25" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA25" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
         <v>17.5</v>
@@ -5303,52 +5303,52 @@
         <v>10</v>
       </c>
       <c r="AH25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK25" t="n">
         <v>21</v>
       </c>
-      <c r="AI25" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AL25" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
-        <v>110</v>
+        <v>390</v>
       </c>
       <c r="AN25" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="AP25" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV25" t="n">
         <v>15.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -5357,22 +5357,22 @@
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC25" t="n">
         <v>18.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>18</v>
       </c>
       <c r="BD25" t="n">
         <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BF25" t="n">
         <v>11.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -5425,13 +5425,13 @@
         <v>2.12</v>
       </c>
       <c r="J26" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K26" t="n">
         <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
@@ -5452,7 +5452,7 @@
         <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T26" t="n">
         <v>1.69</v>
@@ -5464,10 +5464,10 @@
         <v>1.89</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y26" t="n">
         <v>11</v>
@@ -5491,7 +5491,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="AG26" t="n">
         <v>15</v>
@@ -5515,7 +5515,7 @@
         <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AO26" t="n">
         <v>13</v>
@@ -5536,7 +5536,7 @@
         <v>14.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV26" t="n">
         <v>10</v>
@@ -5572,11 +5572,11 @@
         <v>30</v>
       </c>
       <c r="BG26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G27" t="n">
         <v>1.6</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.61</v>
       </c>
       <c r="H27" t="n">
         <v>6.4</v>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K27" t="n">
         <v>4.6</v>
@@ -5655,16 +5655,16 @@
         <v>2.06</v>
       </c>
       <c r="V27" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W27" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="X27" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
@@ -5673,16 +5673,16 @@
         <v>180</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
         <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
         <v>9.800000000000001</v>
@@ -5697,10 +5697,10 @@
         <v>75</v>
       </c>
       <c r="AJ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK27" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>32</v>
@@ -5730,7 +5730,7 @@
         <v>8.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV27" t="n">
         <v>22</v>
@@ -5745,10 +5745,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5760,17 +5760,17 @@
         <v>30</v>
       </c>
       <c r="BE27" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BF27" t="n">
         <v>7.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G28" t="n">
         <v>2.76</v>
@@ -5810,7 +5810,7 @@
         <v>2.84</v>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J28" t="n">
         <v>3.5</v>
@@ -5840,7 +5840,7 @@
         <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T28" t="n">
         <v>1.79</v>
@@ -5858,7 +5858,7 @@
         <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z28" t="n">
         <v>18.5</v>
@@ -5867,7 +5867,7 @@
         <v>44</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC28" t="n">
         <v>7.6</v>
@@ -5894,7 +5894,7 @@
         <v>40</v>
       </c>
       <c r="AK28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL28" t="n">
         <v>42</v>
@@ -5918,7 +5918,7 @@
         <v>17</v>
       </c>
       <c r="AS28" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT28" t="n">
         <v>10.5</v>
@@ -5930,7 +5930,7 @@
         <v>11.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX28" t="n">
         <v>16.5</v>
@@ -5942,16 +5942,16 @@
         <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB28" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BC28" t="n">
         <v>27</v>
       </c>
       <c r="BD28" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BE28" t="n">
         <v>70</v>
@@ -5960,11 +5960,11 @@
         <v>23</v>
       </c>
       <c r="BG28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G29" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H29" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I29" t="n">
         <v>3.95</v>
@@ -6037,16 +6037,16 @@
         <v>3.8</v>
       </c>
       <c r="T29" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U29" t="n">
         <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W29" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X29" t="n">
         <v>13</v>
@@ -6070,7 +6070,7 @@
         <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF29" t="n">
         <v>12.5</v>
@@ -6079,7 +6079,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI29" t="n">
         <v>60</v>
@@ -6091,7 +6091,7 @@
         <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -6136,7 +6136,7 @@
         <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB29" t="n">
         <v>24</v>
@@ -6154,11 +6154,11 @@
         <v>16</v>
       </c>
       <c r="BG29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H30" t="n">
         <v>2.08</v>
       </c>
       <c r="I30" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J30" t="n">
         <v>3.7</v>
@@ -6207,43 +6207,43 @@
         <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V30" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.88</v>
-      </c>
       <c r="W30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y30" t="n">
         <v>8.800000000000001</v>
@@ -6267,10 +6267,10 @@
         <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH30" t="n">
         <v>19.5</v>
@@ -6291,16 +6291,16 @@
         <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR30" t="n">
         <v>11</v>
@@ -6309,22 +6309,22 @@
         <v>21</v>
       </c>
       <c r="AT30" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU30" t="n">
         <v>7.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW30" t="n">
         <v>19.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY30" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ30" t="n">
         <v>17.5</v>
@@ -6336,23 +6336,23 @@
         <v>34</v>
       </c>
       <c r="BC30" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BD30" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BE30" t="n">
         <v>40</v>
       </c>
       <c r="BF30" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BG30" t="n">
         <v>15</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -6386,37 +6386,37 @@
         <v>3.55</v>
       </c>
       <c r="G31" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="I31" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L31" t="n">
         <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O31" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="P31" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R31" t="n">
         <v>1.17</v>
@@ -6425,31 +6425,31 @@
         <v>6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U31" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X31" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AB31" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC31" t="n">
         <v>7.2</v>
@@ -6458,19 +6458,19 @@
         <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF31" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AG31" t="n">
         <v>17</v>
       </c>
       <c r="AH31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ31" t="n">
         <v>900</v>
@@ -6482,71 +6482,71 @@
         <v>540</v>
       </c>
       <c r="AM31" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN31" t="n">
         <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP31" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
         <v>29</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU31" t="n">
         <v>6.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AX31" t="n">
         <v>21</v>
       </c>
       <c r="AY31" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="BC31" t="n">
-        <v>9.6</v>
+        <v>44</v>
       </c>
       <c r="BD31" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BE31" t="n">
-        <v>10.5</v>
+        <v>70</v>
       </c>
       <c r="BF31" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BG31" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
         <v>2.38</v>
       </c>
       <c r="O32" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P32" t="n">
         <v>1.45</v>
@@ -6661,7 +6661,7 @@
         <v>13</v>
       </c>
       <c r="AH32" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AI32" t="n">
         <v>500</v>
@@ -6727,10 +6727,10 @@
         <v>30</v>
       </c>
       <c r="BD32" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BE32" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BF32" t="n">
         <v>23</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G33" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H33" t="n">
         <v>2.4</v>
@@ -6804,7 +6804,7 @@
         <v>1.96</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R33" t="n">
         <v>1.38</v>
@@ -6822,7 +6822,7 @@
         <v>1.69</v>
       </c>
       <c r="W33" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X33" t="n">
         <v>14</v>
@@ -6840,19 +6840,19 @@
         <v>13.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD33" t="n">
         <v>11.5</v>
       </c>
       <c r="AE33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF33" t="n">
         <v>25</v>
       </c>
-      <c r="AF33" t="n">
-        <v>23</v>
-      </c>
       <c r="AG33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH33" t="n">
         <v>17</v>
@@ -6873,10 +6873,10 @@
         <v>90</v>
       </c>
       <c r="AN33" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AO33" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP33" t="n">
         <v>13</v>
@@ -6906,10 +6906,10 @@
         <v>20</v>
       </c>
       <c r="AY33" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA33" t="n">
         <v>34</v>
@@ -6921,20 +6921,20 @@
         <v>32</v>
       </c>
       <c r="BD33" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE33" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BF33" t="n">
         <v>30</v>
       </c>
       <c r="BG33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>1.42</v>
       </c>
       <c r="G34" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H34" t="n">
         <v>9.199999999999999</v>
@@ -6983,7 +6983,7 @@
         <v>5.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M34" t="n">
         <v>1.06</v>
@@ -6998,13 +6998,13 @@
         <v>2.08</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R34" t="n">
         <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T34" t="n">
         <v>2.1</v>
@@ -7013,13 +7013,13 @@
         <v>1.81</v>
       </c>
       <c r="V34" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W34" t="n">
         <v>3.25</v>
       </c>
       <c r="X34" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y34" t="n">
         <v>32</v>
@@ -7028,22 +7028,22 @@
         <v>540</v>
       </c>
       <c r="AA34" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AB34" t="n">
         <v>8</v>
       </c>
       <c r="AC34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD34" t="n">
         <v>36</v>
       </c>
       <c r="AE34" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF34" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG34" t="n">
         <v>10.5</v>
@@ -7055,58 +7055,58 @@
         <v>470</v>
       </c>
       <c r="AJ34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL34" t="n">
         <v>42</v>
       </c>
       <c r="AM34" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN34" t="n">
         <v>7.2</v>
       </c>
       <c r="AO34" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AP34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ34" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AR34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU34" t="n">
         <v>10</v>
       </c>
-      <c r="AS34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AV34" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AW34" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AX34" t="n">
         <v>7.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ34" t="n">
         <v>24</v>
       </c>
       <c r="BA34" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BB34" t="n">
         <v>10</v>
@@ -7118,17 +7118,17 @@
         <v>34</v>
       </c>
       <c r="BE34" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG34" t="n">
         <v>15</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -7165,13 +7165,13 @@
         <v>3.65</v>
       </c>
       <c r="H35" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I35" t="n">
         <v>2.7</v>
       </c>
       <c r="J35" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K35" t="n">
         <v>3.05</v>
@@ -7183,13 +7183,13 @@
         <v>1.16</v>
       </c>
       <c r="N35" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O35" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="P35" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q35" t="n">
         <v>3.1</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G36" t="n">
         <v>2.12</v>
       </c>
       <c r="H36" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I36" t="n">
         <v>4.1</v>
@@ -7368,10 +7368,10 @@
         <v>3.65</v>
       </c>
       <c r="K36" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L36" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
@@ -7404,7 +7404,7 @@
         <v>1.33</v>
       </c>
       <c r="W36" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X36" t="n">
         <v>16</v>
@@ -7440,7 +7440,7 @@
         <v>980</v>
       </c>
       <c r="AI36" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ36" t="n">
         <v>980</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 21:59:15</t>
+          <t>2026-03-12 00:17:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -760,13 +760,13 @@
         <v>1.96</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
@@ -775,49 +775,49 @@
         <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y2" t="n">
         <v>30</v>
       </c>
-      <c r="Y2" t="n">
-        <v>32</v>
-      </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
@@ -829,19 +829,19 @@
         <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
@@ -859,13 +859,13 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
@@ -874,25 +874,25 @@
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
         <v>7.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>24</v>
+        <v>9.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>7.6</v>
@@ -901,7 +901,7 @@
         <v>44</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
         <v>8.4</v>
@@ -910,17 +910,17 @@
         <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
         <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG3" t="n">
         <v>11</v>
       </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
         <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AP3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>18.5</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG3" t="n">
         <v>13.5</v>
       </c>
-      <c r="BC3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.35</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.55</v>
-      </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AK4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4" t="n">
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
         <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY4" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H5" t="n">
         <v>1.9</v>
@@ -1351,28 +1351,28 @@
         <v>1.98</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R5" t="n">
         <v>1.43</v>
@@ -1381,19 +1381,19 @@
         <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
         <v>2.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
         <v>11</v>
@@ -1429,19 +1429,19 @@
         <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AK5" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1471,38 +1471,38 @@
         <v>16.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY5" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA5" t="n">
         <v>15</v>
       </c>
-      <c r="BA5" t="n">
-        <v>14</v>
-      </c>
       <c r="BB5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF5" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>38</v>
       </c>
       <c r="BG5" t="n">
         <v>9.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1533,79 +1533,79 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>6.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>2.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.77</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1614,16 +1614,16 @@
         <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1632,71 +1632,71 @@
         <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.36</v>
+        <v>3.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.35</v>
+        <v>2.42</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.37</v>
+        <v>2.68</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.38</v>
+        <v>3.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.36</v>
+        <v>2.68</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.27</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.36</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.37</v>
+        <v>2.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.37</v>
+        <v>2.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.31</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.38</v>
+        <v>2.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.38</v>
+        <v>2.68</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.38</v>
+        <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.39</v>
+        <v>2.56</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.38</v>
+        <v>2.66</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.55</v>
+        <v>2.64</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="G7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I7" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,25 +1793,25 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>30</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,59 +1838,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU7" t="n">
         <v>5.8</v>
       </c>
       <c r="AV7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY7" t="n">
         <v>5.8</v>
       </c>
-      <c r="AW7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
         <v>6.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BE7" t="n">
         <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
         <v>3.55</v>
@@ -1939,19 +1939,19 @@
         <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
         <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
@@ -1960,7 +1960,7 @@
         <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
         <v>1.76</v>
@@ -1969,25 +1969,25 @@
         <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
         <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
         <v>7.8</v>
@@ -1999,22 +1999,22 @@
         <v>32</v>
       </c>
       <c r="AF8" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>17</v>
       </c>
       <c r="AI8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>40</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>44</v>
-      </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
         <v>40</v>
@@ -2023,28 +2023,28 @@
         <v>90</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
         <v>11.5</v>
@@ -2053,25 +2053,25 @@
         <v>27</v>
       </c>
       <c r="AX8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE8" t="n">
         <v>44</v>
@@ -2080,11 +2080,11 @@
         <v>22</v>
       </c>
       <c r="BG8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2115,76 +2115,76 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="G9" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="H9" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="I9" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
         <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="T9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.92</v>
       </c>
-      <c r="U9" t="n">
-        <v>2.02</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
         <v>11.5</v>
@@ -2193,92 +2193,92 @@
         <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG9" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL9" t="n">
         <v>75</v>
       </c>
-      <c r="AK9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>60</v>
-      </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR9" t="n">
         <v>11</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AS9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
         <v>10</v>
       </c>
       <c r="AW9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB9" t="n">
         <v>23</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BC9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BG9" t="n">
         <v>21</v>
       </c>
-      <c r="AY9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>20</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2327,31 +2327,31 @@
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
         <v>2.12</v>
@@ -2381,10 +2381,10 @@
         <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF10" t="n">
         <v>34</v>
@@ -2408,16 +2408,16 @@
         <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.4</v>
@@ -2426,7 +2426,7 @@
         <v>10.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT10" t="n">
         <v>14</v>
@@ -2447,32 +2447,32 @@
         <v>16.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BC10" t="n">
         <v>50</v>
       </c>
       <c r="BD10" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BE10" t="n">
         <v>50</v>
       </c>
       <c r="BF10" t="n">
-        <v>17.5</v>
+        <v>50</v>
       </c>
       <c r="BG10" t="n">
         <v>11.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2503,85 +2503,85 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="H11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.65</v>
       </c>
       <c r="K11" t="n">
         <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
         <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P11" t="n">
         <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
         <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AB11" t="n">
         <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -2590,83 +2590,83 @@
         <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AS11" t="n">
         <v>60</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BB11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD11" t="n">
         <v>29</v>
       </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BF11" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2697,55 +2697,55 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G12" t="n">
         <v>3.9</v>
       </c>
       <c r="H12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I12" t="n">
         <v>2.24</v>
       </c>
-      <c r="I12" t="n">
-        <v>2.26</v>
-      </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W12" t="n">
         <v>1.34</v>
@@ -2754,16 +2754,16 @@
         <v>11.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
         <v>28</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
         <v>7.4</v>
@@ -2772,16 +2772,16 @@
         <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF12" t="n">
         <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>44</v>
@@ -2793,22 +2793,22 @@
         <v>50</v>
       </c>
       <c r="AL12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
         <v>60</v>
       </c>
       <c r="AO12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR12" t="n">
         <v>11.5</v>
@@ -2817,50 +2817,50 @@
         <v>26</v>
       </c>
       <c r="AT12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BC12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BD12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BG12" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2915,10 +2915,10 @@
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P13" t="n">
         <v>1.65</v>
@@ -2939,25 +2939,25 @@
         <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z13" t="n">
         <v>14.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>7</v>
@@ -2990,7 +2990,7 @@
         <v>65</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>440</v>
       </c>
       <c r="AN13" t="n">
         <v>60</v>
@@ -3002,7 +3002,7 @@
         <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR13" t="n">
         <v>13.5</v>
@@ -3032,7 +3032,7 @@
         <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB13" t="n">
         <v>55</v>
@@ -3044,7 +3044,7 @@
         <v>55</v>
       </c>
       <c r="BE13" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="BF13" t="n">
         <v>50</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3085,127 +3085,127 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H14" t="n">
         <v>2.46</v>
       </c>
       <c r="I14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.45</v>
       </c>
-      <c r="K14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
         <v>1.67</v>
       </c>
       <c r="W14" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA14" t="n">
         <v>34</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
         <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AF14" t="n">
         <v>21</v>
       </c>
       <c r="AG14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR14" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>14</v>
       </c>
       <c r="AS14" t="n">
         <v>32</v>
       </c>
       <c r="AT14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU14" t="n">
         <v>7.2</v>
@@ -3214,41 +3214,41 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX14" t="n">
         <v>20</v>
       </c>
       <c r="AY14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD14" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BE14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="BF14" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BG14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z15" t="n">
         <v>27</v>
       </c>
       <c r="AA15" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
         <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC15" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BE15" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="BF15" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BG15" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3473,64 +3473,64 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="G16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>11.5</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="K16" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R16" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="V16" t="n">
         <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="X16" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1000</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>44</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,10 +3539,10 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AD16" t="n">
         <v>38</v>
@@ -3551,92 +3551,92 @@
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AK16" t="n">
         <v>16.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV16" t="n">
         <v>6</v>
       </c>
-      <c r="AS16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>28</v>
-      </c>
       <c r="AW16" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC16" t="n">
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3667,58 +3667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G17" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I17" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="R17" t="n">
         <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
         <v>1.65</v>
       </c>
       <c r="U17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X17" t="n">
         <v>16.5</v>
@@ -3733,7 +3733,7 @@
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC17" t="n">
         <v>7.6</v>
@@ -3763,7 +3763,7 @@
         <v>29</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
@@ -3778,19 +3778,19 @@
         <v>12.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
         <v>40</v>
       </c>
       <c r="AT17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
@@ -3799,25 +3799,25 @@
         <v>6.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AY17" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
         <v>26</v>
       </c>
       <c r="BC17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
         <v>7.2</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3861,46 +3861,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
         <v>1.74</v>
@@ -3909,19 +3909,19 @@
         <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
         <v>85</v>
@@ -3930,7 +3930,7 @@
         <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD18" t="n">
         <v>11.5</v>
@@ -3939,7 +3939,7 @@
         <v>28</v>
       </c>
       <c r="AF18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
         <v>13.5</v>
@@ -3948,10 +3948,10 @@
         <v>17.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AJ18" t="n">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
         <v>95</v>
@@ -3963,10 +3963,10 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
         <v>11.5</v>
@@ -3990,7 +3990,7 @@
         <v>9.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX18" t="n">
         <v>19.5</v>
@@ -4002,16 +4002,16 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BC18" t="n">
         <v>18</v>
       </c>
       <c r="BD18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE18" t="n">
         <v>10.5</v>
@@ -4020,11 +4020,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4055,67 +4055,67 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="G19" t="n">
         <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I19" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W19" t="n">
         <v>1.5</v>
       </c>
       <c r="X19" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Y19" t="n">
         <v>19.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
@@ -4130,7 +4130,7 @@
         <v>18</v>
       </c>
       <c r="AE19" t="n">
-        <v>75</v>
+        <v>980</v>
       </c>
       <c r="AF19" t="n">
         <v>34</v>
@@ -4151,13 +4151,13 @@
         <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO19" t="n">
         <v>55</v>
@@ -4169,10 +4169,10 @@
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
@@ -4184,10 +4184,10 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
@@ -4196,10 +4196,10 @@
         <v>9</v>
       </c>
       <c r="BA19" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC19" t="n">
         <v>14.5</v>
@@ -4208,17 +4208,17 @@
         <v>18</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>2.46</v>
       </c>
       <c r="I20" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>3.45</v>
@@ -4282,22 +4282,22 @@
         <v>1.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R20" t="n">
         <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
         <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W20" t="n">
         <v>1.43</v>
@@ -4306,7 +4306,7 @@
         <v>12</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z20" t="n">
         <v>15</v>
@@ -4330,7 +4330,7 @@
         <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>18</v>
@@ -4345,7 +4345,7 @@
         <v>38</v>
       </c>
       <c r="AL20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -4354,10 +4354,10 @@
         <v>38</v>
       </c>
       <c r="AO20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ20" t="n">
         <v>9</v>
@@ -4366,13 +4366,13 @@
         <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
         <v>10.5</v>
@@ -4393,13 +4393,13 @@
         <v>38</v>
       </c>
       <c r="BB20" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BC20" t="n">
         <v>34</v>
       </c>
       <c r="BD20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE20" t="n">
         <v>55</v>
@@ -4408,11 +4408,11 @@
         <v>34</v>
       </c>
       <c r="BG20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4443,88 +4443,88 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="K21" t="n">
         <v>3.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="M21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N21" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="O21" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="P21" t="n">
         <v>1.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
         <v>1.11</v>
       </c>
       <c r="S21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="T21" t="n">
         <v>2.66</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="X21" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AA21" t="n">
         <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE21" t="n">
         <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
         <v>44</v>
@@ -4533,19 +4533,19 @@
         <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
         <v>46</v>
       </c>
       <c r="AL21" t="n">
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="AM21" t="n">
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="AO21" t="n">
         <v>500</v>
@@ -4554,46 +4554,46 @@
         <v>3.25</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR21" t="n">
         <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AT21" t="n">
         <v>3.25</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
         <v>18.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BB21" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
         <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.2</v>
+        <v>29</v>
       </c>
       <c r="BE21" t="n">
         <v>28</v>
@@ -4602,11 +4602,11 @@
         <v>9</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4637,170 +4637,170 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H22" t="n">
         <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
         <v>3.35</v>
       </c>
       <c r="L22" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M22" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N22" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="R22" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X22" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AC22" t="n">
         <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
         <v>700</v>
       </c>
       <c r="AF22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AI22" t="n">
         <v>700</v>
       </c>
       <c r="AJ22" t="n">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
         <v>65</v>
       </c>
       <c r="AL22" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM22" t="n">
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AO22" t="n">
         <v>700</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AX22" t="n">
         <v>9.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="BA22" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BD22" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BE22" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="BF22" t="n">
         <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4831,52 +4831,52 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G23" t="n">
         <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="I23" t="n">
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
         <v>7.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="U23" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="V23" t="n">
         <v>1.06</v>
@@ -4885,100 +4885,100 @@
         <v>4.8</v>
       </c>
       <c r="X23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y23" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>180</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>810</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH23" t="n">
         <v>46</v>
       </c>
-      <c r="Z23" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>830</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE23" t="n">
+      <c r="AI23" t="n">
+        <v>300</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
         <v>330</v>
       </c>
-      <c r="AF23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>270</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>260</v>
-      </c>
       <c r="AN23" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AO23" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ23" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AR23" t="n">
         <v>36</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV23" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AW23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY23" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BA23" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD23" t="n">
         <v>42</v>
@@ -4987,14 +4987,14 @@
         <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5025,67 +5025,67 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G24" t="n">
         <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I24" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
         <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA24" t="n">
         <v>21</v>
@@ -5097,7 +5097,7 @@
         <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -5124,13 +5124,13 @@
         <v>75</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AN24" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AO24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP24" t="n">
         <v>12.5</v>
@@ -5139,13 +5139,13 @@
         <v>7.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
@@ -5154,7 +5154,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX24" t="n">
         <v>30</v>
@@ -5163,13 +5163,13 @@
         <v>17</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA24" t="n">
         <v>32</v>
       </c>
       <c r="BB24" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="BC24" t="n">
         <v>50</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5219,91 +5219,91 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="G25" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>3.85</v>
       </c>
       <c r="K25" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="U25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W25" t="n">
         <v>2.08</v>
       </c>
-      <c r="V25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.06</v>
-      </c>
       <c r="X25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y25" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA25" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC25" t="n">
         <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
         <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>320</v>
@@ -5312,77 +5312,77 @@
         <v>22</v>
       </c>
       <c r="AK25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM25" t="n">
-        <v>390</v>
+        <v>130</v>
       </c>
       <c r="AN25" t="n">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="AO25" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV25" t="n">
         <v>16.5</v>
       </c>
-      <c r="AT25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AX25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC25" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD25" t="n">
         <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BF25" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BG25" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5413,170 +5413,170 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="G26" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="H26" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="I26" t="n">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
         <v>1.26</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R26" t="n">
         <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="U26" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="W26" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="X26" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE26" t="n">
         <v>17</v>
       </c>
-      <c r="Y26" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>21</v>
-      </c>
       <c r="AF26" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AI26" t="n">
         <v>32</v>
       </c>
       <c r="AJ26" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AK26" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AL26" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AM26" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN26" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AO26" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
       </c>
       <c r="AQ26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR26" t="n">
         <v>10</v>
       </c>
-      <c r="AR26" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AS26" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AT26" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AX26" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AY26" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB26" t="n">
         <v>28</v>
       </c>
       <c r="BC26" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BD26" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BF26" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BG26" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H27" t="n">
         <v>6.4</v>
       </c>
       <c r="I27" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
         <v>4.4</v>
@@ -5631,16 +5631,16 @@
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R27" t="n">
         <v>1.47</v>
@@ -5649,10 +5649,10 @@
         <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U27" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V27" t="n">
         <v>1.17</v>
@@ -5661,7 +5661,7 @@
         <v>2.62</v>
       </c>
       <c r="X27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y27" t="n">
         <v>23</v>
@@ -5670,13 +5670,13 @@
         <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27" t="n">
         <v>24</v>
@@ -5685,7 +5685,7 @@
         <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG27" t="n">
         <v>9.800000000000001</v>
@@ -5694,7 +5694,7 @@
         <v>20</v>
       </c>
       <c r="AI27" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="n">
         <v>15</v>
@@ -5703,7 +5703,7 @@
         <v>15.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM27" t="n">
         <v>100</v>
@@ -5712,25 +5712,25 @@
         <v>7.6</v>
       </c>
       <c r="AO27" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ27" t="n">
         <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS27" t="n">
         <v>44</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV27" t="n">
         <v>22</v>
@@ -5754,23 +5754,23 @@
         <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD27" t="n">
         <v>30</v>
       </c>
       <c r="BE27" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG27" t="n">
         <v>85</v>
       </c>
-      <c r="BF27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>80</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G28" t="n">
         <v>2.76</v>
@@ -5819,31 +5819,31 @@
         <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.34</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.36</v>
-      </c>
       <c r="S28" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U28" t="n">
         <v>2.18</v>
@@ -5861,7 +5861,7 @@
         <v>11.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA28" t="n">
         <v>44</v>
@@ -5876,37 +5876,37 @@
         <v>12.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF28" t="n">
         <v>17.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
         <v>17</v>
       </c>
       <c r="AI28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL28" t="n">
         <v>44</v>
       </c>
-      <c r="AJ28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK28" t="n">
+      <c r="AM28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO28" t="n">
         <v>29</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>27</v>
       </c>
       <c r="AP28" t="n">
         <v>12.5</v>
@@ -5918,10 +5918,10 @@
         <v>17</v>
       </c>
       <c r="AS28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
         <v>7.2</v>
@@ -5930,31 +5930,31 @@
         <v>11.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX28" t="n">
         <v>16.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ28" t="n">
         <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB28" t="n">
         <v>38</v>
       </c>
       <c r="BC28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD28" t="n">
         <v>38</v>
       </c>
       <c r="BE28" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BF28" t="n">
         <v>23</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6013,13 +6013,13 @@
         <v>3.65</v>
       </c>
       <c r="L29" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
         <v>1.36</v>
@@ -6028,13 +6028,13 @@
         <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R29" t="n">
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T29" t="n">
         <v>1.87</v>
@@ -6046,7 +6046,7 @@
         <v>1.34</v>
       </c>
       <c r="W29" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X29" t="n">
         <v>13</v>
@@ -6055,7 +6055,7 @@
         <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA29" t="n">
         <v>80</v>
@@ -6070,7 +6070,7 @@
         <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF29" t="n">
         <v>12.5</v>
@@ -6097,10 +6097,10 @@
         <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP29" t="n">
         <v>12</v>
@@ -6112,7 +6112,7 @@
         <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT29" t="n">
         <v>8.4</v>
@@ -6127,7 +6127,7 @@
         <v>42</v>
       </c>
       <c r="AX29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
         <v>10</v>
@@ -6136,7 +6136,7 @@
         <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB29" t="n">
         <v>24</v>
@@ -6148,17 +6148,17 @@
         <v>36</v>
       </c>
       <c r="BE29" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="BF29" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="G30" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="H30" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="I30" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="J30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L30" t="n">
         <v>1.44</v>
@@ -6213,13 +6213,13 @@
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P30" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q30" t="n">
         <v>2.08</v>
@@ -6231,128 +6231,128 @@
         <v>3.85</v>
       </c>
       <c r="T30" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U30" t="n">
         <v>2.04</v>
       </c>
       <c r="V30" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="W30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA30" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AB30" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG30" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI30" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK30" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AL30" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="AM30" t="n">
         <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO30" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>8</v>
       </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS30" t="n">
         <v>21</v>
       </c>
       <c r="AT30" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU30" t="n">
         <v>7.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW30" t="n">
         <v>19.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AY30" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
         <v>32</v>
       </c>
       <c r="BB30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC30" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BD30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE30" t="n">
         <v>40</v>
       </c>
       <c r="BF30" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BG30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6383,55 +6383,55 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="G31" t="n">
         <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="J31" t="n">
         <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="M31" t="n">
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="O31" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="P31" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="R31" t="n">
         <v>1.17</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V31" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W31" t="n">
         <v>1.35</v>
@@ -6440,16 +6440,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC31" t="n">
         <v>7.2</v>
@@ -6458,25 +6458,25 @@
         <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AG31" t="n">
         <v>17</v>
       </c>
       <c r="AH31" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>900</v>
+        <v>490</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL31" t="n">
         <v>540</v>
@@ -6488,22 +6488,22 @@
         <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP31" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS31" t="n">
         <v>29</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU31" t="n">
         <v>6.2</v>
@@ -6521,13 +6521,13 @@
         <v>15</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
         <v>50</v>
       </c>
       <c r="BB31" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BC31" t="n">
         <v>44</v>
@@ -6542,11 +6542,11 @@
         <v>36</v>
       </c>
       <c r="BG31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6577,82 +6577,82 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G32" t="n">
         <v>2.34</v>
       </c>
       <c r="H32" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
         <v>3.05</v>
       </c>
       <c r="K32" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="M32" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N32" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O32" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="P32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S32" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="U32" t="n">
         <v>1.66</v>
       </c>
       <c r="V32" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W32" t="n">
         <v>1.75</v>
       </c>
       <c r="X32" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y32" t="n">
         <v>10.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AA32" t="n">
         <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF32" t="n">
         <v>12</v>
@@ -6661,7 +6661,7 @@
         <v>13</v>
       </c>
       <c r="AH32" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AI32" t="n">
         <v>500</v>
@@ -6670,7 +6670,7 @@
         <v>900</v>
       </c>
       <c r="AK32" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AL32" t="n">
         <v>1000</v>
@@ -6682,19 +6682,19 @@
         <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP32" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ32" t="n">
         <v>8.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT32" t="n">
         <v>5.8</v>
@@ -6703,25 +6703,25 @@
         <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW32" t="n">
         <v>48</v>
       </c>
       <c r="AX32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BA32" t="n">
         <v>42</v>
       </c>
       <c r="BB32" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC32" t="n">
         <v>30</v>
@@ -6730,17 +6730,17 @@
         <v>60</v>
       </c>
       <c r="BE32" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="BF32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG32" t="n">
         <v>40</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>3.3</v>
       </c>
       <c r="G33" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H33" t="n">
         <v>2.4</v>
@@ -6783,28 +6783,28 @@
         <v>2.44</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K33" t="n">
         <v>3.55</v>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O33" t="n">
         <v>1.32</v>
       </c>
       <c r="P33" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R33" t="n">
         <v>1.38</v>
@@ -6846,13 +6846,13 @@
         <v>11.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF33" t="n">
         <v>25</v>
       </c>
       <c r="AG33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH33" t="n">
         <v>17</v>
@@ -6867,16 +6867,16 @@
         <v>38</v>
       </c>
       <c r="AL33" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM33" t="n">
         <v>90</v>
       </c>
       <c r="AN33" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AO33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP33" t="n">
         <v>13</v>
@@ -6891,10 +6891,10 @@
         <v>30</v>
       </c>
       <c r="AT33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
@@ -6906,10 +6906,10 @@
         <v>20</v>
       </c>
       <c r="AY33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA33" t="n">
         <v>34</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6965,25 +6965,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G34" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="H34" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J34" t="n">
         <v>4.9</v>
       </c>
       <c r="K34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M34" t="n">
         <v>1.06</v>
@@ -6992,61 +6992,61 @@
         <v>4.1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P34" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R34" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T34" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U34" t="n">
         <v>1.81</v>
       </c>
       <c r="V34" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W34" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="X34" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y34" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Z34" t="n">
-        <v>540</v>
+        <v>170</v>
       </c>
       <c r="AA34" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="AB34" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC34" t="n">
         <v>11</v>
       </c>
       <c r="AD34" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE34" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF34" t="n">
         <v>8</v>
       </c>
       <c r="AG34" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH34" t="n">
         <v>29</v>
@@ -7061,61 +7061,61 @@
         <v>16</v>
       </c>
       <c r="AL34" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM34" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN34" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO34" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AP34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR34" t="n">
         <v>28</v>
       </c>
       <c r="AS34" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AT34" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU34" t="n">
         <v>10</v>
       </c>
       <c r="AV34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW34" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX34" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY34" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA34" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BB34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC34" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BE34" t="n">
         <v>42</v>
@@ -7124,11 +7124,11 @@
         <v>6.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7159,55 +7159,55 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="G35" t="n">
         <v>3.65</v>
       </c>
       <c r="H35" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I35" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J35" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K35" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="M35" t="n">
         <v>1.16</v>
       </c>
       <c r="N35" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="O35" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="P35" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
         <v>1.14</v>
       </c>
       <c r="S35" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V35" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W35" t="n">
         <v>1.37</v>
@@ -7231,7 +7231,7 @@
         <v>7.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>980</v>
+        <v>14.5</v>
       </c>
       <c r="AE35" t="n">
         <v>980</v>
@@ -7240,7 +7240,7 @@
         <v>980</v>
       </c>
       <c r="AG35" t="n">
-        <v>980</v>
+        <v>18</v>
       </c>
       <c r="AH35" t="n">
         <v>980</v>
@@ -7249,16 +7249,16 @@
         <v>90</v>
       </c>
       <c r="AJ35" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK35" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL35" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN35" t="n">
         <v>1000</v>
@@ -7288,41 +7288,41 @@
         <v>11.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX35" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="AY35" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="BA35" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB35" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC35" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BD35" t="n">
         <v>10</v>
       </c>
       <c r="BE35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF35" t="n">
         <v>10</v>
       </c>
-      <c r="BF35" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG35" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G36" t="n">
         <v>2.12</v>
@@ -7362,22 +7362,22 @@
         <v>3.9</v>
       </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>3.65</v>
       </c>
       <c r="K36" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L36" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O36" t="n">
         <v>1.36</v>
@@ -7386,28 +7386,28 @@
         <v>1.87</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R36" t="n">
         <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T36" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U36" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V36" t="n">
         <v>1.33</v>
       </c>
       <c r="W36" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X36" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y36" t="n">
         <v>13.5</v>
@@ -7419,22 +7419,22 @@
         <v>85</v>
       </c>
       <c r="AB36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE36" t="n">
         <v>980</v>
       </c>
-      <c r="AE36" t="n">
-        <v>55</v>
-      </c>
       <c r="AF36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AH36" t="n">
         <v>980</v>
@@ -7455,7 +7455,7 @@
         <v>130</v>
       </c>
       <c r="AN36" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AO36" t="n">
         <v>60</v>
@@ -7467,22 +7467,22 @@
         <v>12</v>
       </c>
       <c r="AR36" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AS36" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="AT36" t="n">
         <v>8</v>
       </c>
       <c r="AU36" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV36" t="n">
         <v>14.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="AX36" t="n">
         <v>11</v>
@@ -7491,10 +7491,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA36" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BB36" t="n">
         <v>22</v>
@@ -7506,17 +7506,17 @@
         <v>32</v>
       </c>
       <c r="BE36" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BF36" t="n">
         <v>15</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.7</v>
+        <v>46</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G2" t="n">
         <v>2.04</v>
@@ -772,37 +772,37 @@
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
         <v>1.29</v>
@@ -811,46 +811,46 @@
         <v>1.96</v>
       </c>
       <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y2" t="n">
-        <v>30</v>
-      </c>
       <c r="Z2" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
         <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
         <v>80</v>
@@ -859,68 +859,68 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS2" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
         <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -951,67 +951,67 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
         <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
         <v>19.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1020,16 +1020,16 @@
         <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1041,22 +1041,22 @@
         <v>390</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
         <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>11.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>310</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
         <v>13.5</v>
@@ -1065,10 +1065,10 @@
         <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>7.8</v>
@@ -1077,13 +1077,13 @@
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3" t="n">
         <v>8.800000000000001</v>
@@ -1092,29 +1092,29 @@
         <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
         <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>2.98</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
         <v>3.95</v>
@@ -1175,10 +1175,10 @@
         <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
         <v>1.35</v>
@@ -1193,10 +1193,10 @@
         <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
         <v>15.5</v>
@@ -1256,7 +1256,7 @@
         <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
         <v>13</v>
@@ -1283,7 +1283,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
         <v>24</v>
@@ -1298,7 +1298,7 @@
         <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -1342,55 +1342,55 @@
         <v>3.95</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H5" t="n">
         <v>1.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
         <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X5" t="n">
         <v>18</v>
@@ -1429,7 +1429,7 @@
         <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300</v>
+        <v>85</v>
       </c>
       <c r="AK5" t="n">
         <v>85</v>
@@ -1438,10 +1438,10 @@
         <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1456,7 +1456,7 @@
         <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT5" t="n">
         <v>14.5</v>
@@ -1480,10 +1480,10 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC5" t="n">
         <v>22</v>
@@ -1492,17 +1492,17 @@
         <v>10.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF5" t="n">
         <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -1533,85 +1533,85 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="H6" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="I6" t="n">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="R6" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="U6" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="X6" t="n">
         <v>500</v>
       </c>
       <c r="Y6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AC6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
         <v>500</v>
@@ -1623,80 +1623,80 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
       </c>
       <c r="AM6" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN6" t="n">
         <v>200</v>
       </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO6" t="n">
-        <v>9.4</v>
+        <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.42</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.68</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.68</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="AV6" t="n">
         <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.68</v>
+        <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.56</v>
+        <v>5.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.66</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.64</v>
+        <v>4.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H7" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.36</v>
@@ -1751,34 +1751,34 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.89</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.9</v>
       </c>
       <c r="V7" t="n">
         <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,7 +1793,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>42</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
         <v>36</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,28 +1838,28 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AV7" t="n">
         <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AY7" t="n">
         <v>5.8</v>
@@ -1868,29 +1868,29 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC7" t="n">
         <v>8.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.8</v>
+        <v>18</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BG7" t="n">
         <v>15</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H8" t="n">
         <v>2.86</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
         <v>3.6</v>
@@ -1951,40 +1951,40 @@
         <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB8" t="n">
         <v>11.5</v>
@@ -1996,7 +1996,7 @@
         <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF8" t="n">
         <v>17.5</v>
@@ -2020,7 +2020,7 @@
         <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN8" t="n">
         <v>24</v>
@@ -2035,13 +2035,13 @@
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
@@ -2050,7 +2050,7 @@
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX8" t="n">
         <v>16</v>
@@ -2059,7 +2059,7 @@
         <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>34</v>
@@ -2077,14 +2077,14 @@
         <v>44</v>
       </c>
       <c r="BF8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -2115,85 +2115,85 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G9" t="n">
         <v>3.95</v>
       </c>
       <c r="H9" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.45</v>
       </c>
-      <c r="K9" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA9" t="n">
         <v>30</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG9" t="n">
         <v>16.5</v>
@@ -2214,40 +2214,40 @@
         <v>75</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY9" t="n">
         <v>15</v>
@@ -2256,7 +2256,7 @@
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB9" t="n">
         <v>23</v>
@@ -2271,14 +2271,14 @@
         <v>29</v>
       </c>
       <c r="BF9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BG9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G10" t="n">
         <v>4.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="I10" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
@@ -2336,28 +2336,28 @@
         <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
         <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W10" t="n">
         <v>1.27</v>
@@ -2366,7 +2366,7 @@
         <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z10" t="n">
         <v>11.5</v>
@@ -2375,10 +2375,10 @@
         <v>21</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
         <v>10</v>
@@ -2390,25 +2390,25 @@
         <v>34</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AH10" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>34</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
-        <v>320</v>
+        <v>130</v>
       </c>
       <c r="AL10" t="n">
         <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="AN10" t="n">
         <v>60</v>
@@ -2429,7 +2429,7 @@
         <v>18.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU10" t="n">
         <v>8</v>
@@ -2453,26 +2453,26 @@
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="BC10" t="n">
         <v>50</v>
       </c>
       <c r="BD10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE10" t="n">
         <v>50</v>
       </c>
       <c r="BF10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BG10" t="n">
         <v>11.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H11" t="n">
         <v>4.1</v>
@@ -2515,22 +2515,22 @@
         <v>4.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
         <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
         <v>2.04</v>
@@ -2545,22 +2545,22 @@
         <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
         <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X11" t="n">
         <v>16</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z11" t="n">
         <v>32</v>
@@ -2569,13 +2569,13 @@
         <v>90</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
         <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
         <v>50</v>
@@ -2593,7 +2593,7 @@
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK11" t="n">
         <v>20</v>
@@ -2605,22 +2605,22 @@
         <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AT11" t="n">
         <v>9.199999999999999</v>
@@ -2632,7 +2632,7 @@
         <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX11" t="n">
         <v>11.5</v>
@@ -2644,29 +2644,29 @@
         <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="BF11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         <v>2.24</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
         <v>3.5</v>
@@ -2730,7 +2730,7 @@
         <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
@@ -2742,13 +2742,13 @@
         <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
         <v>11.5</v>
@@ -2778,10 +2778,10 @@
         <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
         <v>44</v>
@@ -2793,7 +2793,7 @@
         <v>50</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM12" t="n">
         <v>120</v>
@@ -2805,13 +2805,13 @@
         <v>21</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
         <v>26</v>
@@ -2832,7 +2832,7 @@
         <v>23</v>
       </c>
       <c r="AY12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ12" t="n">
         <v>17.5</v>
@@ -2841,16 +2841,16 @@
         <v>38</v>
       </c>
       <c r="BB12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BC12" t="n">
         <v>44</v>
       </c>
       <c r="BD12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE12" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="BF12" t="n">
         <v>50</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>3.35</v>
       </c>
       <c r="G13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I13" t="n">
         <v>2.58</v>
@@ -2909,7 +2909,7 @@
         <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
@@ -2918,10 +2918,10 @@
         <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q13" t="n">
         <v>2.5</v>
@@ -2945,7 +2945,7 @@
         <v>1.41</v>
       </c>
       <c r="X13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
         <v>8.199999999999999</v>
@@ -2972,7 +2972,7 @@
         <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
@@ -2990,7 +2990,7 @@
         <v>65</v>
       </c>
       <c r="AM13" t="n">
-        <v>440</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
         <v>60</v>
@@ -3023,13 +3023,13 @@
         <v>30</v>
       </c>
       <c r="AX13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
         <v>48</v>
@@ -3044,7 +3044,7 @@
         <v>55</v>
       </c>
       <c r="BE13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BF13" t="n">
         <v>50</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -3085,100 +3085,100 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="G14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
         <v>8.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
         <v>34</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
         <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AL14" t="n">
         <v>60</v>
@@ -3187,13 +3187,13 @@
         <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AO14" t="n">
         <v>26</v>
       </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.199999999999999</v>
@@ -3202,16 +3202,16 @@
         <v>13.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
         <v>26</v>
@@ -3220,35 +3220,35 @@
         <v>20</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
         <v>38</v>
       </c>
       <c r="BB14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BD14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BG14" t="n">
         <v>23</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -3285,10 +3285,10 @@
         <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>3.55</v>
@@ -3303,13 +3303,13 @@
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q15" t="n">
         <v>2.14</v>
@@ -3318,22 +3318,22 @@
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
         <v>1.88</v>
       </c>
       <c r="X15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
         <v>13.5</v>
@@ -3345,10 +3345,10 @@
         <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD15" t="n">
         <v>16</v>
@@ -3360,7 +3360,7 @@
         <v>12</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
         <v>18.5</v>
@@ -3369,7 +3369,7 @@
         <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK15" t="n">
         <v>23</v>
@@ -3387,16 +3387,16 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS15" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AT15" t="n">
         <v>8.199999999999999</v>
@@ -3405,13 +3405,13 @@
         <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>48</v>
       </c>
       <c r="AX15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
         <v>21</v>
       </c>
       <c r="BD15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE15" t="n">
         <v>95</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
         <v>1.34</v>
       </c>
       <c r="H16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.28</v>
@@ -3509,19 +3509,19 @@
         <v>1.53</v>
       </c>
       <c r="R16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
         <v>3.85</v>
@@ -3539,10 +3539,10 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD16" t="n">
         <v>38</v>
@@ -3557,16 +3557,16 @@
         <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AK16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL16" t="n">
         <v>36</v>
@@ -3581,40 +3581,40 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
         <v>9.199999999999999</v>
@@ -3623,20 +3623,20 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
         <v>1.42</v>
@@ -3691,76 +3691,76 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
         <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
         <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>980</v>
       </c>
       <c r="AF17" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI17" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
         <v>980</v>
@@ -3769,68 +3769,68 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AP17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AT17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB17" t="n">
+      <c r="BF17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG17" t="n">
         <v>26</v>
       </c>
-      <c r="BC17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -3861,37 +3861,37 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H18" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I18" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
         <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
         <v>2.06</v>
@@ -3924,10 +3924,10 @@
         <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC18" t="n">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>95</v>
       </c>
       <c r="AL18" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AM18" t="n">
         <v>580</v>
@@ -3987,10 +3987,10 @@
         <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX18" t="n">
         <v>19.5</v>
@@ -4002,29 +4002,29 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD18" t="n">
         <v>23</v>
       </c>
-      <c r="BB18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD18" t="n">
+      <c r="BE18" t="n">
         <v>11</v>
       </c>
-      <c r="BE18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF18" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BG18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H19" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
         <v>3.85</v>
@@ -4079,7 +4079,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
         <v>1.28</v>
@@ -4094,49 +4094,49 @@
         <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V19" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="X19" t="n">
         <v>29</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
-        <v>980</v>
+        <v>26</v>
       </c>
       <c r="AF19" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -4145,22 +4145,22 @@
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AK19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL19" t="n">
         <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>85</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>55</v>
+        <v>18.5</v>
       </c>
       <c r="AP19" t="n">
         <v>14</v>
@@ -4169,10 +4169,10 @@
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
@@ -4184,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
         <v>16</v>
@@ -4193,32 +4193,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB19" t="n">
         <v>18</v>
       </c>
-      <c r="BB19" t="n">
-        <v>10</v>
-      </c>
       <c r="BC19" t="n">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BE19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF19" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG19" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G20" t="n">
         <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.45</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.5</v>
       </c>
       <c r="L20" t="n">
         <v>1.46</v>
@@ -4279,25 +4279,25 @@
         <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U20" t="n">
         <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
         <v>1.43</v>
@@ -4336,10 +4336,10 @@
         <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK20" t="n">
         <v>38</v>
@@ -4351,13 +4351,13 @@
         <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO20" t="n">
         <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>9</v>
@@ -4366,7 +4366,7 @@
         <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
@@ -4381,7 +4381,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY20" t="n">
         <v>12.5</v>
@@ -4399,7 +4399,7 @@
         <v>34</v>
       </c>
       <c r="BD20" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE20" t="n">
         <v>55</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -4443,37 +4443,37 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L21" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="M21" t="n">
         <v>1.19</v>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="P21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q21" t="n">
         <v>3.6</v>
@@ -4491,16 +4491,16 @@
         <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W21" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X21" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
         <v>100</v>
@@ -4509,22 +4509,22 @@
         <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE21" t="n">
         <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
         <v>44</v>
@@ -4533,10 +4533,10 @@
         <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AK21" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AL21" t="n">
         <v>240</v>
@@ -4545,68 +4545,68 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="AO21" t="n">
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.25</v>
+        <v>5.9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC21" t="n">
         <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE21" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="BF21" t="n">
         <v>9</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
         <v>2.06</v>
@@ -4646,7 +4646,7 @@
         <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
         <v>3.2</v>
@@ -4661,28 +4661,28 @@
         <v>1.14</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O22" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="P22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V22" t="n">
         <v>1.25</v>
@@ -4691,7 +4691,7 @@
         <v>1.94</v>
       </c>
       <c r="X22" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y22" t="n">
         <v>11.5</v>
@@ -4703,7 +4703,7 @@
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC22" t="n">
         <v>7.6</v>
@@ -4715,13 +4715,13 @@
         <v>700</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG22" t="n">
         <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AI22" t="n">
         <v>700</v>
@@ -4730,22 +4730,22 @@
         <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AL22" t="n">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="AM22" t="n">
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO22" t="n">
         <v>700</v>
       </c>
       <c r="AP22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>10</v>
@@ -4760,10 +4760,10 @@
         <v>5.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW22" t="n">
         <v>36</v>
@@ -4778,7 +4778,7 @@
         <v>26</v>
       </c>
       <c r="BA22" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
@@ -4787,7 +4787,7 @@
         <v>27</v>
       </c>
       <c r="BD22" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BE22" t="n">
         <v>100</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -4837,61 +4837,61 @@
         <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
         <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P23" t="n">
         <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="T23" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="U23" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V23" t="n">
         <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="X23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y23" t="n">
         <v>44</v>
       </c>
       <c r="Z23" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AA23" t="n">
         <v>810</v>
@@ -4903,52 +4903,52 @@
         <v>15.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AE23" t="n">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="AF23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI23" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="AJ23" t="n">
         <v>8.6</v>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL23" t="n">
         <v>55</v>
       </c>
       <c r="AM23" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ23" t="n">
         <v>34</v>
       </c>
       <c r="AR23" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AS23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT23" t="n">
         <v>7.2</v>
@@ -4960,7 +4960,7 @@
         <v>48</v>
       </c>
       <c r="AW23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AX23" t="n">
         <v>6.2</v>
@@ -4969,32 +4969,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BA23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB23" t="n">
         <v>8</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE23" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -5028,34 +5028,34 @@
         <v>4.8</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H24" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I24" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.9</v>
       </c>
-      <c r="K24" t="n">
-        <v>3.95</v>
-      </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
         <v>2.02</v>
@@ -5067,25 +5067,25 @@
         <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V24" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA24" t="n">
         <v>21</v>
@@ -5094,16 +5094,16 @@
         <v>16.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AG24" t="n">
         <v>18.5</v>
@@ -5124,28 +5124,28 @@
         <v>75</v>
       </c>
       <c r="AM24" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AN24" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP24" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
@@ -5157,28 +5157,28 @@
         <v>18</v>
       </c>
       <c r="AX24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AY24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA24" t="n">
         <v>32</v>
       </c>
       <c r="BB24" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="BC24" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE24" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BF24" t="n">
         <v>60</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -5219,25 +5219,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="G25" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
@@ -5249,52 +5249,52 @@
         <v>1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W25" t="n">
         <v>2.14</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.08</v>
-      </c>
       <c r="X25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA25" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB25" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AF25" t="n">
         <v>11</v>
@@ -5303,55 +5303,55 @@
         <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="AJ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM25" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN25" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="AO25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
         <v>12</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AS25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV25" t="n">
         <v>17.5</v>
       </c>
-      <c r="AT25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AW25" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY25" t="n">
         <v>9.4</v>
@@ -5360,29 +5360,29 @@
         <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD25" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE25" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="BF25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG25" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -5416,16 +5416,16 @@
         <v>5.1</v>
       </c>
       <c r="G26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H26" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I26" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
         <v>4.2</v>
@@ -5443,7 +5443,7 @@
         <v>1.26</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
         <v>1.79</v>
@@ -5455,13 +5455,13 @@
         <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V26" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="W26" t="n">
         <v>1.23</v>
@@ -5470,7 +5470,7 @@
         <v>18</v>
       </c>
       <c r="Y26" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z26" t="n">
         <v>11.5</v>
@@ -5479,10 +5479,10 @@
         <v>18</v>
       </c>
       <c r="AB26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
         <v>42</v>
       </c>
       <c r="AG26" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI26" t="n">
         <v>32</v>
@@ -5515,16 +5515,16 @@
         <v>90</v>
       </c>
       <c r="AN26" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR26" t="n">
         <v>10</v>
@@ -5536,47 +5536,47 @@
         <v>17.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY26" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB26" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="BC26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD26" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BE26" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BF26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BG26" t="n">
         <v>8.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G27" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="H27" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J27" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L27" t="n">
         <v>1.35</v>
@@ -5631,58 +5631,58 @@
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R27" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T27" t="n">
         <v>1.88</v>
       </c>
       <c r="U27" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V27" t="n">
         <v>1.17</v>
       </c>
       <c r="W27" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="X27" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF27" t="n">
         <v>9.6</v>
@@ -5691,16 +5691,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
         <v>80</v>
       </c>
       <c r="AJ27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK27" t="n">
         <v>15</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>15.5</v>
       </c>
       <c r="AL27" t="n">
         <v>34</v>
@@ -5709,13 +5709,13 @@
         <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO27" t="n">
         <v>100</v>
       </c>
       <c r="AP27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ27" t="n">
         <v>21</v>
@@ -5727,10 +5727,10 @@
         <v>44</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV27" t="n">
         <v>22</v>
@@ -5745,32 +5745,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA27" t="n">
         <v>70</v>
       </c>
       <c r="BB27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC27" t="n">
         <v>14</v>
       </c>
-      <c r="BC27" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE27" t="n">
         <v>90</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG27" t="n">
         <v>85</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -5801,64 +5801,64 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G28" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H28" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I28" t="n">
         <v>2.88</v>
       </c>
       <c r="J28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.5</v>
       </c>
-      <c r="K28" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M28" t="n">
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U28" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V28" t="n">
         <v>1.53</v>
       </c>
       <c r="W28" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X28" t="n">
         <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z28" t="n">
         <v>18</v>
@@ -5870,7 +5870,7 @@
         <v>11</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD28" t="n">
         <v>12.5</v>
@@ -5885,16 +5885,16 @@
         <v>12.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ28" t="n">
         <v>42</v>
       </c>
       <c r="AK28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL28" t="n">
         <v>44</v>
@@ -5906,16 +5906,16 @@
         <v>28</v>
       </c>
       <c r="AO28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP28" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS28" t="n">
         <v>40</v>
@@ -5936,7 +5936,7 @@
         <v>16.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
         <v>16</v>
@@ -5954,17 +5954,17 @@
         <v>38</v>
       </c>
       <c r="BE28" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BF28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BG28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G29" t="n">
         <v>2.16</v>
@@ -6040,13 +6040,13 @@
         <v>1.87</v>
       </c>
       <c r="U29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V29" t="n">
         <v>1.34</v>
       </c>
       <c r="W29" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X29" t="n">
         <v>13</v>
@@ -6061,7 +6061,7 @@
         <v>80</v>
       </c>
       <c r="AB29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC29" t="n">
         <v>7.8</v>
@@ -6070,7 +6070,7 @@
         <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF29" t="n">
         <v>12.5</v>
@@ -6079,7 +6079,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI29" t="n">
         <v>60</v>
@@ -6109,7 +6109,7 @@
         <v>12.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS29" t="n">
         <v>70</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>4.1</v>
       </c>
       <c r="G30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H30" t="n">
         <v>1.99</v>
@@ -6201,10 +6201,10 @@
         <v>2.02</v>
       </c>
       <c r="J30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.75</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.85</v>
       </c>
       <c r="L30" t="n">
         <v>1.44</v>
@@ -6219,7 +6219,7 @@
         <v>1.36</v>
       </c>
       <c r="P30" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q30" t="n">
         <v>2.08</v>
@@ -6240,7 +6240,7 @@
         <v>1.98</v>
       </c>
       <c r="W30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X30" t="n">
         <v>13.5</v>
@@ -6249,7 +6249,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z30" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AA30" t="n">
         <v>34</v>
@@ -6282,16 +6282,16 @@
         <v>95</v>
       </c>
       <c r="AK30" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AL30" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AM30" t="n">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN30" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO30" t="n">
         <v>16</v>
@@ -6309,7 +6309,7 @@
         <v>21</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU30" t="n">
         <v>7.6</v>
@@ -6324,10 +6324,10 @@
         <v>27</v>
       </c>
       <c r="AY30" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA30" t="n">
         <v>32</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G31" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H31" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I31" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.05</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.2</v>
       </c>
       <c r="L31" t="n">
         <v>1.64</v>
@@ -6410,13 +6410,13 @@
         <v>2.52</v>
       </c>
       <c r="O31" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P31" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R31" t="n">
         <v>1.17</v>
@@ -6425,112 +6425,112 @@
         <v>6.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="U31" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V31" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W31" t="n">
         <v>1.35</v>
       </c>
       <c r="X31" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Z31" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD31" t="n">
         <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AF31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>490</v>
+        <v>85</v>
       </c>
       <c r="AK31" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AL31" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO31" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AX31" t="n">
         <v>21</v>
       </c>
       <c r="AY31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA31" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB31" t="n">
         <v>50</v>
       </c>
-      <c r="BB31" t="n">
-        <v>70</v>
-      </c>
       <c r="BC31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BD31" t="n">
         <v>38</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.05</v>
@@ -6601,13 +6601,13 @@
         <v>1.16</v>
       </c>
       <c r="N32" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="O32" t="n">
         <v>1.71</v>
       </c>
       <c r="P32" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q32" t="n">
         <v>3.2</v>
@@ -6622,19 +6622,19 @@
         <v>2.48</v>
       </c>
       <c r="U32" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="V32" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
         <v>1.75</v>
       </c>
       <c r="X32" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z32" t="n">
         <v>27</v>
@@ -6643,7 +6643,7 @@
         <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
@@ -6667,7 +6667,7 @@
         <v>500</v>
       </c>
       <c r="AJ32" t="n">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AK32" t="n">
         <v>80</v>
@@ -6691,10 +6691,10 @@
         <v>8.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AS32" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AT32" t="n">
         <v>5.8</v>
@@ -6703,10 +6703,10 @@
         <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
@@ -6715,7 +6715,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BA32" t="n">
         <v>42</v>
@@ -6730,17 +6730,17 @@
         <v>60</v>
       </c>
       <c r="BE32" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BF32" t="n">
         <v>24</v>
       </c>
       <c r="BG32" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G33" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H33" t="n">
         <v>2.4</v>
@@ -6786,7 +6786,7 @@
         <v>3.45</v>
       </c>
       <c r="K33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L33" t="n">
         <v>1.41</v>
@@ -6795,25 +6795,25 @@
         <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
         <v>1.32</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R33" t="n">
         <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U33" t="n">
         <v>2.2</v>
@@ -6822,10 +6822,10 @@
         <v>1.69</v>
       </c>
       <c r="W33" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y33" t="n">
         <v>10.5</v>
@@ -6840,7 +6840,7 @@
         <v>13.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD33" t="n">
         <v>11.5</v>
@@ -6849,10 +6849,10 @@
         <v>25</v>
       </c>
       <c r="AF33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH33" t="n">
         <v>17</v>
@@ -6867,46 +6867,46 @@
         <v>38</v>
       </c>
       <c r="AL33" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM33" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO33" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT33" t="n">
         <v>12.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AX33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY33" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ33" t="n">
         <v>15</v>
@@ -6915,7 +6915,7 @@
         <v>34</v>
       </c>
       <c r="BB33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC33" t="n">
         <v>32</v>
@@ -6924,17 +6924,17 @@
         <v>42</v>
       </c>
       <c r="BE33" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BF33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG33" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -6971,10 +6971,10 @@
         <v>1.46</v>
       </c>
       <c r="H34" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I34" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>4.9</v>
@@ -6998,7 +6998,7 @@
         <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R34" t="n">
         <v>1.4</v>
@@ -7007,13 +7007,13 @@
         <v>3.35</v>
       </c>
       <c r="T34" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U34" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V34" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W34" t="n">
         <v>3.15</v>
@@ -7025,7 +7025,7 @@
         <v>75</v>
       </c>
       <c r="Z34" t="n">
-        <v>170</v>
+        <v>540</v>
       </c>
       <c r="AA34" t="n">
         <v>350</v>
@@ -7091,7 +7091,7 @@
         <v>10</v>
       </c>
       <c r="AV34" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW34" t="n">
         <v>16</v>
@@ -7115,7 +7115,7 @@
         <v>14.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE34" t="n">
         <v>42</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H35" t="n">
         <v>2.54</v>
@@ -7174,25 +7174,25 @@
         <v>2.96</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L35" t="n">
         <v>1.71</v>
       </c>
       <c r="M35" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N35" t="n">
         <v>2.32</v>
       </c>
       <c r="O35" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="P35" t="n">
         <v>1.41</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
         <v>1.14</v>
@@ -7201,7 +7201,7 @@
         <v>7.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U35" t="n">
         <v>1.65</v>
@@ -7264,7 +7264,7 @@
         <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP35" t="n">
         <v>6.4</v>
@@ -7297,10 +7297,10 @@
         <v>14.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA35" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB35" t="n">
         <v>9.800000000000001</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K36" t="n">
         <v>3.85</v>
@@ -7374,19 +7374,19 @@
         <v>1.45</v>
       </c>
       <c r="M36" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P36" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R36" t="n">
         <v>1.33</v>
@@ -7395,7 +7395,7 @@
         <v>3.9</v>
       </c>
       <c r="T36" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U36" t="n">
         <v>2.02</v>
@@ -7407,7 +7407,7 @@
         <v>1.89</v>
       </c>
       <c r="X36" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y36" t="n">
         <v>13.5</v>
@@ -7425,10 +7425,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD36" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE36" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AF36" t="n">
         <v>12.5</v>
@@ -7437,7 +7437,7 @@
         <v>12</v>
       </c>
       <c r="AH36" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AI36" t="n">
         <v>60</v>
@@ -7467,13 +7467,13 @@
         <v>12</v>
       </c>
       <c r="AR36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS36" t="n">
         <v>34</v>
       </c>
       <c r="AT36" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU36" t="n">
         <v>7.6</v>
@@ -7482,19 +7482,19 @@
         <v>14.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AX36" t="n">
         <v>11</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ36" t="n">
         <v>18</v>
       </c>
       <c r="BA36" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB36" t="n">
         <v>22</v>
@@ -7503,7 +7503,7 @@
         <v>20</v>
       </c>
       <c r="BD36" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BE36" t="n">
         <v>42</v>
@@ -7512,11 +7512,11 @@
         <v>15</v>
       </c>
       <c r="BG36" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-12 02:35:30</t>
+          <t>2026-03-12 04:53:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I2" t="n">
         <v>3.95</v>
       </c>
-      <c r="I2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD2" t="n">
         <v>27</v>
       </c>
-      <c r="AK2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>14</v>
-      </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
@@ -975,76 +975,76 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1000</v>
       </c>
-      <c r="AB3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>390</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AK3" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL3" t="n">
         <v>80</v>
@@ -1053,68 +1053,68 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO3" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="AT3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC3" t="n">
         <v>15.5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>16</v>
-      </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.98</v>
+        <v>2.64</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="I4" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
         <v>3.95</v>
@@ -1169,146 +1169,146 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.94</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AB4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD4" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AK4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
         <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>13</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
         <v>24</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF4" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I5" t="n">
         <v>1.9</v>
       </c>
-      <c r="I5" t="n">
-        <v>1.99</v>
-      </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.38</v>
@@ -1369,82 +1369,82 @@
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
         <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
         <v>17.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>34</v>
       </c>
       <c r="AG5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>85</v>
+        <v>300</v>
       </c>
       <c r="AK5" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>48</v>
+        <v>250</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP5" t="n">
         <v>15.5</v>
@@ -1456,19 +1456,19 @@
         <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>14.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1480,29 +1480,29 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC5" t="n">
         <v>22</v>
       </c>
       <c r="BD5" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BE5" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="J6" t="n">
         <v>3.7</v>
@@ -1557,16 +1557,16 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R6" t="n">
         <v>1.9</v>
@@ -1575,22 +1575,22 @@
         <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,13 +1599,13 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AC6" t="n">
         <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1623,40 +1623,40 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
         <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AS6" t="n">
         <v>10.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>7</v>
@@ -1665,7 +1665,7 @@
         <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AY6" t="n">
         <v>7</v>
@@ -1674,29 +1674,29 @@
         <v>5.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.9</v>
+        <v>19</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.8</v>
+        <v>17</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.43</v>
       </c>
       <c r="G7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="n">
         <v>9.199999999999999</v>
@@ -1739,10 +1739,10 @@
         <v>10.5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.36</v>
@@ -1754,22 +1754,22 @@
         <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T7" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="U7" t="n">
         <v>1.89</v>
@@ -1781,10 +1781,10 @@
         <v>3.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,13 +1793,13 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
@@ -1808,7 +1808,7 @@
         <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
         <v>75</v>
@@ -1817,19 +1817,19 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,37 +1838,37 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX7" t="n">
         <v>7.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AZ7" t="n">
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7" t="n">
         <v>10.5</v>
@@ -1880,17 +1880,17 @@
         <v>18</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG7" t="n">
         <v>15</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="H8" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="I8" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="J8" t="n">
         <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X8" t="n">
         <v>14.5</v>
@@ -1981,25 +1981,25 @@
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
         <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
@@ -2008,7 +2008,7 @@
         <v>17</v>
       </c>
       <c r="AI8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ8" t="n">
         <v>40</v>
@@ -2020,16 +2020,16 @@
         <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN8" t="n">
         <v>24</v>
       </c>
       <c r="AO8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
@@ -2041,7 +2041,7 @@
         <v>38</v>
       </c>
       <c r="AT8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
@@ -2053,7 +2053,7 @@
         <v>28</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY8" t="n">
         <v>11</v>
@@ -2062,7 +2062,7 @@
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
         <v>34</v>
@@ -2074,17 +2074,17 @@
         <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BF8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -2115,121 +2115,121 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I9" t="n">
         <v>2.22</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.24</v>
-      </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
         <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X9" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
         <v>30</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
         <v>7.4</v>
       </c>
       <c r="AD9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR9" t="n">
         <v>11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
         <v>27</v>
@@ -2238,47 +2238,47 @@
         <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="BC9" t="n">
         <v>44</v>
       </c>
       <c r="BD9" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="BE9" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BF9" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BG9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H10" t="n">
         <v>1.88</v>
@@ -2321,40 +2321,40 @@
         <v>1.89</v>
       </c>
       <c r="J10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.95</v>
       </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.96</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
         <v>2.12</v>
@@ -2363,19 +2363,19 @@
         <v>1.27</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z10" t="n">
         <v>11.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC10" t="n">
         <v>8.6</v>
@@ -2390,46 +2390,46 @@
         <v>34</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AK10" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="n">
         <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>380</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AO10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU10" t="n">
         <v>8</v>
@@ -2438,13 +2438,13 @@
         <v>9.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX10" t="n">
         <v>30</v>
       </c>
       <c r="AY10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>18</v>
@@ -2453,26 +2453,26 @@
         <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BD10" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="BE10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BF10" t="n">
         <v>55</v>
       </c>
       <c r="BG10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="G11" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
         <v>4.4</v>
@@ -2518,19 +2518,19 @@
         <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P11" t="n">
         <v>2.04</v>
@@ -2539,7 +2539,7 @@
         <v>1.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
         <v>3.3</v>
@@ -2551,16 +2551,16 @@
         <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z11" t="n">
         <v>32</v>
@@ -2575,7 +2575,7 @@
         <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
         <v>50</v>
@@ -2590,7 +2590,7 @@
         <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
         <v>24</v>
@@ -2602,19 +2602,19 @@
         <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AN11" t="n">
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP11" t="n">
         <v>14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
         <v>27</v>
@@ -2626,16 +2626,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW11" t="n">
         <v>42</v>
       </c>
       <c r="AX11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
@@ -2647,7 +2647,7 @@
         <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
         <v>18</v>
@@ -2656,7 +2656,7 @@
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF11" t="n">
         <v>12</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="G12" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="I12" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="J12" t="n">
         <v>3.45</v>
@@ -2715,55 +2715,55 @@
         <v>3.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="X12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
         <v>7.4</v>
@@ -2772,25 +2772,25 @@
         <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL12" t="n">
         <v>65</v>
@@ -2799,25 +2799,25 @@
         <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT12" t="n">
         <v>12</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>11.5</v>
       </c>
       <c r="AU12" t="n">
         <v>7.2</v>
@@ -2826,13 +2826,13 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AY12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>17.5</v>
@@ -2841,10 +2841,10 @@
         <v>38</v>
       </c>
       <c r="BB12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BC12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BD12" t="n">
         <v>55</v>
@@ -2856,11 +2856,11 @@
         <v>50</v>
       </c>
       <c r="BG12" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>2.56</v>
       </c>
       <c r="I13" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.15</v>
@@ -2915,13 +2915,13 @@
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
         <v>2.5</v>
@@ -2939,7 +2939,7 @@
         <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W13" t="n">
         <v>1.41</v>
@@ -2948,7 +2948,7 @@
         <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z13" t="n">
         <v>14.5</v>
@@ -2957,7 +2957,7 @@
         <v>38</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC13" t="n">
         <v>7</v>
@@ -2999,7 +2999,7 @@
         <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
         <v>7.8</v>
@@ -3014,10 +3014,10 @@
         <v>9.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
         <v>30</v>
@@ -3044,7 +3044,7 @@
         <v>55</v>
       </c>
       <c r="BE13" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF13" t="n">
         <v>50</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -3091,49 +3091,49 @@
         <v>3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.45</v>
       </c>
-      <c r="K14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W14" t="n">
         <v>1.4</v>
@@ -3142,34 +3142,34 @@
         <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA14" t="n">
         <v>34</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
         <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE14" t="n">
         <v>28</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG14" t="n">
         <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>46</v>
@@ -3178,31 +3178,31 @@
         <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL14" t="n">
         <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AO14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
         <v>13.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -3211,7 +3211,7 @@
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>26</v>
@@ -3220,13 +3220,13 @@
         <v>20</v>
       </c>
       <c r="AY14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB14" t="n">
         <v>60</v>
@@ -3241,14 +3241,14 @@
         <v>95</v>
       </c>
       <c r="BF14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BG14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J15" t="n">
         <v>3.55</v>
@@ -3297,79 +3297,79 @@
         <v>3.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="X15" t="n">
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
         <v>12</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
         <v>23</v>
@@ -3378,25 +3378,25 @@
         <v>40</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT15" t="n">
         <v>8.199999999999999</v>
@@ -3405,7 +3405,7 @@
         <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW15" t="n">
         <v>48</v>
@@ -3423,7 +3423,7 @@
         <v>55</v>
       </c>
       <c r="BB15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC15" t="n">
         <v>21</v>
@@ -3435,14 +3435,14 @@
         <v>95</v>
       </c>
       <c r="BF15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BG15" t="n">
         <v>50</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -3473,64 +3473,64 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="H16" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="T16" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="W16" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="X16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,104 +3539,104 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD16" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR16" t="n">
         <v>7</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>8</v>
-      </c>
       <c r="AS16" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU16" t="n">
         <v>13.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA16" t="n">
         <v>7</v>
       </c>
-      <c r="BA16" t="n">
-        <v>8</v>
-      </c>
       <c r="BB16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC16" t="n">
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE16" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE16" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF16" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G17" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H17" t="n">
         <v>3.05</v>
       </c>
       <c r="I17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
         <v>3.75</v>
@@ -3688,25 +3688,25 @@
         <v>1.42</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
         <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
         <v>1.71</v>
@@ -3715,22 +3715,22 @@
         <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X17" t="n">
         <v>15.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z17" t="n">
         <v>23</v>
       </c>
       <c r="AA17" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
         <v>11.5</v>
@@ -3760,16 +3760,16 @@
         <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
         <v>980</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
         <v>32</v>
@@ -3781,10 +3781,10 @@
         <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT17" t="n">
         <v>9.6</v>
@@ -3811,7 +3811,7 @@
         <v>36</v>
       </c>
       <c r="BB17" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BC17" t="n">
         <v>22</v>
@@ -3820,17 +3820,17 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF17" t="n">
         <v>18</v>
       </c>
       <c r="BG17" t="n">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I18" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L18" t="n">
         <v>1.44</v>
@@ -3888,34 +3888,34 @@
         <v>3.7</v>
       </c>
       <c r="O18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.35</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.34</v>
-      </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U18" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="n">
         <v>11</v>
@@ -3924,19 +3924,19 @@
         <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
         <v>11.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF18" t="n">
         <v>23</v>
@@ -3945,13 +3945,13 @@
         <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>320</v>
       </c>
       <c r="AK18" t="n">
         <v>95</v>
@@ -3960,19 +3960,19 @@
         <v>120</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
@@ -4002,10 +4002,10 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
         <v>27</v>
@@ -4014,17 +4014,17 @@
         <v>23</v>
       </c>
       <c r="BE18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BG18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4055,61 +4055,61 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I19" t="n">
         <v>2.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W19" t="n">
         <v>1.46</v>
       </c>
       <c r="X19" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Y19" t="n">
         <v>12.5</v>
@@ -4142,7 +4142,7 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ19" t="n">
         <v>55</v>
@@ -4157,13 +4157,13 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO19" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ19" t="n">
         <v>10</v>
@@ -4187,7 +4187,7 @@
         <v>21</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
@@ -4196,29 +4196,29 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BB19" t="n">
         <v>18</v>
       </c>
       <c r="BC19" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE19" t="n">
-        <v>28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I20" t="n">
         <v>2.44</v>
       </c>
-      <c r="I20" t="n">
-        <v>2.48</v>
-      </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
         <v>1.46</v>
@@ -4279,7 +4279,7 @@
         <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" t="n">
         <v>2.14</v>
@@ -4291,22 +4291,22 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
         <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z20" t="n">
         <v>15</v>
@@ -4315,7 +4315,7 @@
         <v>34</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
         <v>7.4</v>
@@ -4324,10 +4324,10 @@
         <v>11.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG20" t="n">
         <v>14</v>
@@ -4339,7 +4339,7 @@
         <v>42</v>
       </c>
       <c r="AJ20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="n">
         <v>38</v>
@@ -4363,10 +4363,10 @@
         <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
@@ -4378,16 +4378,16 @@
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX20" t="n">
         <v>20</v>
       </c>
       <c r="AY20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
         <v>38</v>
@@ -4399,20 +4399,20 @@
         <v>34</v>
       </c>
       <c r="BD20" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE20" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BF20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BG20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4449,55 +4449,55 @@
         <v>2.1</v>
       </c>
       <c r="H21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I21" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K21" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L21" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="M21" t="n">
         <v>1.19</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="O21" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="P21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
         <v>1.11</v>
       </c>
       <c r="S21" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
         <v>1.9</v>
       </c>
       <c r="X21" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="Y21" t="n">
         <v>11</v>
@@ -4509,25 +4509,25 @@
         <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AC21" t="n">
         <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE21" t="n">
         <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AI21" t="n">
         <v>500</v>
@@ -4548,31 +4548,31 @@
         <v>180</v>
       </c>
       <c r="AO21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR21" t="n">
         <v>32</v>
       </c>
       <c r="AS21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
         <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX21" t="n">
         <v>9</v>
@@ -4584,29 +4584,29 @@
         <v>32</v>
       </c>
       <c r="BA21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BB21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC21" t="n">
         <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE21" t="n">
         <v>100</v>
       </c>
       <c r="BF21" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BG21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4637,40 +4637,40 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G22" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I22" t="n">
         <v>4.8</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
       </c>
       <c r="J22" t="n">
         <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M22" t="n">
         <v>1.14</v>
       </c>
       <c r="N22" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P22" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="R22" t="n">
         <v>1.17</v>
@@ -4682,16 +4682,16 @@
         <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W22" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="X22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="n">
         <v>11.5</v>
@@ -4706,16 +4706,16 @@
         <v>6.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
         <v>700</v>
       </c>
       <c r="AF22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
         <v>12</v>
@@ -4727,7 +4727,7 @@
         <v>700</v>
       </c>
       <c r="AJ22" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK22" t="n">
         <v>32</v>
@@ -4739,28 +4739,28 @@
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AO22" t="n">
         <v>700</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
         <v>42</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV22" t="n">
         <v>19.5</v>
@@ -4769,16 +4769,16 @@
         <v>36</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
@@ -4793,14 +4793,14 @@
         <v>100</v>
       </c>
       <c r="BF22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG22" t="n">
         <v>44</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="K23" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="U23" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
         <v>44</v>
       </c>
       <c r="Z23" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AA23" t="n">
-        <v>810</v>
+        <v>990</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC23" t="n">
         <v>15.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AE23" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="AF23" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AI23" t="n">
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AK23" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM23" t="n">
-        <v>310</v>
+        <v>450</v>
       </c>
       <c r="AN23" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AR23" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU23" t="n">
         <v>14</v>
       </c>
       <c r="AV23" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AW23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BA23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE23" t="n">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5025,151 +5025,151 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="G24" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="H24" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="I24" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.02</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.9</v>
-      </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="V24" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>21</v>
       </c>
       <c r="AF24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>260</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW24" t="n">
         <v>18.5</v>
       </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>18</v>
-      </c>
       <c r="AX24" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AY24" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB24" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="BC24" t="n">
         <v>55</v>
@@ -5178,17 +5178,17 @@
         <v>60</v>
       </c>
       <c r="BE24" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="BF24" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BG24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="G25" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="H25" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.47</v>
@@ -5243,58 +5243,58 @@
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
         <v>2.16</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.99</v>
       </c>
-      <c r="U25" t="n">
-        <v>1.96</v>
-      </c>
       <c r="V25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="X25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA25" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD25" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF25" t="n">
         <v>11</v>
@@ -5306,83 +5306,83 @@
         <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM25" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AS25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV25" t="n">
         <v>17</v>
       </c>
-      <c r="AT25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AW25" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY25" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
         <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>16.5</v>
+        <v>60</v>
       </c>
       <c r="BB25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE25" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BF25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG25" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="G26" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="H26" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="I26" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="J26" t="n">
         <v>4.1</v>
@@ -5431,7 +5431,7 @@
         <v>4.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
@@ -5443,140 +5443,140 @@
         <v>1.26</v>
       </c>
       <c r="P26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U26" t="n">
         <v>2.18</v>
       </c>
-      <c r="Q26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.22</v>
-      </c>
       <c r="V26" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="W26" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE26" t="n">
         <v>17</v>
       </c>
       <c r="AF26" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG26" t="n">
         <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
         <v>32</v>
       </c>
       <c r="AJ26" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL26" t="n">
         <v>65</v>
       </c>
       <c r="AM26" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO26" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT26" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26" t="n">
         <v>9.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX26" t="n">
         <v>38</v>
       </c>
       <c r="AY26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
         <v>28</v>
       </c>
       <c r="BB26" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="BC26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BD26" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF26" t="n">
         <v>55</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
         <v>4.6</v>
       </c>
       <c r="K27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L27" t="n">
         <v>1.35</v>
@@ -5637,22 +5637,22 @@
         <v>1.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T27" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U27" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V27" t="n">
         <v>1.17</v>
@@ -5661,7 +5661,7 @@
         <v>2.72</v>
       </c>
       <c r="X27" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="n">
         <v>24</v>
@@ -5682,10 +5682,10 @@
         <v>25</v>
       </c>
       <c r="AE27" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG27" t="n">
         <v>9.800000000000001</v>
@@ -5700,10 +5700,10 @@
         <v>14.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM27" t="n">
         <v>100</v>
@@ -5712,13 +5712,13 @@
         <v>7.2</v>
       </c>
       <c r="AO27" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR27" t="n">
         <v>48</v>
@@ -5727,10 +5727,10 @@
         <v>44</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV27" t="n">
         <v>22</v>
@@ -5745,7 +5745,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
         <v>70</v>
@@ -5754,7 +5754,7 @@
         <v>13.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD27" t="n">
         <v>29</v>
@@ -5766,11 +5766,11 @@
         <v>6.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G28" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H28" t="n">
         <v>2.82</v>
       </c>
       <c r="I28" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J28" t="n">
         <v>3.45</v>
@@ -5819,7 +5819,7 @@
         <v>3.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
         <v>1.08</v>
@@ -5831,19 +5831,19 @@
         <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
         <v>3.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U28" t="n">
         <v>2.14</v>
@@ -5882,7 +5882,7 @@
         <v>17.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>17.5</v>
@@ -5906,7 +5906,7 @@
         <v>28</v>
       </c>
       <c r="AO28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP28" t="n">
         <v>12.5</v>
@@ -5915,7 +5915,7 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS28" t="n">
         <v>40</v>
@@ -5936,7 +5936,7 @@
         <v>16.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ28" t="n">
         <v>16</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5998,22 +5998,22 @@
         <v>2.12</v>
       </c>
       <c r="G29" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H29" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K29" t="n">
         <v>3.6</v>
       </c>
-      <c r="K29" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6022,10 +6022,10 @@
         <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P29" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
@@ -6034,19 +6034,19 @@
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U29" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X29" t="n">
         <v>13</v>
@@ -6055,10 +6055,10 @@
         <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA29" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB29" t="n">
         <v>8.800000000000001</v>
@@ -6070,19 +6070,19 @@
         <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF29" t="n">
         <v>12.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ29" t="n">
         <v>26</v>
@@ -6091,16 +6091,16 @@
         <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP29" t="n">
         <v>12</v>
@@ -6109,13 +6109,13 @@
         <v>12.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS29" t="n">
         <v>70</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU29" t="n">
         <v>7.4</v>
@@ -6124,10 +6124,10 @@
         <v>15</v>
       </c>
       <c r="AW29" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AX29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY29" t="n">
         <v>10</v>
@@ -6154,11 +6154,11 @@
         <v>16.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -6189,85 +6189,85 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G30" t="n">
         <v>4.4</v>
       </c>
       <c r="H30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I30" t="n">
         <v>1.99</v>
       </c>
-      <c r="I30" t="n">
-        <v>2.02</v>
-      </c>
       <c r="J30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P30" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U30" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V30" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
         <v>1.29</v>
       </c>
       <c r="X30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AB30" t="n">
         <v>14.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD30" t="n">
         <v>10.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG30" t="n">
         <v>17</v>
@@ -6276,28 +6276,28 @@
         <v>20</v>
       </c>
       <c r="AI30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ30" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AK30" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AL30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM30" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO30" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>8</v>
@@ -6306,40 +6306,40 @@
         <v>10.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV30" t="n">
         <v>9.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ30" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB30" t="n">
         <v>36</v>
       </c>
       <c r="BC30" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BD30" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE30" t="n">
         <v>40</v>
@@ -6348,11 +6348,11 @@
         <v>55</v>
       </c>
       <c r="BG30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="G31" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="H31" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="I31" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="J31" t="n">
         <v>3</v>
@@ -6401,136 +6401,136 @@
         <v>3.05</v>
       </c>
       <c r="L31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O31" t="n">
         <v>1.64</v>
       </c>
-      <c r="M31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.63</v>
-      </c>
       <c r="P31" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="R31" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V31" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="W31" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="Z31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD31" t="n">
         <v>13.5</v>
       </c>
-      <c r="AA31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE31" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AF31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG31" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AH31" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI31" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN31" t="n">
         <v>85</v>
       </c>
-      <c r="AK31" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>100</v>
-      </c>
       <c r="AO31" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP31" t="n">
         <v>7</v>
       </c>
       <c r="AQ31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU31" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY31" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BB31" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BD31" t="n">
         <v>38</v>
@@ -6542,11 +6542,11 @@
         <v>36</v>
       </c>
       <c r="BG31" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -6577,64 +6577,64 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="G32" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="J32" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M32" t="n">
         <v>1.16</v>
       </c>
       <c r="N32" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="P32" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
         <v>1.14</v>
       </c>
       <c r="S32" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="T32" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V32" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="X32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z32" t="n">
         <v>27</v>
@@ -6643,7 +6643,7 @@
         <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
@@ -6655,10 +6655,10 @@
         <v>170</v>
       </c>
       <c r="AF32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG32" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH32" t="n">
         <v>32</v>
@@ -6667,7 +6667,7 @@
         <v>500</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK32" t="n">
         <v>80</v>
@@ -6685,13 +6685,13 @@
         <v>500</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AR32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS32" t="n">
         <v>60</v>
@@ -6700,10 +6700,10 @@
         <v>5.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW32" t="n">
         <v>46</v>
@@ -6712,10 +6712,10 @@
         <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA32" t="n">
         <v>42</v>
@@ -6724,23 +6724,23 @@
         <v>29</v>
       </c>
       <c r="BC32" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD32" t="n">
         <v>60</v>
       </c>
       <c r="BE32" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF32" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BG32" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -6771,25 +6771,25 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="G33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J33" t="n">
         <v>3.4</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.45</v>
       </c>
       <c r="K33" t="n">
         <v>3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
@@ -6798,7 +6798,7 @@
         <v>3.9</v>
       </c>
       <c r="O33" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P33" t="n">
         <v>1.96</v>
@@ -6807,91 +6807,91 @@
         <v>2.02</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T33" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U33" t="n">
         <v>2.2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W33" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X33" t="n">
         <v>13.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB33" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC33" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD33" t="n">
         <v>11.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK33" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM33" t="n">
         <v>320</v>
       </c>
       <c r="AN33" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AO33" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AP33" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR33" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT33" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU33" t="n">
         <v>7.2</v>
@@ -6900,19 +6900,19 @@
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY33" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ33" t="n">
         <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB33" t="n">
         <v>48</v>
@@ -6921,20 +6921,20 @@
         <v>32</v>
       </c>
       <c r="BD33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE33" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BF33" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG33" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -6968,10 +6968,10 @@
         <v>1.44</v>
       </c>
       <c r="G34" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H34" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I34" t="n">
         <v>9.800000000000001</v>
@@ -6980,7 +6980,7 @@
         <v>4.9</v>
       </c>
       <c r="K34" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
         <v>1.39</v>
@@ -6998,7 +6998,7 @@
         <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R34" t="n">
         <v>1.4</v>
@@ -7016,28 +7016,28 @@
         <v>1.11</v>
       </c>
       <c r="W34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y34" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="Z34" t="n">
-        <v>540</v>
+        <v>85</v>
       </c>
       <c r="AA34" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AB34" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC34" t="n">
         <v>11</v>
       </c>
       <c r="AD34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE34" t="n">
         <v>160</v>
@@ -7046,13 +7046,13 @@
         <v>8</v>
       </c>
       <c r="AG34" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH34" t="n">
         <v>29</v>
       </c>
       <c r="AI34" t="n">
-        <v>470</v>
+        <v>150</v>
       </c>
       <c r="AJ34" t="n">
         <v>12</v>
@@ -7070,7 +7070,7 @@
         <v>7.6</v>
       </c>
       <c r="AO34" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP34" t="n">
         <v>15</v>
@@ -7079,10 +7079,10 @@
         <v>25</v>
       </c>
       <c r="AR34" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AS34" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AT34" t="n">
         <v>7.2</v>
@@ -7094,10 +7094,10 @@
         <v>30</v>
       </c>
       <c r="AW34" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AX34" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY34" t="n">
         <v>9.199999999999999</v>
@@ -7106,7 +7106,7 @@
         <v>25</v>
       </c>
       <c r="BA34" t="n">
-        <v>16.5</v>
+        <v>36</v>
       </c>
       <c r="BB34" t="n">
         <v>11</v>
@@ -7115,20 +7115,20 @@
         <v>14.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE34" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG34" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G35" t="n">
         <v>3.7</v>
@@ -7168,31 +7168,31 @@
         <v>2.54</v>
       </c>
       <c r="I35" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J35" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K35" t="n">
         <v>2.98</v>
       </c>
       <c r="L35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O35" t="n">
         <v>1.71</v>
       </c>
-      <c r="M35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.72</v>
-      </c>
       <c r="P35" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
         <v>1.14</v>
@@ -7201,58 +7201,58 @@
         <v>7.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U35" t="n">
         <v>1.65</v>
       </c>
       <c r="V35" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W35" t="n">
         <v>1.37</v>
       </c>
       <c r="X35" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>980</v>
+        <v>14.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>980</v>
+        <v>85</v>
       </c>
       <c r="AB35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE35" t="n">
         <v>980</v>
       </c>
       <c r="AF35" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AG35" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AH35" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AI35" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ35" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
         <v>120</v>
@@ -7264,65 +7264,65 @@
         <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="AP35" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR35" t="n">
         <v>12</v>
       </c>
       <c r="AS35" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AT35" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU35" t="n">
         <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW35" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AX35" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AZ35" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BA35" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="BB35" t="n">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BC35" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BD35" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BE35" t="n">
-        <v>10.5</v>
+        <v>110</v>
       </c>
       <c r="BF35" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BG35" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="G36" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="H36" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K36" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L36" t="n">
         <v>1.45</v>
@@ -7377,13 +7377,13 @@
         <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O36" t="n">
         <v>1.37</v>
       </c>
       <c r="P36" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q36" t="n">
         <v>2.1</v>
@@ -7395,128 +7395,128 @@
         <v>3.9</v>
       </c>
       <c r="T36" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="U36" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V36" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W36" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="X36" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF36" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y36" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD36" t="n">
+      <c r="AG36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN36" t="n">
         <v>20</v>
       </c>
-      <c r="AE36" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>21</v>
-      </c>
       <c r="AO36" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AP36" t="n">
         <v>12</v>
       </c>
       <c r="AQ36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF36" t="n">
         <v>18</v>
       </c>
-      <c r="AS36" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>15</v>
-      </c>
       <c r="BG36" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH30"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Estonian Esiliiga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:00:18</t>
+          <t>13:00:55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>FC Maardu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>FC Elva</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4</v>
+        <v>1.16</v>
       </c>
       <c r="J2" t="n">
-        <v>1.27</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,28 +787,28 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.21</v>
+        <v>7.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.5</v>
+        <v>1.13</v>
       </c>
       <c r="R2" t="n">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="S2" t="n">
-        <v>34</v>
+        <v>1.64</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>7.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -817,34 +817,34 @@
         <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AB2" t="n">
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.24</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -853,81 +853,81 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.22</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>46</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>70</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Estonian Esiliiga</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,75 +937,75 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:01:13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Maardu</t>
+          <t>Erokspor A.S</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Elva</t>
+          <t>Bandirmaspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>1.06</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9</v>
+        <v>90</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>200</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="P3" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>2.82</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>1.49</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.78</v>
+        <v>18</v>
       </c>
       <c r="X3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1029,99 +1029,99 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>250</v>
+        <v>6.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>250</v>
+        <v>14.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>630</v>
       </c>
       <c r="AN3" t="n">
-        <v>200</v>
+        <v>2.5</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="AW3" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="BE3" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>2.38</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.7</v>
+        <v>44</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erokspor A.S</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bandirmaspor</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>3.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.45</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>2.42</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>2.44</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="W4" t="n">
-        <v>3.15</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
-        <v>27</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>80</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>85</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>75</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19.5</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AL4" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.6</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW4" t="n">
         <v>27</v>
       </c>
-      <c r="AR4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AX4" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>50</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.800000000000001</v>
+        <v>90</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.7</v>
+        <v>48</v>
       </c>
       <c r="BG4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -1330,179 +1330,179 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
       <c r="G5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.04</v>
       </c>
-      <c r="H5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.91</v>
-      </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD5" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AE5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AS5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD5" t="n">
         <v>60</v>
       </c>
-      <c r="AF5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>36</v>
-      </c>
       <c r="BE5" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="BF5" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="BG5" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -1524,106 +1524,106 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="G6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.5</v>
       </c>
-      <c r="H6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
         <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AK6" t="n">
         <v>44</v>
@@ -1632,71 +1632,71 @@
         <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
         <v>40</v>
       </c>
       <c r="BB6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BC6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD6" t="n">
         <v>50</v>
       </c>
       <c r="BE6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BG6" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>1.99</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>2.14</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W7" t="n">
         <v>2</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.6</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC7" t="n">
         <v>7.6</v>
       </c>
       <c r="AD7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="n">
         <v>11</v>
       </c>
-      <c r="AE7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>28</v>
-      </c>
       <c r="AG7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW7" t="n">
         <v>55</v>
       </c>
-      <c r="AL7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>22</v>
-      </c>
       <c r="AX7" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BB7" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="BC7" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE7" t="n">
         <v>100</v>
       </c>
       <c r="BF7" t="n">
-        <v>50</v>
+        <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>17.5</v>
+        <v>65</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="H8" t="n">
-        <v>2.58</v>
+        <v>1.81</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.23</v>
       </c>
-      <c r="S8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X8" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC8" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Z8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AD8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF8" t="n">
         <v>38</v>
       </c>
-      <c r="AB8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>21</v>
-      </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AJ8" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AK8" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AM8" t="n">
         <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AO8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA8" t="n">
         <v>36</v>
       </c>
-      <c r="AP8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>48</v>
-      </c>
       <c r="BB8" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="BC8" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BD8" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BE8" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BF8" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="BG8" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="H9" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.16</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.98</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="W9" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AB9" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AF9" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AG9" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AN9" t="n">
         <v>110</v>
       </c>
       <c r="AO9" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AT9" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AX9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AY9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BB9" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BC9" t="n">
         <v>55</v>
       </c>
       <c r="BD9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BE9" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="BF9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BG9" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>4.1</v>
+        <v>2.76</v>
       </c>
       <c r="H10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.26</v>
       </c>
-      <c r="I10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="V10" t="n">
         <v>1.53</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD10" t="n">
         <v>12</v>
       </c>
-      <c r="AA10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU10" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AV10" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
       </c>
       <c r="AX10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG10" t="n">
         <v>24</v>
       </c>
-      <c r="AY10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>70</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>70</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>75</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>27</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>1.86</v>
       </c>
       <c r="G11" t="n">
-        <v>2.74</v>
+        <v>1.87</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
         <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="X11" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF11" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AG11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AO11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB11" t="n">
         <v>18.5</v>
       </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK11" t="n">
+      <c r="BC11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD11" t="n">
         <v>29</v>
       </c>
-      <c r="AL11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="BE11" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>23</v>
-      </c>
       <c r="BG11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.95</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="U12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W12" t="n">
         <v>4.3</v>
       </c>
-      <c r="I12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.02</v>
-      </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="Y12" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>610</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL12" t="n">
         <v>32</v>
       </c>
-      <c r="AA12" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AM12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX12" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="AY12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA12" t="n">
         <v>22</v>
       </c>
-      <c r="AK12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ12" t="n">
+      <c r="BB12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG12" t="n">
         <v>15</v>
       </c>
-      <c r="AR12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>44</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Batin</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.28</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="H13" t="n">
-        <v>11</v>
-      </c>
-      <c r="I13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="P13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU13" t="n">
         <v>7.4</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>610</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AV13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY13" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK13" t="n">
+      <c r="AZ13" t="n">
         <v>14</v>
       </c>
-      <c r="AL13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>24</v>
-      </c>
       <c r="BA13" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="BC13" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BD13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE13" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.75</v>
+        <v>18</v>
       </c>
       <c r="BG13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.56</v>
+        <v>2.48</v>
       </c>
       <c r="G14" t="n">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4</v>
+        <v>2.98</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>2.72</v>
+        <v>1.64</v>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT14" t="n">
         <v>10</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AU14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB14" t="n">
         <v>25</v>
       </c>
-      <c r="AE14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="BC14" t="n">
         <v>22</v>
       </c>
-      <c r="AI14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BE14" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>2.48</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>2.54</v>
       </c>
       <c r="J15" t="n">
         <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.46</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="X15" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR15" t="n">
         <v>14</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AS15" t="n">
         <v>28</v>
       </c>
-      <c r="AA15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG15" t="n">
+      <c r="AT15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="AW15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="BB15" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE15" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="BF15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BG15" t="n">
-        <v>50</v>
+        <v>19.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.78</v>
+        <v>1.56</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8</v>
+        <v>1.58</v>
       </c>
       <c r="H16" t="n">
-        <v>2.88</v>
+        <v>6.6</v>
       </c>
       <c r="I16" t="n">
-        <v>2.92</v>
+        <v>6.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.47</v>
       </c>
-      <c r="M16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>2.72</v>
       </c>
       <c r="X16" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Z16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP16" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN16" t="n">
+      <c r="AQ16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>80</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD16" t="n">
         <v>30</v>
       </c>
-      <c r="AO16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>38</v>
-      </c>
       <c r="BE16" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG16" t="n">
         <v>90</v>
       </c>
-      <c r="BF16" t="n">
-        <v>27</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>29</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>2.44</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="T17" t="n">
         <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.69</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="X17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF17" t="n">
         <v>12</v>
       </c>
-      <c r="Y17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK17" t="n">
         <v>22</v>
       </c>
-      <c r="AG17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>40</v>
-      </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.5</v>
+        <v>26</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="AT17" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AX17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC17" t="n">
         <v>20</v>
       </c>
-      <c r="AY17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>38</v>
-      </c>
       <c r="BD17" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BE17" t="n">
         <v>90</v>
       </c>
       <c r="BF17" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="BG17" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.5</v>
+        <v>2.74</v>
       </c>
       <c r="G18" t="n">
-        <v>5.6</v>
+        <v>2.78</v>
       </c>
       <c r="H18" t="n">
-        <v>1.71</v>
+        <v>2.92</v>
       </c>
       <c r="I18" t="n">
-        <v>1.72</v>
+        <v>2.94</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.79</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>2.38</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="X18" t="n">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
         <v>10.5</v>
       </c>
       <c r="Z18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB18" t="n">
         <v>10.5</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF18" t="n">
         <v>16.5</v>
       </c>
-      <c r="AB18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX18" t="n">
         <v>16</v>
       </c>
-      <c r="AF18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM18" t="n">
+      <c r="AY18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE18" t="n">
         <v>90</v>
       </c>
-      <c r="AN18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>55</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>75</v>
-      </c>
       <c r="BF18" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.26</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>1.27</v>
+        <v>3.45</v>
       </c>
       <c r="H19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>16.5</v>
-      </c>
-      <c r="I19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="X19" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>180</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>990</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>570</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>42</v>
       </c>
       <c r="BA19" t="n">
         <v>38</v>
       </c>
       <c r="BB19" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="BC19" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="BD19" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF19" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="BG19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="G20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="I20" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.5</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="T20" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="U20" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="W20" t="n">
         <v>1.21</v>
       </c>
       <c r="X20" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR20" t="n">
         <v>10</v>
       </c>
-      <c r="AA20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>9</v>
-      </c>
       <c r="AS20" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AT20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW20" t="n">
         <v>14.5</v>
       </c>
-      <c r="AU20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW20" t="n">
+      <c r="AX20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY20" t="n">
         <v>18.5</v>
       </c>
-      <c r="AX20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>19</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
         <v>65</v>
       </c>
       <c r="BC20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE20" t="n">
         <v>70</v>
       </c>
-      <c r="BD20" t="n">
-        <v>75</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>29</v>
-      </c>
       <c r="BF20" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="BG20" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="G21" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
         <v>3.2</v>
@@ -4461,22 +4461,22 @@
         <v>3.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O21" t="n">
         <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
         <v>1.17</v>
@@ -4485,19 +4485,19 @@
         <v>6.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W21" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
@@ -4506,58 +4506,58 @@
         <v>36</v>
       </c>
       <c r="AA21" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AB21" t="n">
         <v>6.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="AF21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG21" t="n">
         <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI21" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AJ21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN21" t="n">
         <v>27</v>
       </c>
-      <c r="AK21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>30</v>
-      </c>
       <c r="AO21" t="n">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AS21" t="n">
         <v>42</v>
@@ -4572,48 +4572,48 @@
         <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY21" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD21" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BE21" t="n">
         <v>110</v>
       </c>
       <c r="BF21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BG21" t="n">
         <v>65</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.02</v>
+        <v>5.9</v>
       </c>
       <c r="G22" t="n">
-        <v>2.06</v>
+        <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5</v>
+        <v>1.75</v>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>1.77</v>
       </c>
       <c r="J22" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.84</v>
       </c>
-      <c r="P22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S22" t="n">
-        <v>9</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.51</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>2.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.94</v>
+        <v>1.19</v>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA22" t="n">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="AB22" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AG22" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="AH22" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="AK22" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AL22" t="n">
         <v>110</v>
       </c>
       <c r="AM22" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX22" t="n">
         <v>40</v>
       </c>
-      <c r="AO22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9</v>
-      </c>
       <c r="AY22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>70</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>120</v>
+      </c>
+      <c r="BG22" t="n">
         <v>12.5</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>90</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>18</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.98</v>
+        <v>1.27</v>
       </c>
       <c r="G23" t="n">
-        <v>1.99</v>
+        <v>1.28</v>
       </c>
       <c r="H23" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>4.7</v>
+        <v>16.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.99</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="V23" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="X23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>990</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG23" t="n">
         <v>12</v>
       </c>
-      <c r="Y23" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AH23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>350</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW23" t="n">
         <v>110</v>
       </c>
-      <c r="AB23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AX23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY23" t="n">
         <v>11</v>
       </c>
-      <c r="AG23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW23" t="n">
+      <c r="AZ23" t="n">
         <v>40</v>
       </c>
-      <c r="AX23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>19</v>
-      </c>
       <c r="BA23" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BB23" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BD23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>160</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG23" t="n">
         <v>38</v>
       </c>
-      <c r="BE23" t="n">
-        <v>100</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>70</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="G24" t="n">
-        <v>4.4</v>
+        <v>1.99</v>
       </c>
       <c r="H24" t="n">
-        <v>1.98</v>
+        <v>5.9</v>
       </c>
       <c r="I24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X24" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>32</v>
-      </c>
       <c r="AG24" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AI24" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK24" t="n">
         <v>38</v>
       </c>
-      <c r="AJ24" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>55</v>
-      </c>
       <c r="AL24" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AM24" t="n">
         <v>500</v>
       </c>
       <c r="AN24" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AO24" t="n">
-        <v>14.5</v>
+        <v>600</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX24" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>28</v>
-      </c>
       <c r="AY24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17.5</v>
+        <v>38</v>
       </c>
       <c r="BA24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC24" t="n">
         <v>32</v>
       </c>
-      <c r="BB24" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC24" t="n">
+      <c r="BD24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE24" t="n">
         <v>46</v>
       </c>
-      <c r="BD24" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>40</v>
-      </c>
       <c r="BF24" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BG24" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.6</v>
       </c>
-      <c r="G25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
-      </c>
       <c r="L25" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="O25" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="P25" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="U25" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="V25" t="n">
-        <v>1.63</v>
+        <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="X25" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AA25" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AB25" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AF25" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
         <v>85</v>
       </c>
       <c r="AJ25" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="AK25" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AL25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO25" t="n">
         <v>110</v>
       </c>
-      <c r="AM25" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>60</v>
-      </c>
       <c r="AP25" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AX25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BA25" t="n">
         <v>65</v>
       </c>
       <c r="BB25" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="BC25" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BE25" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF25" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="BG25" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="G26" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="H26" t="n">
-        <v>3.7</v>
+        <v>1.96</v>
       </c>
       <c r="I26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.85</v>
       </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.1</v>
-      </c>
       <c r="L26" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>2.28</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.97</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.48</v>
+        <v>1.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Y26" t="n">
         <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AA26" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AF26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP26" t="n">
         <v>13</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AQ26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT26" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ26" t="n">
+      <c r="AU26" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV26" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>65</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF26" t="n">
         <v>50</v>
       </c>
-      <c r="AX26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>32</v>
-      </c>
       <c r="BG26" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="G27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q27" t="n">
         <v>3.2</v>
       </c>
-      <c r="H27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
       <c r="R27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.37</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.45</v>
-      </c>
       <c r="X27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD27" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="AE27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS27" t="n">
         <v>36</v>
       </c>
-      <c r="AB27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ27" t="n">
+      <c r="AT27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA27" t="n">
         <v>65</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>36</v>
       </c>
       <c r="BB27" t="n">
         <v>50</v>
       </c>
       <c r="BC27" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BD27" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BE27" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF27" t="n">
         <v>60</v>
       </c>
-      <c r="BF27" t="n">
-        <v>32</v>
-      </c>
       <c r="BG27" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.42</v>
+        <v>2.42</v>
       </c>
       <c r="G28" t="n">
-        <v>1.44</v>
+        <v>2.48</v>
       </c>
       <c r="H28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y28" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="I28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD28" t="n">
         <v>19</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AE28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH28" t="n">
         <v>30</v>
       </c>
-      <c r="Z28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>340</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="AI28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX28" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>65</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AY28" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
         <v>25</v>
       </c>
       <c r="BA28" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BB28" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BC28" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="BD28" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF28" t="n">
         <v>34</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BG28" t="n">
         <v>48</v>
       </c>
-      <c r="BF28" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>27</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>Vasco Da Gama</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="G29" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="H29" t="n">
         <v>2.52</v>
       </c>
       <c r="I29" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J29" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="K29" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="M29" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>2.34</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="P29" t="n">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>7.2</v>
+        <v>3.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.42</v>
+        <v>1.81</v>
       </c>
       <c r="U29" t="n">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="V29" t="n">
         <v>1.64</v>
       </c>
       <c r="W29" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="X29" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y29" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z29" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AC29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU29" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR29" t="n">
+      <c r="AV29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY29" t="n">
         <v>12</v>
       </c>
-      <c r="AS29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="BA29" t="n">
         <v>36</v>
       </c>
       <c r="BB29" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC29" t="n">
         <v>34</v>
       </c>
-      <c r="BC29" t="n">
-        <v>32</v>
-      </c>
       <c r="BD29" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BE29" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="BF29" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BG29" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-12 11:56:18</t>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>
@@ -6175,184 +6175,572 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.26</v>
+        <v>1.42</v>
       </c>
       <c r="G30" t="n">
-        <v>2.28</v>
+        <v>1.44</v>
       </c>
       <c r="H30" t="n">
-        <v>3.5</v>
+        <v>9.4</v>
       </c>
       <c r="I30" t="n">
-        <v>3.55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="M30" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="P30" t="n">
-        <v>1.9</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="S30" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="V30" t="n">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="W30" t="n">
-        <v>1.78</v>
+        <v>3.3</v>
       </c>
       <c r="X30" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="Y30" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="Z30" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="AA30" t="n">
-        <v>70</v>
+        <v>340</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AD30" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="AE30" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AG30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AJ30" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AL30" t="n">
         <v>40</v>
       </c>
       <c r="AM30" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-12 14:26:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X31" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN31" t="n">
         <v>110</v>
       </c>
-      <c r="AN30" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO30" t="n">
+      <c r="AO31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>65</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-12 14:26:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO32" t="n">
         <v>46</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AP32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX32" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY30" t="n">
+      <c r="AY32" t="n">
         <v>10</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="AZ32" t="n">
         <v>17.5</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BA32" t="n">
         <v>48</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BB32" t="n">
         <v>27</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BC32" t="n">
         <v>22</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BD32" t="n">
         <v>36</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BE32" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG32" t="n">
         <v>40</v>
       </c>
-      <c r="BF30" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>40</v>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2026-03-12 11:56:18</t>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-12 14:26:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Estonian Esiliiga</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:55</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Maardu</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Elva</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,147 +787,147 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:01:13</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erokspor A.S</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bandirmaspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -975,153 +975,153 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,186 +1136,186 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,179 +1330,179 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>15:45:02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.2</v>
+        <v>1.15</v>
       </c>
       <c r="G9" t="n">
-        <v>4.3</v>
+        <v>1.16</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
+        <v>46</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P9" t="n">
         <v>2.22</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>1.81</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="X9" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>450</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>350</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AK9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>520</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU9" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR9" t="n">
+      <c r="AV9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>85</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>55</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>75</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>150</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>80</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>24</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.76</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>2.8</v>
       </c>
-      <c r="I10" t="n">
-        <v>2.9</v>
-      </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.45</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>18.5</v>
       </c>
-      <c r="AG10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ10" t="n">
+      <c r="BE10" t="n">
         <v>40</v>
       </c>
-      <c r="AK10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>80</v>
-      </c>
       <c r="BF10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BG10" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>16:00:14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="G11" t="n">
-        <v>1.87</v>
+        <v>3.65</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>2.72</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>2.82</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>2.74</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>2.84</v>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>5.5</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>1.23</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.87</v>
+        <v>5.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>13.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="W11" t="n">
-        <v>2.14</v>
+        <v>1.37</v>
       </c>
       <c r="X11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV11" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AW11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY11" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AZ11" t="n">
         <v>38</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="BA11" t="n">
         <v>110</v>
       </c>
-      <c r="AB11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>50</v>
-      </c>
       <c r="BB11" t="n">
-        <v>18.5</v>
+        <v>75</v>
       </c>
       <c r="BC11" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="BD11" t="n">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="BE11" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
-        <v>10.5</v>
+        <v>130</v>
       </c>
       <c r="BG11" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Batin</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.82</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U12" t="n">
         <v>2.24</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.9</v>
       </c>
       <c r="V12" t="n">
         <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="X12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>610</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>46</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>990</v>
       </c>
       <c r="AI12" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV12" t="n">
         <v>10.5</v>
       </c>
-      <c r="AK12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS12" t="n">
+      <c r="AW12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB12" t="n">
         <v>14</v>
       </c>
-      <c r="AT12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BC12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="BE12" t="n">
-        <v>65</v>
+        <v>3.75</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.65</v>
+        <v>17</v>
       </c>
       <c r="BG12" t="n">
-        <v>15</v>
+        <v>3.05</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>1.94</v>
       </c>
       <c r="G13" t="n">
-        <v>3.15</v>
+        <v>1.95</v>
       </c>
       <c r="H13" t="n">
-        <v>2.42</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>2.52</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="AB13" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AK13" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AO13" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AS13" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="AT13" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
         <v>7.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AX13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>19</v>
       </c>
-      <c r="AY13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>14</v>
-      </c>
       <c r="BA13" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BB13" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE13" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="BF13" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.98</v>
+        <v>2.68</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S14" t="n">
         <v>4</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.45</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="W14" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR14" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL14" t="n">
+      <c r="AS14" t="n">
         <v>38</v>
       </c>
-      <c r="AM14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>36</v>
-      </c>
       <c r="AT14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
         <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB14" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="BC14" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BD14" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BE14" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="BF14" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="BG14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="H15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I15" t="n">
         <v>2.48</v>
       </c>
-      <c r="I15" t="n">
-        <v>2.54</v>
-      </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="U15" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Y15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD15" t="n">
         <v>11</v>
       </c>
-      <c r="Z15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AE15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR15" t="n">
         <v>13</v>
       </c>
-      <c r="AC15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>14</v>
-      </c>
       <c r="AS15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
         <v>10.5</v>
       </c>
       <c r="AW15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>60</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG15" t="n">
         <v>22</v>
       </c>
-      <c r="AX15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I16" t="n">
         <v>6.6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>6.8</v>
       </c>
       <c r="J16" t="n">
         <v>4.6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
         <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V16" t="n">
         <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X16" t="n">
         <v>19.5</v>
@@ -3536,19 +3536,19 @@
         <v>55</v>
       </c>
       <c r="AA16" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
@@ -3557,13 +3557,13 @@
         <v>9.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK16" t="n">
         <v>15.5</v>
@@ -3572,37 +3572,37 @@
         <v>32</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AO16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
         <v>50</v>
       </c>
       <c r="AS16" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -3611,13 +3611,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BB16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3626,24 +3626,24 @@
         <v>30</v>
       </c>
       <c r="BE16" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.08</v>
+        <v>4.8</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="I17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J17" t="n">
         <v>4.2</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1.9</v>
+        <v>1.26</v>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Z17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI17" t="n">
         <v>28</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AJ17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM17" t="n">
         <v>85</v>
       </c>
-      <c r="AB17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AN17" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN17" t="n">
+      <c r="AS17" t="n">
         <v>17</v>
       </c>
-      <c r="AO17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR17" t="n">
+      <c r="AT17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA17" t="n">
         <v>26</v>
       </c>
-      <c r="AS17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>65</v>
-      </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="BD17" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BE17" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="BF17" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="BG17" t="n">
-        <v>50</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.74</v>
+        <v>5.3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78</v>
+        <v>5.4</v>
       </c>
       <c r="H18" t="n">
-        <v>2.92</v>
+        <v>1.83</v>
       </c>
       <c r="I18" t="n">
-        <v>2.94</v>
+        <v>1.85</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V18" t="n">
         <v>2.18</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.51</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD18" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AE18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI18" t="n">
         <v>46</v>
       </c>
-      <c r="AB18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>48</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AM18" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="AO18" t="n">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS18" t="n">
         <v>17.5</v>
       </c>
-      <c r="AS18" t="n">
-        <v>42</v>
-      </c>
       <c r="AT18" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="AX18" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB18" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="BC18" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="BD18" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BE18" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="BF18" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="BG18" t="n">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="G19" t="n">
-        <v>3.45</v>
+        <v>1.26</v>
       </c>
       <c r="H19" t="n">
-        <v>2.42</v>
+        <v>16.5</v>
       </c>
       <c r="I19" t="n">
-        <v>2.44</v>
+        <v>17.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="K19" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>2.58</v>
       </c>
       <c r="U19" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.41</v>
+        <v>4.8</v>
       </c>
       <c r="X19" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>350</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG19" t="n">
         <v>12</v>
       </c>
-      <c r="Y19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>14</v>
-      </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="AI19" t="n">
-        <v>42</v>
+        <v>310</v>
       </c>
       <c r="AJ19" t="n">
-        <v>60</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>15.5</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
       </c>
       <c r="AM19" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>640</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR19" t="n">
         <v>100</v>
       </c>
-      <c r="AN19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AS19" t="n">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="AT19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY19" t="n">
         <v>11</v>
       </c>
-      <c r="AU19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>13</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="BA19" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="BB19" t="n">
-        <v>50</v>
+        <v>7.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="BD19" t="n">
         <v>46</v>
       </c>
       <c r="BE19" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="BF19" t="n">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5.4</v>
+        <v>1.97</v>
       </c>
       <c r="G20" t="n">
-        <v>5.6</v>
+        <v>2.02</v>
       </c>
       <c r="H20" t="n">
-        <v>1.71</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>1.72</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="P20" t="n">
-        <v>2.26</v>
+        <v>1.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.76</v>
+        <v>2.92</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>2.92</v>
+        <v>6.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="V20" t="n">
-        <v>2.38</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>1.98</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="Y20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>540</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>460</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY20" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG20" t="n">
+      <c r="AZ20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB20" t="n">
         <v>21</v>
       </c>
-      <c r="AH20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK20" t="n">
+      <c r="BC20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD20" t="n">
         <v>65</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="BE20" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG20" t="n">
         <v>65</v>
       </c>
-      <c r="AM20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>55</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>55</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="H21" t="n">
         <v>5.1</v>
       </c>
       <c r="I21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="M21" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="P21" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="S21" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="U21" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="X21" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
         <v>36</v>
       </c>
       <c r="AA21" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AC21" t="n">
         <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE21" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
         <v>10</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AI21" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="AJ21" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AK21" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AL21" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AM21" t="n">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AO21" t="n">
-        <v>190</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>32</v>
       </c>
       <c r="AS21" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>44</v>
+      </c>
+      <c r="BA21" t="n">
         <v>20</v>
       </c>
-      <c r="AW21" t="n">
-        <v>95</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>70</v>
-      </c>
       <c r="BB21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG21" t="n">
         <v>21</v>
       </c>
-      <c r="BC21" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>65</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2</v>
+        <v>1.91</v>
       </c>
       <c r="H22" t="n">
-        <v>1.75</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.77</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K22" t="n">
         <v>3.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="T22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W22" t="n">
         <v>2.1</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.19</v>
-      </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="Z22" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="AA22" t="n">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="AB22" t="n">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF22" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK22" t="n">
         <v>20</v>
       </c>
-      <c r="AF22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>100</v>
-      </c>
       <c r="AL22" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="AM22" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>600</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="AP22" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="AS22" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="AT22" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="AU22" t="n">
         <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="AX22" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AY22" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BB22" t="n">
-        <v>100</v>
+        <v>19.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="BD22" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BF22" t="n">
-        <v>120</v>
+        <v>12.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>12.5</v>
+        <v>65</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,184 +4817,184 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.27</v>
+        <v>4.3</v>
       </c>
       <c r="G23" t="n">
-        <v>1.28</v>
+        <v>4.5</v>
       </c>
       <c r="H23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY23" t="n">
         <v>16</v>
       </c>
-      <c r="I23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>990</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH23" t="n">
+      <c r="AZ23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>60</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF23" t="n">
         <v>50</v>
       </c>
-      <c r="AI23" t="n">
-        <v>350</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>370</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>120</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU23" t="n">
+      <c r="BG23" t="n">
         <v>13</v>
       </c>
-      <c r="AV23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>40</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>160</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>38</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.95</v>
+        <v>3.65</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99</v>
+        <v>3.7</v>
       </c>
       <c r="H24" t="n">
-        <v>5.9</v>
+        <v>2.56</v>
       </c>
       <c r="I24" t="n">
-        <v>6.2</v>
+        <v>2.58</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="L24" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="M24" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="N24" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="O24" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="P24" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="S24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB24" t="n">
         <v>9</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AC24" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AD24" t="n">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="AF24" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH24" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AI24" t="n">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="AK24" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AL24" t="n">
         <v>110</v>
       </c>
       <c r="AM24" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AN24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS24" t="n">
         <v>36</v>
       </c>
-      <c r="AO24" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR24" t="n">
+      <c r="AT24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW24" t="n">
         <v>38</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AX24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>24</v>
       </c>
-      <c r="AT24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>38</v>
-      </c>
       <c r="BA24" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="BB24" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="BC24" t="n">
         <v>32</v>
       </c>
       <c r="BD24" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BE24" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF24" t="n">
         <v>46</v>
       </c>
-      <c r="BF24" t="n">
-        <v>32</v>
-      </c>
       <c r="BG24" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,184 +5205,184 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="N25" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="O25" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="P25" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="S25" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="X25" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
         <v>32</v>
       </c>
       <c r="AA25" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC25" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC25" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AD25" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AI25" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="AK25" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AL25" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN25" t="n">
-        <v>18.5</v>
+        <v>600</v>
       </c>
       <c r="AO25" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AR25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB25" t="n">
         <v>28</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="BC25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD25" t="n">
         <v>50</v>
       </c>
-      <c r="AT25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>40</v>
-      </c>
       <c r="BE25" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="BF25" t="n">
-        <v>17</v>
+        <v>7.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>75</v>
+        <v>8.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vasco Da Gama</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="G26" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="H26" t="n">
-        <v>1.96</v>
+        <v>2.54</v>
       </c>
       <c r="I26" t="n">
-        <v>1.99</v>
+        <v>2.56</v>
       </c>
       <c r="J26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S26" t="n">
         <v>3.8</v>
       </c>
-      <c r="K26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T26" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="U26" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V26" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>440</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP26" t="n">
         <v>12</v>
       </c>
-      <c r="AA26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AQ26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS26" t="n">
         <v>32</v>
       </c>
-      <c r="AG26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR26" t="n">
+      <c r="AT26" t="n">
         <v>11</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AU26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG26" t="n">
         <v>20</v>
       </c>
-      <c r="AT26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>44</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>50</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>13</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.6</v>
+        <v>1.42</v>
       </c>
       <c r="G27" t="n">
-        <v>3.7</v>
+        <v>1.44</v>
       </c>
       <c r="H27" t="n">
-        <v>2.58</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>2.98</v>
+        <v>5.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="M27" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.69</v>
+        <v>1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>1.44</v>
+        <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="S27" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="V27" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="W27" t="n">
-        <v>1.37</v>
+        <v>3.25</v>
       </c>
       <c r="X27" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>340</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN27" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>110</v>
-      </c>
       <c r="AO27" t="n">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="AR27" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="AS27" t="n">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="AT27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX27" t="n">
         <v>8</v>
       </c>
-      <c r="AU27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>20</v>
-      </c>
       <c r="AY27" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
         <v>24</v>
       </c>
       <c r="BA27" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE27" t="n">
         <v>65</v>
       </c>
-      <c r="BB27" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>48</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>100</v>
-      </c>
       <c r="BF27" t="n">
-        <v>60</v>
+        <v>6.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>46</v>
+        <v>18.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="G28" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="H28" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="I28" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>2.32</v>
+        <v>3.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="P28" t="n">
-        <v>1.43</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="R28" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="U28" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="X28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU28" t="n">
         <v>7.2</v>
       </c>
-      <c r="Y28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF28" t="n">
+      <c r="AV28" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>16</v>
-      </c>
       <c r="AW28" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AX28" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="BA28" t="n">
         <v>48</v>
       </c>
       <c r="BB28" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BC28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD28" t="n">
         <v>34</v>
       </c>
-      <c r="BD28" t="n">
-        <v>55</v>
-      </c>
       <c r="BE28" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BF28" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="BG28" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>CA Huracan</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="G29" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="H29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.52</v>
       </c>
-      <c r="I29" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.81</v>
-      </c>
       <c r="U29" t="n">
-        <v>2.16</v>
+        <v>1.61</v>
       </c>
       <c r="V29" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W29" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="X29" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA29" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AB29" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AC29" t="n">
         <v>7.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV29" t="n">
         <v>13</v>
       </c>
-      <c r="AH29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK29" t="n">
+      <c r="AW29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA29" t="n">
         <v>38</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="BB29" t="n">
         <v>48</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="BC29" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE29" t="n">
         <v>100</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="BF29" t="n">
         <v>65</v>
       </c>
-      <c r="AO29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB29" t="n">
+      <c r="BG29" t="n">
         <v>50</v>
       </c>
-      <c r="BC29" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>40</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>20</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,572 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L30" t="n">
         <v>1.42</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.36</v>
-      </c>
       <c r="M30" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.27</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.3</v>
-      </c>
       <c r="X30" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC30" t="n">
         <v>36</v>
       </c>
-      <c r="AE30" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>14</v>
-      </c>
       <c r="BD30" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE30" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF30" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-12 14:26:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CA Huracan</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X31" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>65</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>50</v>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026-03-12 14:26:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Brazilian Serie A</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Gremio</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Red Bull Bragantino</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>40</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-03-12 14:26:03</t>
+          <t>2026-03-12 16:57:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,17 +743,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-12 19:42:14</t>
+          <t>2026-03-12 22:13:16</t>
         </is>
       </c>
     </row>
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:04</t>
+          <t>19:30:05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vasco Da Gama</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-12 19:42:14</t>
+          <t>2026-03-12 22:13:16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>20:02:06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6</v>
+        <v>1.02</v>
       </c>
       <c r="H4" t="n">
-        <v>2.58</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.96</v>
+        <v>95</v>
       </c>
       <c r="K4" t="n">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
-        <v>2.44</v>
+        <v>5.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85</v>
+        <v>5.8</v>
       </c>
       <c r="AK4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.8</v>
+        <v>3.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>3.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>38</v>
+        <v>3.75</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>3.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>3.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>40</v>
+        <v>3.75</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>1.71</v>
       </c>
       <c r="AY4" t="n">
-        <v>16</v>
+        <v>3.75</v>
       </c>
       <c r="AZ4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="BB4" t="n">
-        <v>70</v>
+        <v>3.85</v>
       </c>
       <c r="BC4" t="n">
-        <v>50</v>
+        <v>3.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="BE4" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="BF4" t="n">
-        <v>90</v>
+        <v>3.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>48</v>
+        <v>3.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-12 19:42:14</t>
+          <t>2026-03-12 22:13:16</t>
         </is>
       </c>
     </row>
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>21:30:03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>CA Huracan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>3.65</v>
       </c>
       <c r="G5" t="n">
-        <v>2.34</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q5" t="n">
         <v>4.1</v>
       </c>
-      <c r="I5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.25</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="S5" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AC5" t="n">
         <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>570</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR5" t="n">
         <v>12</v>
       </c>
-      <c r="AG5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>390</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>23</v>
-      </c>
       <c r="AS5" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU5" t="n">
         <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BA5" t="n">
-        <v>95</v>
+        <v>10.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="BC5" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BD5" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="BE5" t="n">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="BF5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="BG5" t="n">
-        <v>75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-12 19:42:14</t>
+          <t>2026-03-12 22:13:16</t>
         </is>
       </c>
     </row>
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:30:13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>1.52</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="I6" t="n">
-        <v>2.52</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.14</v>
+        <v>1.54</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="V6" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.43</v>
+        <v>2.92</v>
       </c>
       <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB6" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="BC6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF6" t="n">
         <v>9.6</v>
       </c>
-      <c r="Z6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>40</v>
-      </c>
       <c r="BG6" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-12 19:42:14</t>
+          <t>2026-03-12 22:13:16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,766 +1713,184 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.47</v>
+        <v>3.8</v>
       </c>
       <c r="G7" t="n">
-        <v>1.49</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>8.199999999999999</v>
+        <v>2.04</v>
       </c>
       <c r="I7" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U7" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.93</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
-        <v>3</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>310</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.6</v>
+        <v>60</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
       </c>
       <c r="AI7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL7" t="n">
         <v>110</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AM7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AK7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL7" t="n">
+      <c r="AZ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD7" t="n">
         <v>36</v>
       </c>
-      <c r="AM7" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD7" t="n">
+      <c r="BE7" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF7" t="n">
         <v>32</v>
       </c>
-      <c r="BE7" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG7" t="n">
-        <v>120</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-12 19:42:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CA Huracan</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>27</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>80</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>80</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>65</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2026-03-12 19:42:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Brazilian Serie A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Gremio</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Red Bull Bragantino</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X9" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-03-12 19:42:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Platense FC</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CD Olimpia</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X10" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2026-03-12 19:42:14</t>
+          <t>2026-03-12 22:13:16</t>
         </is>
       </c>
     </row>
